--- a/projects/Assumption_Log.xlsx
+++ b/projects/Assumption_Log.xlsx
@@ -49,7 +49,7 @@
       <color rgb="FF808080"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="15">
     <fill>
       <patternFill/>
     </fill>
@@ -111,6 +111,16 @@
         <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DEEAF6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -153,7 +163,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -199,6 +209,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -744,7 +760,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="8.21875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1508,6 +1524,276 @@
         <is>
           <t>6</t>
         </is>
+      </c>
+    </row>
+    <row r="17" ht="58.05" customHeight="1">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>QNL-023</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C17" s="17" t="inlineStr">
+        <is>
+          <t>Structure</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="inlineStr">
+        <is>
+          <t>Metadata</t>
+        </is>
+      </c>
+      <c r="E17" s="11" t="inlineStr">
+        <is>
+          <t>12 equipment families (AHU, FCU, DX, HEX, pumps, CCU, EF, generator, pressurisation, climate)</t>
+        </is>
+      </c>
+      <c r="F17" s="11" t="inlineStr">
+        <is>
+          <t>Manufacturer datasheets give properties per component (cooling coil, fans, motors, outdoor unit)</t>
+        </is>
+      </c>
+      <c r="G17" s="11" t="inlineStr">
+        <is>
+          <t>Added the 16 metadata predicates in the Dar Cairo/SSC/HQ row shapes: literals as props, quantities as &lt;blanknode&gt; value+unit; component properties on brick:hasPart sub-entities (CHW-Coil, SF, RF, Motor, OD) - all Brick 1.4 classes, no para: minted</t>
+        </is>
+      </c>
+      <c r="H17" s="11" t="inlineStr">
+        <is>
+          <t>The three reference models attach component metadata to sub-entities and write quantities as blanknodes</t>
+        </is>
+      </c>
+      <c r="I17" s="11" t="n">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="18" ht="58.05" customHeight="1">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>QNL-024</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C18" s="13" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="inlineStr">
+        <is>
+          <t>Metadata</t>
+        </is>
+      </c>
+      <c r="E18" s="11" t="inlineStr">
+        <is>
+          <t>All quantity metadata rows</t>
+        </is>
+      </c>
+      <c r="F18" s="11" t="inlineStr">
+        <is>
+          <t>QF HQ v0.4 carries several wrong brick:hasUnit (air flow as unit:V, cooling capacity as unit:HZ)</t>
+        </is>
+      </c>
+      <c r="G18" s="11" t="inlineStr">
+        <is>
+          <t>Took brick:value and brick:hasUnit from the workbook's 'Value (Dar Cairo)' / 'Unit (QUDT)' columns, never HQ's</t>
+        </is>
+      </c>
+      <c r="H18" s="11" t="inlineStr">
+        <is>
+          <t>Dar Cairo is the unit authority; HQ's own README documents its units as wrong</t>
+        </is>
+      </c>
+      <c r="I18" s="11" t="n">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="19" ht="58.05" customHeight="1">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>QNL-025</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C19" s="18" t="inlineStr">
+        <is>
+          <t>Identifier</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="inlineStr">
+        <is>
+          <t>Metadata</t>
+        </is>
+      </c>
+      <c r="E19" s="11" t="inlineStr">
+        <is>
+          <t>Heat exchangers, pumps, generator</t>
+        </is>
+      </c>
+      <c r="F19" s="11" t="inlineStr">
+        <is>
+          <t>Datasheets tag them PHX/B/01-05, CHWP/B/01-04, 'GENERATOR SET'; the ontology has HEX01-05, CHW_P01-04, ELEC_Gen</t>
+        </is>
+      </c>
+      <c r="G19" s="11" t="inlineStr">
+        <is>
+          <t>Joined HEX by index (PHX/B/0n -&gt; HEX0n, user-confirmed), pumps CHWP/B/0n -&gt; CHW_P0n, generator -&gt; ELEC_Gen</t>
+        </is>
+      </c>
+      <c r="H19" s="11" t="inlineStr">
+        <is>
+          <t>Prefixes differ but the units correspond 1:1 by number/position</t>
+        </is>
+      </c>
+      <c r="I19" s="11" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" ht="58.05" customHeight="1">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>QNL-026</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C20" s="16" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="inlineStr">
+        <is>
+          <t>Metadata</t>
+        </is>
+      </c>
+      <c r="E20" s="11" t="inlineStr">
+        <is>
+          <t>FCU family - 94 of 137 units</t>
+        </is>
+      </c>
+      <c r="F20" s="11" t="inlineStr">
+        <is>
+          <t>FCU datasheets are 28 Euroclima selection sheets keyed by position (B/03,04; 1F/04-54), one model per group</t>
+        </is>
+      </c>
+      <c r="G20" s="11" t="inlineStr">
+        <is>
+          <t>Expanded each selection-sheet tag to the FCUs it names and wrote its model/capacity/flow/power to every unit in the group</t>
+        </is>
+      </c>
+      <c r="H20" s="11" t="inlineStr">
+        <is>
+          <t>The selection sheet groups identical units under one model; the group tag names them explicitly</t>
+        </is>
+      </c>
+      <c r="I20" s="11" t="n">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="21" ht="58.05" customHeight="1">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>QNL-027</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C21" s="16" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="inlineStr">
+        <is>
+          <t>Metadata</t>
+        </is>
+      </c>
+      <c r="E21" s="11" t="inlineStr">
+        <is>
+          <t>FCU 2F 06-33; closed control units; climate &amp; pressurisation units; out-of-range CAV/VAV/EF</t>
+        </is>
+      </c>
+      <c r="F21" s="11" t="inlineStr">
+        <is>
+          <t>Their datasheet tags do not correspond to any ontology entity (2F numbers 06-33 vs 034-062; CC/B vs CCU_808n; no MCG/PU entity; units absent from the register)</t>
+        </is>
+      </c>
+      <c r="G21" s="11" t="inlineStr">
+        <is>
+          <t>Left them without metadata and reported every tag in QNL_metadata_join_report.csv; did not guess a join</t>
+        </is>
+      </c>
+      <c r="H21" s="11" t="inlineStr">
+        <is>
+          <t>User confirmed FCU 2F 06-33 are different units, not a numbering offset; the rest have no matching entity - do not assume metadata a source cannot place</t>
+        </is>
+      </c>
+      <c r="I21" s="11" t="n">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="22" ht="58.05" customHeight="1">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>QNL-028</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C22" s="18" t="inlineStr">
+        <is>
+          <t>Identifier</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="inlineStr">
+        <is>
+          <t>All layers</t>
+        </is>
+      </c>
+      <c r="E22" s="11" t="inlineStr">
+        <is>
+          <t>Every subject/object identifier</t>
+        </is>
+      </c>
+      <c r="F22" s="11" t="inlineStr">
+        <is>
+          <t>Points were named as BMS tokens (AvgSpcHumd_PV, RunSts); equipment/rooms used '_' between word-parts</t>
+        </is>
+      </c>
+      <c r="G22" s="11" t="inlineStr">
+        <is>
+          <t>Aligned to Dar Cairo: datapoints renamed to dashed English from label or class (Return-Temperature, Run-Status); equipment/part tags kept their industry codes (AHU, SF, CHW-Coil) with '_'-&gt;'-' within the tag; 277 room name-words dashed. ref:hasTimeseriesId/para:hasEntityId untouched; crosswalk written</t>
+        </is>
+      </c>
+      <c r="H22" s="11" t="inlineStr">
+        <is>
+          <t>Client asked to match Dar Cairo's naming convention; camelCase 71%-&gt;0%, join keys preserved via the crosswalk</t>
+        </is>
+      </c>
+      <c r="I22" s="11" t="n">
+        <v>3753</v>
       </c>
     </row>
   </sheetData>

--- a/projects/Assumption_Log.xlsx
+++ b/projects/Assumption_Log.xlsx
@@ -760,7 +760,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="8.21875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1794,6 +1794,96 @@
       </c>
       <c r="I22" s="11" t="n">
         <v>3753</v>
+      </c>
+    </row>
+    <row r="23" ht="58.05" customHeight="1">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>QNL-029</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C23" s="17" t="inlineStr">
+        <is>
+          <t>Structure</t>
+        </is>
+      </c>
+      <c r="D23" s="11" t="inlineStr">
+        <is>
+          <t>Metadata</t>
+        </is>
+      </c>
+      <c r="E23" s="11" t="inlineStr">
+        <is>
+          <t>FCU/AHU/HEX control valves; FCU 2F 034-062 and 1F 059-065</t>
+        </is>
+      </c>
+      <c r="F23" s="11" t="inlineStr">
+        <is>
+          <t>The BAS valve schedule (BAS_QNL_Assets.pdf) gives each unit's CHW control-valve model, FCU actuator model and design flow</t>
+        </is>
+      </c>
+      <c r="G23" s="11" t="inlineStr">
+        <is>
+          <t>Added a brick:Cooling_Valve part to every FCU/AHU/HEX with rec:modelNumber (FCU valves+actuators Honeywell; AHU/HEX valves ITQ, make not stated); FCU actuator as a para:Valve_Actuator sub-part; gap-filled para:ratedChilledWaterFlowrate on the 43 FCUs that had none (all of 2F 034-062, 1F 059-065)</t>
+        </is>
+      </c>
+      <c r="H23" s="11" t="inlineStr">
+        <is>
+          <t>The BAS is a valid as-built source; brick:Cooling_Valve is Dar Cairo's CHW-valve class (76 uses); para:Valve_Actuator minted (no Brick/Dar Cairo/SSC class for a valve actuator)</t>
+        </is>
+      </c>
+      <c r="I23" s="11" t="n">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="24" ht="58.05" customHeight="1">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>QNL-030</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="C24" s="13" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="inlineStr">
+        <is>
+          <t>Metadata</t>
+        </is>
+      </c>
+      <c r="E24" s="11" t="inlineStr">
+        <is>
+          <t>FCU 1F-002, 1F-003, 2F-005 chilled-water flow</t>
+        </is>
+      </c>
+      <c r="F24" s="11" t="inlineStr">
+        <is>
+          <t>The BAS valve schedule gives 0.36 L/s where the Euroclima selection sheet gave 0.27 L/s</t>
+        </is>
+      </c>
+      <c r="G24" s="11" t="inlineStr">
+        <is>
+          <t>Kept the Euroclima value; did not overwrite. Flagged for the supplier. The other 91 of 94 shared FCUs agree within +/-0.02 L/s, verifying the metadata</t>
+        </is>
+      </c>
+      <c r="H24" s="11" t="inlineStr">
+        <is>
+          <t>Two sources, minor disagreement on 3 units; the Euroclima selection sheet is the equipment nameplate, the BAS the valve sizing - a supplier question, not ours to resolve</t>
+        </is>
+      </c>
+      <c r="I24" s="11" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/projects/Assumption_Log.xlsx
+++ b/projects/Assumption_Log.xlsx
@@ -49,7 +49,7 @@
       <color rgb="FF808080"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="16">
     <fill>
       <patternFill/>
     </fill>
@@ -121,6 +121,11 @@
         <fgColor rgb="00DDEBF7"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FBE5D6"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -163,7 +168,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -215,6 +220,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -582,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="8.21875" customWidth="1" min="1" max="1"/>
@@ -648,17 +656,272 @@
     <row r="2" ht="58.05" customHeight="1">
       <c r="A2" s="10" t="inlineStr">
         <is>
-          <t>(no entries yet)</t>
-        </is>
-      </c>
-      <c r="B2" s="11" t="n"/>
-      <c r="C2" s="11" t="n"/>
-      <c r="D2" s="11" t="n"/>
-      <c r="E2" s="11" t="n"/>
-      <c r="F2" s="11" t="n"/>
-      <c r="G2" s="11" t="n"/>
-      <c r="H2" s="11" t="n"/>
-      <c r="I2" s="11" t="n"/>
+          <t>SSC-001</t>
+        </is>
+      </c>
+      <c r="B2" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C2" s="15" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="D2" s="11" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>7 exhaust fans: GEFB0001, KEF0103, KEF0303, TEF0101, TEF0102, TEF0301, TEF0302</t>
+        </is>
+      </c>
+      <c r="F2" s="11" t="inlineStr">
+        <is>
+          <t>All seven carry rec:locatedIn entity:Level7_Office0367, and that room entity carries no rdfs:label_en anywhere in the sheet - so it has no readable name.</t>
+        </is>
+      </c>
+      <c r="G2" s="11" t="inlineStr">
+        <is>
+          <t>Left the triples as delivered and flagged all seven for the client. Two of them are settled by the screens: KEF0103 is drawn in 01.005 KITCHEN and TEF0101 in 01.028 CORRIDOR (SSC/FF-part2).</t>
+        </is>
+      </c>
+      <c r="H2" s="11" t="inlineStr">
+        <is>
+          <t>A room with no label cannot be shown in the front end and cannot be checked against a drawing. Seven fans on seven different levels sharing one seventh-floor office reads as a fill-down, not as seven readings.</t>
+        </is>
+      </c>
+      <c r="I2" s="11" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" ht="58.05" customHeight="1">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>SSC-002</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="D3" s="11" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="E3" s="11" t="inlineStr">
+        <is>
+          <t>Every other located SSC entity</t>
+        </is>
+      </c>
+      <c r="F3" s="11" t="inlineStr">
+        <is>
+          <t>All 166 rec:locatedIn rows in SSC_Ontology_Ver0.6 name a real room entity - no entity:&lt;Location&gt; placeholders, no blank objects.</t>
+        </is>
+      </c>
+      <c r="G3" s="11" t="inlineStr">
+        <is>
+          <t>Recorded the check; nothing to raise.</t>
+        </is>
+      </c>
+      <c r="H3" s="11" t="inlineStr">
+        <is>
+          <t>Stated so the SSC sheet is not read as silent on the question that HQ fails. SSC has no equipment carrying points and no rec:locatedIn at all.</t>
+        </is>
+      </c>
+      <c r="I3" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" ht="58.05" customHeight="1">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>SSC-003</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="E4" s="11" t="inlineStr">
+        <is>
+          <t>DX-B-0001, DX-B-0002, DX-B-0004, DX-B-0006, DX-B-0007, DX-B-0008, DX-B-0009, DX-B-0010, CCU-B-0004, CCU-B-0007</t>
+        </is>
+      </c>
+      <c r="F4" s="11" t="inlineStr">
+        <is>
+          <t>The ontology room and the room the BMS serving-area leader points at differ on all ten. DX-B-0009 is B1.020 FM STORAGE in the ontology and B.002 HV ROOM on the screen; CCU-B-0007 is B1.017 MDF-2 against B.026 MDF/SER.1.</t>
+        </is>
+      </c>
+      <c r="G4" s="11" t="inlineStr">
+        <is>
+          <t>Did not overwrite the ontology. Wrote the screen room beside it and flagged all ten in HQ_SSC_equipment_rooms.xlsx for the client to settle.</t>
+        </is>
+      </c>
+      <c r="H4" s="11" t="inlineStr">
+        <is>
+          <t>Two as-built sources disagree. The screen is the live BMS graphic and the ontology room came from the register, so neither can be assumed correct - a guess written into the room column is indistinguishable from a reading.</t>
+        </is>
+      </c>
+      <c r="I4" s="11" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" ht="58.05" customHeight="1">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>SSC-004</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C5" s="19" t="inlineStr">
+        <is>
+          <t>Source defect</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>DX-B-0001 to DX-B-0004; DX-B-0007 and DX-B-0008</t>
+        </is>
+      </c>
+      <c r="F5" s="11" t="inlineStr">
+        <is>
+          <t>DX-B-0001 to 0004 all carry B1.005 UPS; DX-B-0007 and DX-B-0008 both carry B1.019 FM STORAGE. The screens put them in B.022 SSP, B.022 SSP, B.005 UPS, B.008 VENT PLANT and in B.006 SERVICE AREA, B.008 VENT PLANT.</t>
+        </is>
+      </c>
+      <c r="G5" s="11" t="inlineStr">
+        <is>
+          <t>Reported the pattern rather than correcting it.</t>
+        </is>
+      </c>
+      <c r="H5" s="11" t="inlineStr">
+        <is>
+          <t>Four consecutive units sharing one room where the screens spread them across four rooms is the signature of a filled-down cell, not of four units in one plant room. Only DX-B-0003 matches - and it is the third of the four.</t>
+        </is>
+      </c>
+      <c r="I5" s="11" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" ht="58.05" customHeight="1">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>SSC-005</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C6" s="16" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="inlineStr">
+        <is>
+          <t>The SSC BMS screen pass</t>
+        </is>
+      </c>
+      <c r="F6" s="11" t="inlineStr">
+        <is>
+          <t>Seven SSC floor-plan screens were supplied: BF-part1, BF-part2, FF-part1, FF-part2, Second Floor, TF-part1, TF-part2.</t>
+        </is>
+      </c>
+      <c r="G6" s="11" t="inlineStr">
+        <is>
+          <t>87 SSC units were read off those screens in the AHU/VAV/FCU pass, and a further 19 non-AHU/VAV/FCU units (DX, CRAC, exhaust fans) in the equipment pass. Every reading carries the screen it came from and an ok/check confidence. Units on no supplied screen were left blank with a reason.</t>
+        </is>
+      </c>
+      <c r="H6" s="11" t="inlineStr">
+        <is>
+          <t>A leader that could not be followed, or a marker landing on a wall, is recorded as blank-with-a-reason rather than filled in. Over-inclusion is worse than omission: a wrong room validates clean.</t>
+        </is>
+      </c>
+      <c r="I6" s="11" t="n">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="7" ht="58.05" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>SSC-006</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="E7" s="11" t="inlineStr">
+        <is>
+          <t>Screen findings across the three buildings reviewed - QNL, HQ, SSC</t>
+        </is>
+      </c>
+      <c r="F7" s="11" t="inlineStr">
+        <is>
+          <t>The same serving-area leaders were traced on all three buildings for which screens exist. RDC has never had screens supplied.</t>
+        </is>
+      </c>
+      <c r="G7" s="11" t="inlineStr">
+        <is>
+          <t>QNL: 230 of 551 register rows read across 17 screens, 78 raised for review (19 outright disagreements, 59 wanting a second look), 321 left blank each with a recorded reason. HQ: 19 units read in the AHU/VAV/FCU pass plus 9 in the equipment pass, over 31 screens. SSC: 87 plus 19, over 7 screens.</t>
+        </is>
+      </c>
+      <c r="H7" s="11" t="inlineStr">
+        <is>
+          <t>One method, three buildings, so the findings are comparable. The largest single finding is on QNL: 27 second-floor units (11 VAV-2F-S12, 16 VAV-2F-S14) carry first-floor rooms in the register.</t>
+        </is>
+      </c>
+      <c r="I7" s="11" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -671,7 +934,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="8.21875" customWidth="1" min="1" max="1"/>
@@ -737,17 +1000,452 @@
     <row r="2" ht="58.05" customHeight="1">
       <c r="A2" s="10" t="inlineStr">
         <is>
-          <t>(no entries yet)</t>
-        </is>
-      </c>
-      <c r="B2" s="11" t="n"/>
-      <c r="C2" s="11" t="n"/>
-      <c r="D2" s="11" t="n"/>
-      <c r="E2" s="11" t="n"/>
-      <c r="F2" s="11" t="n"/>
-      <c r="G2" s="11" t="n"/>
-      <c r="H2" s="11" t="n"/>
-      <c r="I2" s="11" t="n"/>
+          <t>HQ-001</t>
+        </is>
+      </c>
+      <c r="B2" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C2" s="15" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="D2" s="11" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>52 equipment entities: 27 CEF car-park exhaust fans, 11 GEF general exhaust fans, 5 heat exchangers HEX01-HEX05, 4 chilled-water booster pumps CHW_CHWP01-04, 4 TEF toilet exhaust fans, CCU_B0005</t>
+        </is>
+      </c>
+      <c r="F2" s="11" t="inlineStr">
+        <is>
+          <t>Their rec:locatedIn object is the literal placeholder entity:&lt;Location&gt; - the template text was never replaced with a room.</t>
+        </is>
+      </c>
+      <c r="G2" s="11" t="inlineStr">
+        <is>
+          <t>Left the rows as delivered and flagged all 52. One is settled by the screens: CCU-B-0005 leads into VIP Parking B.115 on HQ/Basment Floor/BF-2, alongside CCU-B-0006/0007/0008 which the ontology already puts there.</t>
+        </is>
+      </c>
+      <c r="H2" s="11" t="inlineStr">
+        <is>
+          <t>entity:&lt;Location&gt; is not a room. It converts to a dangling reference in the TTL and the front end has nothing to place the unit against.</t>
+        </is>
+      </c>
+      <c r="I2" s="11" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" ht="58.05" customHeight="1">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>HQ-002</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="D3" s="11" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="E3" s="11" t="inlineStr">
+        <is>
+          <t>HEX, DX_CP, DX_ODSB0101, DX_ODSB0102, DX_ODSB0201, DX_ODSB0202</t>
+        </is>
+      </c>
+      <c r="F3" s="11" t="inlineStr">
+        <is>
+          <t>The rec:locatedIn row exists but its object cell is empty.</t>
+        </is>
+      </c>
+      <c r="G3" s="11" t="inlineStr">
+        <is>
+          <t>Left as delivered and flagged all six.</t>
+        </is>
+      </c>
+      <c r="H3" s="11" t="inlineStr">
+        <is>
+          <t>An empty object is a triple with two terms. It is a different defect from the placeholder above and needs a different fix, so it is logged apart.</t>
+        </is>
+      </c>
+      <c r="I3" s="11" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" ht="58.05" customHeight="1">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>HQ-003</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="E4" s="11" t="inlineStr">
+        <is>
+          <t>entity:HQ_ELEC_Gen2, entity:HQ_ELEC_Gen3</t>
+        </is>
+      </c>
+      <c r="F4" s="11" t="inlineStr">
+        <is>
+          <t>Both generators carry brick:hasPoint rows but no rec:locatedIn row at all.</t>
+        </is>
+      </c>
+      <c r="G4" s="11" t="inlineStr">
+        <is>
+          <t>Left as delivered and flagged both.</t>
+        </is>
+      </c>
+      <c r="H4" s="11" t="inlineStr">
+        <is>
+          <t>These are the only two top-level HQ entities carrying points with no location row. The other 95 hits are VFD and electrical-meter sub-entities that hang off a parent and are located with it, which is correct.</t>
+        </is>
+      </c>
+      <c r="I4" s="11" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" ht="58.05" customHeight="1">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>HQ-004</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>entity:HQ_FCU0097, entity:HQ_FCU00133</t>
+        </is>
+      </c>
+      <c r="F5" s="11" t="inlineStr">
+        <is>
+          <t>Both carry rec:locatedIn entity:&lt;FCU-Ref_Location&gt; - a second, differently spelled placeholder.</t>
+        </is>
+      </c>
+      <c r="G5" s="11" t="inlineStr">
+        <is>
+          <t>Reported. Outside the scope of the equipment pass, which excludes AHU, VAV and FCU, so these two are not in HQ_SSC_equipment_rooms.xlsx.</t>
+        </is>
+      </c>
+      <c r="H5" s="11" t="inlineStr">
+        <is>
+          <t>Logged so a search for entity:&lt;Location&gt; is not mistaken for a complete list of unlocated HQ equipment. FCU0097 does have a screen reading from the earlier pass: B.512 IDF ROOM on HQ/Basment Floor/BF-2.</t>
+        </is>
+      </c>
+      <c r="I5" s="11" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" ht="58.05" customHeight="1">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>HQ-005</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C6" s="16" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="inlineStr">
+        <is>
+          <t>18 car-park fans: JF-B-0001 to JF-B-0010, IF-B-0001 to IF-B-0008</t>
+        </is>
+      </c>
+      <c r="F6" s="11" t="inlineStr">
+        <is>
+          <t>All 18 are drawn and tagged on the HQ car-park screens. The ontology has no entity for any of them - not unlocated, absent.</t>
+        </is>
+      </c>
+      <c r="G6" s="11" t="inlineStr">
+        <is>
+          <t>Listed all 18 in HQ_SSC_equipment_rooms.xlsx with the screen they appear on.</t>
+        </is>
+      </c>
+      <c r="H6" s="11" t="inlineStr">
+        <is>
+          <t>Jet fans and induction fans are the car park ventilation. They are monitored on the BMS, so the historian has their points, and an ontology that omits them leaves those points unreachable.</t>
+        </is>
+      </c>
+      <c r="I6" s="11" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" ht="58.05" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>HQ-006</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="E7" s="11" t="inlineStr">
+        <is>
+          <t>The 27 CEF car-park exhaust fans of HQ-001</t>
+        </is>
+      </c>
+      <c r="F7" s="11" t="inlineStr">
+        <is>
+          <t>Each CEF B-number maps to a car park deck screen, so the screens do say which deck the fan is on.</t>
+        </is>
+      </c>
+      <c r="G7" s="11" t="inlineStr">
+        <is>
+          <t>Recorded the deck against each fan; did not invent a room.</t>
+        </is>
+      </c>
+      <c r="H7" s="11" t="inlineStr">
+        <is>
+          <t>The car park decks carry no room names at all - bay numbers, Exit and Public Vehicle Out, nothing else. The deck is real information but it is not a room, so the 52 placeholders cannot be closed from these screens.</t>
+        </is>
+      </c>
+      <c r="I7" s="11" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" ht="58.05" customHeight="1">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>HQ-007</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="E8" s="11" t="inlineStr">
+        <is>
+          <t>DX-B-0011, DX-B-0016, DX-B-0003, CCU-B-0003A</t>
+        </is>
+      </c>
+      <c r="F8" s="11" t="inlineStr">
+        <is>
+          <t>The ontology room and the room the serving-area leader points at differ. DX-B-0011: B1.009 MV SWITCH ROOM against UPS Room B.26. DX-B-0016: B1.018 PA ROOM against AHU-3 B.022. CCU-B-0003A: B1.106 VVIP PARKING 6 CAR SPOTS against the Chauffer Room B.117 band. DX-B-0003 lands in an unlabelled cell east of Transformer Substation B.010.</t>
+        </is>
+      </c>
+      <c r="G8" s="11" t="inlineStr">
+        <is>
+          <t>Did not overwrite. Wrote the screen room beside the ontology room and flagged all four.</t>
+        </is>
+      </c>
+      <c r="H8" s="11" t="inlineStr">
+        <is>
+          <t>Two as-built sources disagree and neither is provably right. DX-B-0003 is flagged for a different reason: the screen has no name for the cell the dot is in, so it cannot confirm the ontology room either way.</t>
+        </is>
+      </c>
+      <c r="I8" s="11" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" ht="58.05" customHeight="1">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>HQ-008</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>CCU-B-0005, CCU-B-0006, CCU-B-0007, CCU-B-0008</t>
+        </is>
+      </c>
+      <c r="F9" s="11" t="inlineStr">
+        <is>
+          <t>An earlier draft of this pass flagged eight HQ CRACs on the grounds that a CRAC located in a parking bay looked like a fill error.</t>
+        </is>
+      </c>
+      <c r="G9" s="11" t="inlineStr">
+        <is>
+          <t>Flag withdrawn. The screens show all four leaders running into VIP Parking B.115, which is what the ontology says for three of them.</t>
+        </is>
+      </c>
+      <c r="H9" s="11" t="inlineStr">
+        <is>
+          <t>That flag was an inference about what is plausible, not a reading off a screen. Once HQ.zip arrived the screens settled it, and a plausibility hunch that survives into the sheet is indistinguishable from evidence.</t>
+        </is>
+      </c>
+      <c r="I9" s="11" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" ht="58.05" customHeight="1">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>HQ-009</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C10" s="16" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="E10" s="11" t="inlineStr">
+        <is>
+          <t>The HQ BMS screen pass</t>
+        </is>
+      </c>
+      <c r="F10" s="11" t="inlineStr">
+        <is>
+          <t>31 HQ floor-plan screens were supplied, across the basement, ground, 1F-11F, the roof and the car park decks.</t>
+        </is>
+      </c>
+      <c r="G10" s="11" t="inlineStr">
+        <is>
+          <t>19 HQ units were read off them in the AHU/VAV/FCU pass and 9 in the equipment pass. HQ screens label rooms outside the room polygon, joined by their own dashed pointer, so each reading resolves the polygon first and then finds the label pointing into it.</t>
+        </is>
+      </c>
+      <c r="H10" s="11" t="inlineStr">
+        <is>
+          <t>Reading the nearest text instead of the polygon is what put VAV0026 in the lobby. Every HQ reading carries its screen and an ok/check confidence, and units the screens do not settle are left blank with a reason.</t>
+        </is>
+      </c>
+      <c r="I10" s="11" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" ht="58.05" customHeight="1">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>HQ-010</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C11" s="15" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>Screen findings across the three buildings reviewed - QNL, HQ, SSC</t>
+        </is>
+      </c>
+      <c r="F11" s="11" t="inlineStr">
+        <is>
+          <t>The same serving-area leaders were traced on all three buildings for which screens exist. RDC has never had screens supplied.</t>
+        </is>
+      </c>
+      <c r="G11" s="11" t="inlineStr">
+        <is>
+          <t>QNL: 230 of 551 register rows read across 17 screens, 78 raised for review (19 outright disagreements, 59 wanting a second look), 321 left blank each with a recorded reason. HQ: 19 plus 9 units over 31 screens. SSC: 87 plus 19 units over 7 screens.</t>
+        </is>
+      </c>
+      <c r="H11" s="11" t="inlineStr">
+        <is>
+          <t>One method, three buildings, so the findings are comparable. HQ is the only one of the three whose ontology leaves equipment unlocated - 52 placeholders, 6 empty objects, 2 with no location row and 18 units with no entity at all. SSC has none of that but has the DX fill-down; QNL's largest finding is 27 second-floor units carrying first-floor rooms.</t>
+        </is>
+      </c>
+      <c r="I11" s="11" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/projects/Assumption_Log.xlsx
+++ b/projects/Assumption_Log.xlsx
@@ -760,7 +760,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="8.21875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1884,6 +1884,382 @@
       </c>
       <c r="I24" s="11" t="n">
         <v>3</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>QNL-031</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C25" s="13" t="inlineStr">
+        <is>
+          <t>Structure</t>
+        </is>
+      </c>
+      <c r="D25" s="11" t="inlineStr">
+        <is>
+          <t>Metering</t>
+        </is>
+      </c>
+      <c r="E25" s="11" t="inlineStr">
+        <is>
+          <t>virtual metering layer, 1,460 meters</t>
+        </is>
+      </c>
+      <c r="F25" s="11" t="inlineStr">
+        <is>
+          <t>No metering layer existed. A hand-built workbook (VirtualMeters_QNL_manual_v1.xlsm) proposed one from a 9-class x 3-tier matrix.</t>
+        </is>
+      </c>
+      <c r="G25" s="11" t="inlineStr">
+        <is>
+          <t>Regenerated the layer from that tier matrix against the live ontology rather than importing the workbook, and archived the workbook under projects/QNL/sources/.</t>
+        </is>
+      </c>
+      <c r="H25" s="11" t="inlineStr">
+        <is>
+          <t>None of the workbook's 353 room identifiers matched the live sheet - it was built before align_naming ran. Regenerating makes the identifiers agree by construction instead of by remap.</t>
+        </is>
+      </c>
+      <c r="I25" s="11" t="inlineStr">
+        <is>
+          <t>8,760</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>QNL-032</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C26" s="13" t="inlineStr">
+        <is>
+          <t>Identifier</t>
+        </is>
+      </c>
+      <c r="D26" s="11" t="inlineStr">
+        <is>
+          <t>Metering</t>
+        </is>
+      </c>
+      <c r="E26" s="11" t="inlineStr">
+        <is>
+          <t>353 room-tier meters</t>
+        </is>
+      </c>
+      <c r="F26" s="11" t="inlineStr">
+        <is>
+          <t>Workbook rooms read QNL_B_001A_BREAK-OUT-AREA; the ontology reads QNL_B-001A_Break-Out-Area.</t>
+        </is>
+      </c>
+      <c r="G26" s="11" t="inlineStr">
+        <is>
+          <t>Used the ontology form. Zero identifiers changed in the ontology.</t>
+        </is>
+      </c>
+      <c r="H26" s="11" t="inlineStr">
+        <is>
+          <t>A fuzzy key (case, separators, leading zeros) matched 353 of 353, so the two name the same rooms; the ontology form is the one the rest of the sheet and the crosswalk already use.</t>
+        </is>
+      </c>
+      <c r="I26" s="11" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="11" t="inlineStr">
+        <is>
+          <t>QNL-033</t>
+        </is>
+      </c>
+      <c r="B27" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C27" s="13" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="D27" s="11" t="inlineStr">
+        <is>
+          <t>Metering</t>
+        </is>
+      </c>
+      <c r="E27" s="11" t="inlineStr">
+        <is>
+          <t>entity:QNL_L1-145_ILL-Director</t>
+        </is>
+      </c>
+      <c r="F27" s="11" t="inlineStr">
+        <is>
+          <t>The workbook metered 353 rooms; the ontology has 354.</t>
+        </is>
+      </c>
+      <c r="G27" s="11" t="inlineStr">
+        <is>
+          <t>Gave it the same four room-tier meters as its siblings.</t>
+        </is>
+      </c>
+      <c r="H27" s="11" t="inlineStr">
+        <is>
+          <t>The room was added by the room-retarget pass (QNL_room_retarget_changes.csv, "new room") after the workbook was built. Note the open question from that pass: if 144 and 145 are one room, 144 should be retired and its meters with it.</t>
+        </is>
+      </c>
+      <c r="I27" s="11" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="11" t="inlineStr">
+        <is>
+          <t>QNL-034</t>
+        </is>
+      </c>
+      <c r="B28" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C28" s="13" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+      <c r="D28" s="11" t="inlineStr">
+        <is>
+          <t>Metering</t>
+        </is>
+      </c>
+      <c r="E28" s="11" t="inlineStr">
+        <is>
+          <t>732 thermal meter points</t>
+        </is>
+      </c>
+      <c r="F28" s="11" t="inlineStr">
+        <is>
+          <t>The workbook gave CHW and HW thermal points unit:KiloW and unit:KiloW-HR, the same tokens as the electrical meters. Dar Cairo splits: brick:Thermal_Power_Meter uses para:KiloWt/para:KiloWt-HR, its own para:CHW_Meter is 70 rows kW against 2 kWt.</t>
+        </is>
+      </c>
+      <c r="G28" s="11" t="inlineStr">
+        <is>
+          <t>Used para:KiloWt and para:KiloWt-HR, and declared both as qudt:Unit rows.</t>
+        </is>
+      </c>
+      <c r="H28" s="11" t="inlineStr">
+        <is>
+          <t>Client decision. Thermal kW written as unit:KiloW is indistinguishable from electrical kW, so any building rollup that sums demand double-counts. Diverges from the 7 pre-existing QNL thermal rows on unit:KiloW - those are left alone and listed for a later pass.</t>
+        </is>
+      </c>
+      <c r="I28" s="11" t="inlineStr">
+        <is>
+          <t>732</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t>QNL-035</t>
+        </is>
+      </c>
+      <c r="B29" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C29" s="13" t="inlineStr">
+        <is>
+          <t>Structure</t>
+        </is>
+      </c>
+      <c r="D29" s="11" t="inlineStr">
+        <is>
+          <t>Metering</t>
+        </is>
+      </c>
+      <c r="E29" s="11" t="inlineStr">
+        <is>
+          <t>2,920 meter points</t>
+        </is>
+      </c>
+      <c r="F29" s="11" t="inlineStr">
+        <is>
+          <t>Dar Cairo populates every virtual-meter point with a ref:TimeseriesReference. The QNL historian (QNL_Historian_IO_list_CP2.xlsx) carries no calculated tags at all - zero *_CALC, zero ContributionFraction.</t>
+        </is>
+      </c>
+      <c r="G29" s="11" t="inlineStr">
+        <is>
+          <t>Wrote the points with no reference row, and listed all 2,920 in QNL_virtual_meter_timeseries_pending.csv with the Dar Cairo tsid proposed and entityId blank.</t>
+        </is>
+      </c>
+      <c r="H29" s="11" t="inlineStr">
+        <is>
+          <t>The workbook wrote 2,912 reference rows with both keys blank. A half-filled blank node looks finished and reads as a working telemetry link; an absent one is visible as W-PT-1 and tracked in a file.</t>
+        </is>
+      </c>
+      <c r="I29" s="11" t="inlineStr">
+        <is>
+          <t>2,920 (W-PT-1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>QNL-036</t>
+        </is>
+      </c>
+      <c r="B30" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C30" s="13" t="inlineStr">
+        <is>
+          <t>Structure</t>
+        </is>
+      </c>
+      <c r="D30" s="11" t="inlineStr">
+        <is>
+          <t>Metering</t>
+        </is>
+      </c>
+      <c r="E30" s="11" t="inlineStr">
+        <is>
+          <t>297 AHU-fed terminal units</t>
+        </is>
+      </c>
+      <c r="F30" s="11" t="inlineStr">
+        <is>
+          <t>Client asked for para:contributionFraction on every unit fed by an AHU, skipping units in shafts or risers.</t>
+        </is>
+      </c>
+      <c r="G30" s="11" t="inlineStr">
+        <is>
+          <t>Added it to all 297 (246 VAV + 51 CAV) with tsid ContributionFraction and the entityId each unit's existing points already carry.</t>
+        </is>
+      </c>
+      <c r="H30" s="11" t="inlineStr">
+        <is>
+          <t>The shaft rule matched nothing: QNL's shaft-dwelling assets are 62 FCUs and 2 exhaust fans, and no AHU feeds any of them. The rule is implemented for the next building. entity:QNL_CAV-B-S13-050 carries no points, so its entityId was derived - the derivation matches all 296 units that do have one.</t>
+        </is>
+      </c>
+      <c r="I30" s="11" t="inlineStr">
+        <is>
+          <t>594</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>QNL-037</t>
+        </is>
+      </c>
+      <c r="B31" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C31" s="13" t="inlineStr">
+        <is>
+          <t>Class</t>
+        </is>
+      </c>
+      <c r="D31" s="11" t="inlineStr">
+        <is>
+          <t>Metering</t>
+        </is>
+      </c>
+      <c r="E31" s="11" t="inlineStr">
+        <is>
+          <t>entity:QNL_Utility-Virtual-Meter vs entity:QNL_Total-Energy</t>
+        </is>
+      </c>
+      <c r="F31" s="11" t="inlineStr">
+        <is>
+          <t>QNL already carries entity:QNL_Total-Energy typed para:Utility_Meter, with a real historian tag QNL_TotalEnergy.Energy. The tier matrix asks for a building-tier Utility_Meter as well.</t>
+        </is>
+      </c>
+      <c r="G31" s="11" t="inlineStr">
+        <is>
+          <t>Wrote both, and flagged the overlap rather than resolving it.</t>
+        </is>
+      </c>
+      <c r="H31" s="11" t="inlineStr">
+        <is>
+          <t>OPEN. Both claim the building utility supply and only Total-Energy has data behind it. Either retrofit Total-Energy into the metering layer and drop the virtual one, or say what the virtual one measures that Total-Energy does not.</t>
+        </is>
+      </c>
+      <c r="I31" s="11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>QNL-038</t>
+        </is>
+      </c>
+      <c r="B32" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C32" s="13" t="inlineStr">
+        <is>
+          <t>Source defect</t>
+        </is>
+      </c>
+      <c r="D32" s="11" t="inlineStr">
+        <is>
+          <t>Metering</t>
+        </is>
+      </c>
+      <c r="E32" s="11" t="inlineStr">
+        <is>
+          <t>brick:Electrical_Meter family</t>
+        </is>
+      </c>
+      <c r="F32" s="11" t="inlineStr">
+        <is>
+          <t>14 pre-existing physical meters (MFM, VCB) share brick:Electrical_Meter with the 360 new virtual ones, so check_consistency compares them as one family.</t>
+        </is>
+      </c>
+      <c r="G32" s="11" t="inlineStr">
+        <is>
+          <t>Left the class as-is; 25 E-CON errors are accepted and named here.</t>
+        </is>
+      </c>
+      <c r="H32" s="11" t="inlineStr">
+        <is>
+          <t>Dar Cairo does the same - brick:Electrical_Meter covers both its physical and virtual meters. Splitting the virtual ones under a para: subclass would depart from the primary reference to quiet a checker.</t>
+        </is>
+      </c>
+      <c r="I32" s="11" t="inlineStr">
+        <is>
+          <t>25 (E-CON-1/2)</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/projects/Assumption_Log.xlsx
+++ b/projects/Assumption_Log.xlsx
@@ -760,7 +760,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="8.21875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -2201,17 +2201,17 @@
       </c>
       <c r="G31" s="11" t="inlineStr">
         <is>
-          <t>Wrote both, and flagged the overlap rather than resolving it.</t>
+          <t>Suppressed the virtual one. A virtual meter only fills a gap where no physical meter exists, and Total-Energy is the physical utility meter.</t>
         </is>
       </c>
       <c r="H31" s="11" t="inlineStr">
         <is>
-          <t>OPEN. Both claim the building utility supply and only Total-Energy has data behind it. Either retrofit Total-Energy into the metering layer and drop the virtual one, or say what the virtual one measures that Total-Energy does not.</t>
+          <t>Client rule, confirmed 2026-09-03: virtual meters are created only for actual meters that do not exist. The generator now carries an ALREADY_METERED list, each entry naming the physical meter that justifies the suppression.</t>
         </is>
       </c>
       <c r="I31" s="11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0 (6 not written)</t>
         </is>
       </c>
     </row>
@@ -2259,6 +2259,100 @@
       <c r="I32" s="11" t="inlineStr">
         <is>
           <t>25 (E-CON-1/2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="11" t="inlineStr">
+        <is>
+          <t>QNL-039</t>
+        </is>
+      </c>
+      <c r="B33" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C33" s="13" t="inlineStr">
+        <is>
+          <t>Source defect</t>
+        </is>
+      </c>
+      <c r="D33" s="11" t="inlineStr">
+        <is>
+          <t>Metering</t>
+        </is>
+      </c>
+      <c r="E33" s="11" t="inlineStr">
+        <is>
+          <t>all 16 pre-existing physical meters</t>
+        </is>
+      </c>
+      <c r="F33" s="11" t="inlineStr">
+        <is>
+          <t>None carries a brick:meters row. Each is brick:isPartOf entity:Electrical_System with points, and nothing says what it measures.</t>
+        </is>
+      </c>
+      <c r="G33" s="11" t="inlineStr">
+        <is>
+          <t>Left them as they are; recorded the gap and hand-listed the one suppression it blocked.</t>
+        </is>
+      </c>
+      <c r="H33" s="11" t="inlineStr">
+        <is>
+          <t>The "virtual only where physical does not exist" rule cannot be evaluated from the graph while this holds - it needs a human to say what each meter covers. Adding the brick:meters rows is the durable fix and is proposed in the handover.</t>
+        </is>
+      </c>
+      <c r="I33" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t>QNL-040</t>
+        </is>
+      </c>
+      <c r="B34" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C34" s="13" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="D34" s="11" t="inlineStr">
+        <is>
+          <t>Metering</t>
+        </is>
+      </c>
+      <c r="E34" s="11" t="inlineStr">
+        <is>
+          <t>entity:QNL_CHWS-MAIN-LOOP_Energy-Meter vs the building-tier para:CHW_Meter</t>
+        </is>
+      </c>
+      <c r="F34" s="11" t="inlineStr">
+        <is>
+          <t>QNL carries a brick:Building_Chilled_Water_Meter on the main CHW loop with 7 live points, among them CHW-Consumption-KW and CHW-CHW-Energy-PV.</t>
+        </is>
+      </c>
+      <c r="G34" s="11" t="inlineStr">
+        <is>
+          <t>Kept entity:QNL_CHW-Power-Thermal-Virtual-Meter for now and raised the overlap.</t>
+        </is>
+      </c>
+      <c r="H34" s="11" t="inlineStr">
+        <is>
+          <t>OPEN. By the same rule that removed the Utility virtual meter, this pair looks like a duplicate - the loop meter measures the building's chilled water. Different classes, so no checker will catch it. Needs confirmation that the loop meter covers the whole building.</t>
+        </is>
+      </c>
+      <c r="I34" s="11" t="inlineStr">
+        <is>
+          <t>6</t>
         </is>
       </c>
     </row>

--- a/projects/Assumption_Log.xlsx
+++ b/projects/Assumption_Log.xlsx
@@ -760,7 +760,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="8.21875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -2353,6 +2353,100 @@
       <c r="I34" s="11" t="inlineStr">
         <is>
           <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="11" t="inlineStr">
+        <is>
+          <t>QNL-041</t>
+        </is>
+      </c>
+      <c r="B35" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C35" s="13" t="inlineStr">
+        <is>
+          <t>Source defect</t>
+        </is>
+      </c>
+      <c r="D35" s="11" t="inlineStr">
+        <is>
+          <t>Metadata</t>
+        </is>
+      </c>
+      <c r="E35" s="11" t="inlineStr">
+        <is>
+          <t>VAV 1F-S15-006 to 009 and B-S15-001 to 004</t>
+        </is>
+      </c>
+      <c r="F35" s="11" t="inlineStr">
+        <is>
+          <t>Two MEP drawings schedule the same boxes and disagree on air flow. 1F: 290 l/s on the S11/S15 drawing against 220 l/s on the second 1F drawing. Basement: 261 l/s on the heating-capacity drawing against 251 l/s on the model-and-make drawing. QNL_Full_Metadata.xlsx recorded both and its Open Items sheet marks each "Unresolved".</t>
+        </is>
+      </c>
+      <c r="G35" s="11" t="inlineStr">
+        <is>
+          <t>Kept 290 l/s and 251 l/s; dropped the other eight rows.</t>
+        </is>
+      </c>
+      <c r="H35" s="11" t="inlineStr">
+        <is>
+          <t>Client decision 2026-09-03, on one rule: where two drawings of the same schedule disagree, keep the one that names the box model, since the flow has to match the box selected. 290 comes with model NBOQOB250 and makes boxes 005-009 one consistent run; 251 comes with model NBOQE03. Title blocks are cropped on every drawing image, so no revision date could settle it instead. Reversible - both values remain in QNL_Full_Metadata.xlsx.</t>
+        </is>
+      </c>
+      <c r="I35" s="11" t="inlineStr">
+        <is>
+          <t>8 dropped</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t>QNL-042</t>
+        </is>
+      </c>
+      <c r="B36" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C36" s="13" t="inlineStr">
+        <is>
+          <t>Source defect</t>
+        </is>
+      </c>
+      <c r="D36" s="11" t="inlineStr">
+        <is>
+          <t>References</t>
+        </is>
+      </c>
+      <c r="E36" s="11" t="inlineStr">
+        <is>
+          <t>all 564 ref:IFCReference rows</t>
+        </is>
+      </c>
+      <c r="F36" s="11" t="inlineStr">
+        <is>
+          <t>Every row declares para:IFC_ID with a blank value; ref:ifcName carries the entity identifier. No reference model carries a real IFC GUID either - across Dar Cairo, SSC, HQ and QNL, none of 2,133 values matches the 22-character IfcGloballyUniqueId shape.</t>
+        </is>
+      </c>
+      <c r="G36" s="11" t="inlineStr">
+        <is>
+          <t>Left as-is and recorded. Not changed in this pass.</t>
+        </is>
+      </c>
+      <c r="H36" s="11" t="inlineStr">
+        <is>
+          <t>These 564 blanks are 564 of the sheet's 574 E-PAIR-1 errors. Dar Cairo writes ref:ifcName only and no IFC_ID at all; SSC writes the same string into both columns; HQ makes IFC_ID primary. CLAUDE.md describes para:IFC_ID as the BIM GUID, which no delivered model does. Needs a PARA-team decision on which column QNL should carry and whether real GUIDs are obtainable.</t>
+        </is>
+      </c>
+      <c r="I36" s="11" t="inlineStr">
+        <is>
+          <t>0 (564 E-PAIR-1)</t>
         </is>
       </c>
     </row>

--- a/projects/Assumption_Log.xlsx
+++ b/projects/Assumption_Log.xlsx
@@ -2436,17 +2436,17 @@
       </c>
       <c r="G36" s="11" t="inlineStr">
         <is>
-          <t>Left as-is and recorded. Not changed in this pass.</t>
+          <t>Filled all 564 para:IFC_ID cells with the entity identifier, the same string ref:ifcName already carried. QF SSC's shape.</t>
         </is>
       </c>
       <c r="H36" s="11" t="inlineStr">
         <is>
-          <t>These 564 blanks are 564 of the sheet's 574 E-PAIR-1 errors. Dar Cairo writes ref:ifcName only and no IFC_ID at all; SSC writes the same string into both columns; HQ makes IFC_ID primary. CLAUDE.md describes para:IFC_ID as the BIM GUID, which no delivered model does. Needs a PARA-team decision on which column QNL should carry and whether real GUIDs are obtainable.</t>
+          <t>Client decision 2026-09-03. SSC writes the identifier into both columns on all 165 of its IFC rows; QNL was already built to that shape but left IFC_ID empty. Note that no delivered model carries a real IFC GUID - across Dar Cairo, SSC, HQ and QNL none of 2,133 values matches the 22-character IfcGloballyUniqueId shape - so para:IFC_ID holds the asset tag, not the BIM GUID that CLAUDE.md describes. If real GUIDs are exported later they overwrite these in one pass.</t>
         </is>
       </c>
       <c r="I36" s="11" t="inlineStr">
         <is>
-          <t>0 (564 E-PAIR-1)</t>
+          <t>564 (574 errors -&gt; 10)</t>
         </is>
       </c>
     </row>

--- a/projects/Assumption_Log.xlsx
+++ b/projects/Assumption_Log.xlsx
@@ -760,7 +760,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I36"/>
+  <dimension ref="A1:I37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="8.21875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -2447,6 +2447,53 @@
       <c r="I36" s="11" t="inlineStr">
         <is>
           <t>564 (574 errors -&gt; 10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="11" t="inlineStr">
+        <is>
+          <t>QNL-043</t>
+        </is>
+      </c>
+      <c r="B37" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C37" s="13" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="D37" s="11" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="E37" s="11" t="inlineStr">
+        <is>
+          <t>26 standalone assets with no room</t>
+        </is>
+      </c>
+      <c r="F37" s="11" t="inlineStr">
+        <is>
+          <t>The asset register gives no room for 6 CRACs, 2 DX units, 1 CAV, 1 VAV, 1 booster pump and 15 electrical meters. Earlier practice was to write no rec:locatedIn at all rather than invent one.</t>
+        </is>
+      </c>
+      <c r="G37" s="11" t="inlineStr">
+        <is>
+          <t>Wrote rec:locatedIn entity:QNL (rec:Building) on all 26. Every one already carried brick:isPartOf its system, so no system row was needed.</t>
+        </is>
+      </c>
+      <c r="H37" s="11" t="inlineStr">
+        <is>
+          <t>House rule changed 2026-09-03: an asset with no room is still certainly in the building and certainly on its system, so assert both rather than nothing. rec:feeds is still not written - the served space is the part nobody knows. Dar Cairo has precedent, locating 36 entities at a rec:Building. Excludes the 174 parts that also lack a location (137 CHW valves, 22 fans, 10 HEX valves, 2 breakers, 2 pumps): a part inherits its parent's location and Dar Cairo locates only 19 of its 801 parts separately. Clears 26 W-GR-2; the 10 E-FEED-1 stand.</t>
+        </is>
+      </c>
+      <c r="I37" s="11" t="inlineStr">
+        <is>
+          <t>26</t>
         </is>
       </c>
     </row>

--- a/projects/Assumption_Log.xlsx
+++ b/projects/Assumption_Log.xlsx
@@ -2488,7 +2488,7 @@
       </c>
       <c r="H37" s="11" t="inlineStr">
         <is>
-          <t>House rule changed 2026-09-03: an asset with no room is still certainly in the building and certainly on its system, so assert both rather than nothing. rec:feeds is still not written - the served space is the part nobody knows. Dar Cairo has precedent, locating 36 entities at a rec:Building. Excludes the 174 parts that also lack a location (137 CHW valves, 22 fans, 10 HEX valves, 2 breakers, 2 pumps): a part inherits its parent's location and Dar Cairo locates only 19 of its 801 parts separately. Clears 26 W-GR-2; the 10 E-FEED-1 stand.</t>
+          <t>PROJECT ASSUMPTION FOR QNL ONLY - not a house rule, and deliberately not written into the skill. An asset with no room is still certainly in the building and certainly on its system, so both are asserted rather than nothing. rec:feeds is still not written - the served space is the part nobody knows. Dar Cairo has precedent, locating 36 entities at a rec:Building. Excludes the 174 parts that also lack a location (137 CHW valves, 22 fans, 10 HEX valves, 2 breakers, 2 pumps): a part inherits its parent's location and Dar Cairo locates only 19 of its 801 parts separately. Clears 26 W-GR-2; the 10 E-FEED-1 stand.</t>
         </is>
       </c>
       <c r="I37" s="11" t="inlineStr">

--- a/projects/Assumption_Log.xlsx
+++ b/projects/Assumption_Log.xlsx
@@ -49,7 +49,7 @@
       <color rgb="FF808080"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="16">
     <fill>
       <patternFill/>
     </fill>
@@ -121,6 +121,11 @@
         <fgColor rgb="00DDEBF7"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FBE5D6"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -163,7 +168,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -215,6 +220,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -582,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="8.21875" customWidth="1" min="1" max="1"/>
@@ -648,17 +656,272 @@
     <row r="2" ht="58.05" customHeight="1">
       <c r="A2" s="10" t="inlineStr">
         <is>
-          <t>(no entries yet)</t>
-        </is>
-      </c>
-      <c r="B2" s="11" t="n"/>
-      <c r="C2" s="11" t="n"/>
-      <c r="D2" s="11" t="n"/>
-      <c r="E2" s="11" t="n"/>
-      <c r="F2" s="11" t="n"/>
-      <c r="G2" s="11" t="n"/>
-      <c r="H2" s="11" t="n"/>
-      <c r="I2" s="11" t="n"/>
+          <t>SSC-001</t>
+        </is>
+      </c>
+      <c r="B2" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C2" s="15" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="D2" s="11" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>7 exhaust fans: GEFB0001, KEF0103, KEF0303, TEF0101, TEF0102, TEF0301, TEF0302</t>
+        </is>
+      </c>
+      <c r="F2" s="11" t="inlineStr">
+        <is>
+          <t>All seven carry rec:locatedIn entity:Level7_Office0367, and that room entity carries no rdfs:label_en anywhere in the sheet - so it has no readable name.</t>
+        </is>
+      </c>
+      <c r="G2" s="11" t="inlineStr">
+        <is>
+          <t>Left the triples as delivered and flagged all seven for the client. Two of them are settled by the screens: KEF0103 is drawn in 01.005 KITCHEN and TEF0101 in 01.028 CORRIDOR (SSC/FF-part2).</t>
+        </is>
+      </c>
+      <c r="H2" s="11" t="inlineStr">
+        <is>
+          <t>A room with no label cannot be shown in the front end and cannot be checked against a drawing. Seven fans on seven different levels sharing one seventh-floor office reads as a fill-down, not as seven readings. Unlike HQ this is a naming gap, not a missing location - the room entity exists and is referenced, it simply has no label.</t>
+        </is>
+      </c>
+      <c r="I2" s="11" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" ht="58.05" customHeight="1">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>SSC-002</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="D3" s="11" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="E3" s="11" t="inlineStr">
+        <is>
+          <t>Every other located SSC entity</t>
+        </is>
+      </c>
+      <c r="F3" s="11" t="inlineStr">
+        <is>
+          <t>All 166 rec:locatedIn rows in SSC_Ontology_Ver0.6 name a real room entity - no entity:&lt;Location&gt; placeholders, no blank objects.</t>
+        </is>
+      </c>
+      <c r="G3" s="11" t="inlineStr">
+        <is>
+          <t>Recorded the check; nothing to raise.</t>
+        </is>
+      </c>
+      <c r="H3" s="11" t="inlineStr">
+        <is>
+          <t>Stated so the SSC sheet is not read as silent on the question that HQ fails. SSC has no equipment carrying points and no rec:locatedIn at all.</t>
+        </is>
+      </c>
+      <c r="I3" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" ht="58.05" customHeight="1">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>SSC-003</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="E4" s="11" t="inlineStr">
+        <is>
+          <t>DX-B-0001, DX-B-0002, DX-B-0004, DX-B-0006, DX-B-0007, DX-B-0008, DX-B-0009, DX-B-0010, CCU-B-0004, CCU-B-0007</t>
+        </is>
+      </c>
+      <c r="F4" s="11" t="inlineStr">
+        <is>
+          <t>The ontology room and the room the BMS serving-area leader points at differ on all ten. DX-B-0009 is B1.020 FM STORAGE in the ontology and B.002 HV ROOM on the screen; CCU-B-0007 is B1.017 MDF-2 against B.026 MDF/SER.1.</t>
+        </is>
+      </c>
+      <c r="G4" s="11" t="inlineStr">
+        <is>
+          <t>Did not overwrite the ontology. Wrote the screen room beside it and flagged all ten in HQ_SSC_equipment_rooms.xlsx for the client to settle.</t>
+        </is>
+      </c>
+      <c r="H4" s="11" t="inlineStr">
+        <is>
+          <t>Two as-built sources disagree. The screen is the live BMS graphic and the ontology room came from the register, so neither can be assumed correct - a guess written into the room column is indistinguishable from a reading.</t>
+        </is>
+      </c>
+      <c r="I4" s="11" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" ht="58.05" customHeight="1">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>SSC-004</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C5" s="19" t="inlineStr">
+        <is>
+          <t>Source defect</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>DX-B-0001 to DX-B-0004; DX-B-0007 and DX-B-0008</t>
+        </is>
+      </c>
+      <c r="F5" s="11" t="inlineStr">
+        <is>
+          <t>DX-B-0001 to 0004 all carry B1.005 UPS; DX-B-0007 and DX-B-0008 both carry B1.019 FM STORAGE. The screens put them in B.022 SSP, B.022 SSP, B.005 UPS, B.008 VENT PLANT and in B.006 SERVICE AREA, B.008 VENT PLANT.</t>
+        </is>
+      </c>
+      <c r="G5" s="11" t="inlineStr">
+        <is>
+          <t>Reported the pattern rather than correcting it.</t>
+        </is>
+      </c>
+      <c r="H5" s="11" t="inlineStr">
+        <is>
+          <t>Four consecutive units sharing one room where the screens spread them across four rooms is the signature of a filled-down cell, not of four units in one plant room. Only DX-B-0003 matches - and it is the third of the four.</t>
+        </is>
+      </c>
+      <c r="I5" s="11" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" ht="58.05" customHeight="1">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>SSC-005</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C6" s="16" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="inlineStr">
+        <is>
+          <t>The SSC BMS screen pass</t>
+        </is>
+      </c>
+      <c r="F6" s="11" t="inlineStr">
+        <is>
+          <t>Seven SSC floor-plan screens were supplied: BF-part1, BF-part2, FF-part1, FF-part2, Second Floor, TF-part1, TF-part2.</t>
+        </is>
+      </c>
+      <c r="G6" s="11" t="inlineStr">
+        <is>
+          <t>87 SSC units were read off those screens in the AHU/VAV/FCU pass, and a further 19 non-AHU/VAV/FCU units (DX, CRAC, exhaust fans) in the equipment pass. Every reading carries the screen it came from and an ok/check confidence. Units on no supplied screen were left blank with a reason.</t>
+        </is>
+      </c>
+      <c r="H6" s="11" t="inlineStr">
+        <is>
+          <t>A leader that could not be followed, or a marker landing on a wall, is recorded as blank-with-a-reason rather than filled in. Over-inclusion is worse than omission: a wrong room validates clean.</t>
+        </is>
+      </c>
+      <c r="I6" s="11" t="n">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="7" ht="58.05" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>SSC-006</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="E7" s="11" t="inlineStr">
+        <is>
+          <t>Screen findings across the three buildings reviewed - QNL, HQ, SSC</t>
+        </is>
+      </c>
+      <c r="F7" s="11" t="inlineStr">
+        <is>
+          <t>The same serving-area leaders were traced on all three buildings for which screens exist. RDC has never had screens supplied.</t>
+        </is>
+      </c>
+      <c r="G7" s="11" t="inlineStr">
+        <is>
+          <t>QNL: 230 of 551 register rows read across 17 screens, 78 raised for review (19 outright disagreements, 59 wanting a second look), 321 left blank each with a recorded reason. HQ: 19 units read in the AHU/VAV/FCU pass plus 9 in the equipment pass, over 31 screens. SSC: 87 plus 19, over 7 screens.</t>
+        </is>
+      </c>
+      <c r="H7" s="11" t="inlineStr">
+        <is>
+          <t>One method, three buildings, so the findings are comparable. The largest single finding is on QNL: 27 second-floor units (11 VAV-2F-S12, 16 VAV-2F-S14) carry first-floor rooms in the register.</t>
+        </is>
+      </c>
+      <c r="I7" s="11" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -671,7 +934,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="8.21875" customWidth="1" min="1" max="1"/>
@@ -737,17 +1000,452 @@
     <row r="2" ht="58.05" customHeight="1">
       <c r="A2" s="10" t="inlineStr">
         <is>
-          <t>(no entries yet)</t>
-        </is>
-      </c>
-      <c r="B2" s="11" t="n"/>
-      <c r="C2" s="11" t="n"/>
-      <c r="D2" s="11" t="n"/>
-      <c r="E2" s="11" t="n"/>
-      <c r="F2" s="11" t="n"/>
-      <c r="G2" s="11" t="n"/>
-      <c r="H2" s="11" t="n"/>
-      <c r="I2" s="11" t="n"/>
+          <t>HQ-001</t>
+        </is>
+      </c>
+      <c r="B2" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C2" s="15" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="D2" s="11" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>52 equipment entities: 27 CEF car-park exhaust fans, 11 GEF general exhaust fans, 5 heat exchangers HEX01-HEX05, 4 chilled-water booster pumps CHW_CHWP01-04, 4 TEF toilet exhaust fans, CCU_B0005</t>
+        </is>
+      </c>
+      <c r="F2" s="11" t="inlineStr">
+        <is>
+          <t>Their rec:locatedIn object is the literal placeholder entity:&lt;Location&gt; - the template text was never replaced with a room.</t>
+        </is>
+      </c>
+      <c r="G2" s="11" t="inlineStr">
+        <is>
+          <t>Left the rows as delivered and flagged all 52. One is settled by the screens: CCU-B-0005 leads into VIP Parking B.115 on HQ/Basment Floor/BF-2, alongside CCU-B-0006/0007/0008 which the ontology already puts there.</t>
+        </is>
+      </c>
+      <c r="H2" s="11" t="inlineStr">
+        <is>
+          <t>entity:&lt;Location&gt; is not a room. It converts to a dangling reference in the TTL and the front end has nothing to place the unit against. QNL-043 on the QNL sheet is the precedent for a fix - rec:locatedIn the building entity where no room is known - but that was a decision taken on an ontology we build, and HQ is a delivered model, so it is raised here rather than applied.</t>
+        </is>
+      </c>
+      <c r="I2" s="11" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" ht="58.05" customHeight="1">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>HQ-002</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="D3" s="11" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="E3" s="11" t="inlineStr">
+        <is>
+          <t>HEX, DX_CP, DX_ODSB0101, DX_ODSB0102, DX_ODSB0201, DX_ODSB0202</t>
+        </is>
+      </c>
+      <c r="F3" s="11" t="inlineStr">
+        <is>
+          <t>The rec:locatedIn row exists but its object cell is empty.</t>
+        </is>
+      </c>
+      <c r="G3" s="11" t="inlineStr">
+        <is>
+          <t>Left as delivered and flagged all six.</t>
+        </is>
+      </c>
+      <c r="H3" s="11" t="inlineStr">
+        <is>
+          <t>An empty object is a triple with two terms. It is a different defect from the placeholder above and needs a different fix, so it is logged apart.</t>
+        </is>
+      </c>
+      <c r="I3" s="11" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" ht="58.05" customHeight="1">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>HQ-003</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="E4" s="11" t="inlineStr">
+        <is>
+          <t>entity:HQ_ELEC_Gen2, entity:HQ_ELEC_Gen3</t>
+        </is>
+      </c>
+      <c r="F4" s="11" t="inlineStr">
+        <is>
+          <t>Both generators carry brick:hasPoint rows but no rec:locatedIn row at all.</t>
+        </is>
+      </c>
+      <c r="G4" s="11" t="inlineStr">
+        <is>
+          <t>Left as delivered and flagged both.</t>
+        </is>
+      </c>
+      <c r="H4" s="11" t="inlineStr">
+        <is>
+          <t>These are the only two top-level HQ entities carrying points with no location row. The other 95 hits are VFD and electrical-meter sub-entities that hang off a parent and are located with it, which is correct.</t>
+        </is>
+      </c>
+      <c r="I4" s="11" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" ht="58.05" customHeight="1">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>HQ-004</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>entity:HQ_FCU0097, entity:HQ_FCU00133</t>
+        </is>
+      </c>
+      <c r="F5" s="11" t="inlineStr">
+        <is>
+          <t>Both carry rec:locatedIn entity:&lt;FCU-Ref_Location&gt; - a second, differently spelled placeholder.</t>
+        </is>
+      </c>
+      <c r="G5" s="11" t="inlineStr">
+        <is>
+          <t>Reported. Outside the scope of the equipment pass, which excludes AHU, VAV and FCU, so these two are not in HQ_SSC_equipment_rooms.xlsx.</t>
+        </is>
+      </c>
+      <c r="H5" s="11" t="inlineStr">
+        <is>
+          <t>Logged so a search for entity:&lt;Location&gt; is not mistaken for a complete list of unlocated HQ equipment. FCU0097 does have a screen reading from the earlier pass: B.512 IDF ROOM on HQ/Basment Floor/BF-2.</t>
+        </is>
+      </c>
+      <c r="I5" s="11" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" ht="58.05" customHeight="1">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>HQ-005</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C6" s="16" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="inlineStr">
+        <is>
+          <t>18 car-park fans: JF-B-0001 to JF-B-0010, IF-B-0001 to IF-B-0008</t>
+        </is>
+      </c>
+      <c r="F6" s="11" t="inlineStr">
+        <is>
+          <t>All 18 are drawn and tagged on the HQ car-park screens. The ontology has no entity for any of them - not unlocated, absent.</t>
+        </is>
+      </c>
+      <c r="G6" s="11" t="inlineStr">
+        <is>
+          <t>Listed all 18 in HQ_SSC_equipment_rooms.xlsx with the screen they appear on.</t>
+        </is>
+      </c>
+      <c r="H6" s="11" t="inlineStr">
+        <is>
+          <t>Jet fans and induction fans are the car park ventilation. They are monitored on the BMS, so the historian has their points, and an ontology that omits them leaves those points unreachable.</t>
+        </is>
+      </c>
+      <c r="I6" s="11" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" ht="58.05" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>HQ-006</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="E7" s="11" t="inlineStr">
+        <is>
+          <t>The 27 CEF car-park exhaust fans of HQ-001</t>
+        </is>
+      </c>
+      <c r="F7" s="11" t="inlineStr">
+        <is>
+          <t>Each CEF B-number maps to a car park deck screen, so the screens do say which deck the fan is on.</t>
+        </is>
+      </c>
+      <c r="G7" s="11" t="inlineStr">
+        <is>
+          <t>Recorded the deck against each fan; did not invent a room.</t>
+        </is>
+      </c>
+      <c r="H7" s="11" t="inlineStr">
+        <is>
+          <t>The car park decks carry no room names at all - bay numbers, Exit and Public Vehicle Out, nothing else. The deck is real information but it is not a room, so the 52 placeholders cannot be closed from these screens.</t>
+        </is>
+      </c>
+      <c r="I7" s="11" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" ht="58.05" customHeight="1">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>HQ-007</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="E8" s="11" t="inlineStr">
+        <is>
+          <t>DX-B-0011, DX-B-0016, DX-B-0003, CCU-B-0003A</t>
+        </is>
+      </c>
+      <c r="F8" s="11" t="inlineStr">
+        <is>
+          <t>The ontology room and the room the serving-area leader points at differ. DX-B-0011: B1.009 MV SWITCH ROOM against UPS Room B.26. DX-B-0016: B1.018 PA ROOM against AHU-3 B.022. CCU-B-0003A: B1.106 VVIP PARKING 6 CAR SPOTS against the Chauffer Room B.117 band. DX-B-0003 lands in an unlabelled cell east of Transformer Substation B.010.</t>
+        </is>
+      </c>
+      <c r="G8" s="11" t="inlineStr">
+        <is>
+          <t>Did not overwrite. Wrote the screen room beside the ontology room and flagged all four.</t>
+        </is>
+      </c>
+      <c r="H8" s="11" t="inlineStr">
+        <is>
+          <t>Two as-built sources disagree and neither is provably right. DX-B-0003 is flagged for a different reason: the screen has no name for the cell the dot is in, so it cannot confirm the ontology room either way.</t>
+        </is>
+      </c>
+      <c r="I8" s="11" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" ht="58.05" customHeight="1">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>HQ-008</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>CCU-B-0005, CCU-B-0006, CCU-B-0007, CCU-B-0008</t>
+        </is>
+      </c>
+      <c r="F9" s="11" t="inlineStr">
+        <is>
+          <t>An earlier draft of this pass flagged eight HQ CRACs on the grounds that a CRAC located in a parking bay looked like a fill error.</t>
+        </is>
+      </c>
+      <c r="G9" s="11" t="inlineStr">
+        <is>
+          <t>Flag withdrawn. The screens show all four leaders running into VIP Parking B.115, which is what the ontology says for three of them.</t>
+        </is>
+      </c>
+      <c r="H9" s="11" t="inlineStr">
+        <is>
+          <t>That flag was an inference about what is plausible, not a reading off a screen. Once HQ.zip arrived the screens settled it, and a plausibility hunch that survives into the sheet is indistinguishable from evidence.</t>
+        </is>
+      </c>
+      <c r="I9" s="11" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" ht="58.05" customHeight="1">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>HQ-009</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C10" s="16" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="E10" s="11" t="inlineStr">
+        <is>
+          <t>The HQ BMS screen pass</t>
+        </is>
+      </c>
+      <c r="F10" s="11" t="inlineStr">
+        <is>
+          <t>31 HQ floor-plan screens were supplied, across the basement, ground, 1F-11F, the roof and the car park decks.</t>
+        </is>
+      </c>
+      <c r="G10" s="11" t="inlineStr">
+        <is>
+          <t>19 HQ units were read off them in the AHU/VAV/FCU pass and 9 in the equipment pass. HQ screens label rooms outside the room polygon, joined by their own dashed pointer, so each reading resolves the polygon first and then finds the label pointing into it.</t>
+        </is>
+      </c>
+      <c r="H10" s="11" t="inlineStr">
+        <is>
+          <t>Reading the nearest text instead of the polygon is what put VAV0026 in the lobby. Every HQ reading carries its screen and an ok/check confidence, and units the screens do not settle are left blank with a reason.</t>
+        </is>
+      </c>
+      <c r="I10" s="11" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" ht="58.05" customHeight="1">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>HQ-010</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C11" s="15" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>Screen findings across the three buildings reviewed - QNL, HQ, SSC</t>
+        </is>
+      </c>
+      <c r="F11" s="11" t="inlineStr">
+        <is>
+          <t>The same serving-area leaders were traced on all three buildings for which screens exist. RDC has never had screens supplied.</t>
+        </is>
+      </c>
+      <c r="G11" s="11" t="inlineStr">
+        <is>
+          <t>QNL: 230 of 551 register rows read across 17 screens, 78 raised for review (19 outright disagreements, 59 wanting a second look), 321 left blank each with a recorded reason. HQ: 19 plus 9 units over 31 screens. SSC: 87 plus 19 units over 7 screens.</t>
+        </is>
+      </c>
+      <c r="H11" s="11" t="inlineStr">
+        <is>
+          <t>One method, three buildings, so the findings are comparable. HQ is the only one of the three whose ontology leaves equipment unlocated - 52 placeholders, 6 empty objects, 2 with no location row and 18 units with no entity at all. SSC has none of that but has the DX fill-down; QNL's largest finding is 27 second-floor units carrying first-floor rooms.</t>
+        </is>
+      </c>
+      <c r="I11" s="11" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1886,7 +2584,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="58.05" customHeight="1">
       <c r="A25" s="11" t="inlineStr">
         <is>
           <t>QNL-031</t>
@@ -1897,7 +2595,7 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="C25" s="13" t="inlineStr">
+      <c r="C25" s="17" t="inlineStr">
         <is>
           <t>Structure</t>
         </is>
@@ -1933,7 +2631,7 @@
         </is>
       </c>
     </row>
-    <row r="26">
+    <row r="26" ht="58.05" customHeight="1">
       <c r="A26" s="11" t="inlineStr">
         <is>
           <t>QNL-032</t>
@@ -1944,7 +2642,7 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="C26" s="13" t="inlineStr">
+      <c r="C26" s="18" t="inlineStr">
         <is>
           <t>Identifier</t>
         </is>
@@ -1980,7 +2678,7 @@
         </is>
       </c>
     </row>
-    <row r="27">
+    <row r="27" ht="58.05" customHeight="1">
       <c r="A27" s="11" t="inlineStr">
         <is>
           <t>QNL-033</t>
@@ -1991,7 +2689,7 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="C27" s="13" t="inlineStr">
+      <c r="C27" s="16" t="inlineStr">
         <is>
           <t>Scope</t>
         </is>
@@ -2027,7 +2725,7 @@
         </is>
       </c>
     </row>
-    <row r="28">
+    <row r="28" ht="58.05" customHeight="1">
       <c r="A28" s="11" t="inlineStr">
         <is>
           <t>QNL-034</t>
@@ -2074,7 +2772,7 @@
         </is>
       </c>
     </row>
-    <row r="29">
+    <row r="29" ht="58.05" customHeight="1">
       <c r="A29" s="11" t="inlineStr">
         <is>
           <t>QNL-035</t>
@@ -2085,7 +2783,7 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="C29" s="13" t="inlineStr">
+      <c r="C29" s="17" t="inlineStr">
         <is>
           <t>Structure</t>
         </is>
@@ -2121,7 +2819,7 @@
         </is>
       </c>
     </row>
-    <row r="30">
+    <row r="30" ht="58.05" customHeight="1">
       <c r="A30" s="11" t="inlineStr">
         <is>
           <t>QNL-036</t>
@@ -2132,7 +2830,7 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="C30" s="13" t="inlineStr">
+      <c r="C30" s="17" t="inlineStr">
         <is>
           <t>Structure</t>
         </is>
@@ -2168,7 +2866,7 @@
         </is>
       </c>
     </row>
-    <row r="31">
+    <row r="31" ht="58.05" customHeight="1">
       <c r="A31" s="11" t="inlineStr">
         <is>
           <t>QNL-037</t>
@@ -2179,7 +2877,7 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="C31" s="13" t="inlineStr">
+      <c r="C31" s="14" t="inlineStr">
         <is>
           <t>Class</t>
         </is>
@@ -2215,7 +2913,7 @@
         </is>
       </c>
     </row>
-    <row r="32">
+    <row r="32" ht="58.05" customHeight="1">
       <c r="A32" s="11" t="inlineStr">
         <is>
           <t>QNL-038</t>
@@ -2226,7 +2924,7 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="C32" s="13" t="inlineStr">
+      <c r="C32" s="19" t="inlineStr">
         <is>
           <t>Source defect</t>
         </is>
@@ -2262,7 +2960,7 @@
         </is>
       </c>
     </row>
-    <row r="33">
+    <row r="33" ht="58.05" customHeight="1">
       <c r="A33" s="11" t="inlineStr">
         <is>
           <t>QNL-039</t>
@@ -2273,7 +2971,7 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="C33" s="13" t="inlineStr">
+      <c r="C33" s="19" t="inlineStr">
         <is>
           <t>Source defect</t>
         </is>
@@ -2309,7 +3007,7 @@
         </is>
       </c>
     </row>
-    <row r="34">
+    <row r="34" ht="58.05" customHeight="1">
       <c r="A34" s="11" t="inlineStr">
         <is>
           <t>QNL-040</t>
@@ -2320,7 +3018,7 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="C34" s="13" t="inlineStr">
+      <c r="C34" s="16" t="inlineStr">
         <is>
           <t>Scope</t>
         </is>
@@ -2356,7 +3054,7 @@
         </is>
       </c>
     </row>
-    <row r="35">
+    <row r="35" ht="58.05" customHeight="1">
       <c r="A35" s="11" t="inlineStr">
         <is>
           <t>QNL-041</t>
@@ -2367,7 +3065,7 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="C35" s="13" t="inlineStr">
+      <c r="C35" s="19" t="inlineStr">
         <is>
           <t>Source defect</t>
         </is>
@@ -2403,7 +3101,7 @@
         </is>
       </c>
     </row>
-    <row r="36">
+    <row r="36" ht="58.05" customHeight="1">
       <c r="A36" s="11" t="inlineStr">
         <is>
           <t>QNL-042</t>
@@ -2414,7 +3112,7 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="C36" s="13" t="inlineStr">
+      <c r="C36" s="19" t="inlineStr">
         <is>
           <t>Source defect</t>
         </is>
@@ -2450,7 +3148,7 @@
         </is>
       </c>
     </row>
-    <row r="37">
+    <row r="37" ht="58.05" customHeight="1">
       <c r="A37" s="11" t="inlineStr">
         <is>
           <t>QNL-043</t>
@@ -2461,7 +3159,7 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="C37" s="13" t="inlineStr">
+      <c r="C37" s="15" t="inlineStr">
         <is>
           <t>Location</t>
         </is>

--- a/projects/Assumption_Log.xlsx
+++ b/projects/Assumption_Log.xlsx
@@ -2,8 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="22932" yWindow="-2916" windowWidth="30936" windowHeight="16776" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="SSC" sheetId="1" state="visible" r:id="rId1"/>
@@ -11,33 +12,26 @@
     <sheet name="QNL" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="RDC" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'SSC'!$A$1:$I$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'HQ'!$A$1:$I$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'QNL'!$A$1:$I$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'RDC'!$A$1:$I$2</definedName>
+  </definedNames>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <i val="1"/>
-      <color rgb="FF808080"/>
-      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
@@ -49,7 +43,7 @@
       <color rgb="FF808080"/>
     </font>
   </fonts>
-  <fills count="16">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -63,27 +57,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE2EFDA"/>
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
+        <fgColor rgb="00FBE5D6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE4DFEC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCE4D6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
     <fill>
@@ -103,16 +87,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00DEEAF6"/>
       </patternFill>
     </fill>
@@ -121,13 +95,8 @@
         <fgColor rgb="00DDEBF7"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FBE5D6"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -148,32 +117,16 @@
       <bottom style="thin">
         <color rgb="FFBFBFBF"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFBFBFBF"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFBFBFBF"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFBFBFBF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFBFBFBF"/>
-      </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -192,42 +145,21 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -591,339 +523,338 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8.21875" customWidth="1" min="1" max="1"/>
     <col width="10.33203125" customWidth="1" min="2" max="2"/>
     <col width="12.21875" customWidth="1" min="3" max="3"/>
     <col width="9.6640625" customWidth="1" min="4" max="4"/>
     <col width="32.77734375" customWidth="1" min="5" max="5"/>
-    <col width="46" customWidth="1" min="6" max="7"/>
+    <col width="46" customWidth="1" min="6" max="6"/>
     <col width="45" customWidth="1" min="7" max="7"/>
     <col width="52" customWidth="1" min="8" max="8"/>
     <col width="12.88671875" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="C1" s="9" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D1" s="9" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Layer</t>
         </is>
       </c>
-      <c r="E1" s="9" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Entity / Scope</t>
         </is>
       </c>
-      <c r="F1" s="9" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>What the source says</t>
         </is>
       </c>
-      <c r="G1" s="9" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>What we did</t>
         </is>
       </c>
-      <c r="H1" s="9" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Why / basis</t>
         </is>
       </c>
-      <c r="I1" s="9" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Rows affected</t>
         </is>
       </c>
     </row>
     <row r="2" ht="58.05" customHeight="1">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>SSC-001</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="C2" s="15" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="D2" s="11" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Equipment</t>
         </is>
       </c>
-      <c r="E2" s="11" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>7 exhaust fans: GEFB0001, KEF0103, KEF0303, TEF0101, TEF0102, TEF0301, TEF0302</t>
         </is>
       </c>
-      <c r="F2" s="11" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>All seven carry rec:locatedIn entity:Level7_Office0367, and that room entity carries no rdfs:label_en anywhere in the sheet - so it has no readable name.</t>
         </is>
       </c>
-      <c r="G2" s="11" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Left the triples as delivered and flagged all seven for the client. Two of them are settled by the screens: KEF0103 is drawn in 01.005 KITCHEN and TEF0101 in 01.028 CORRIDOR (SSC/FF-part2).</t>
         </is>
       </c>
-      <c r="H2" s="11" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>A room with no label cannot be shown in the front end and cannot be checked against a drawing. Seven fans on seven different levels sharing one seventh-floor office reads as a fill-down, not as seven readings. Unlike HQ this is a naming gap, not a missing location - the room entity exists and is referenced, it simply has no label.</t>
         </is>
       </c>
-      <c r="I2" s="11" t="n">
+      <c r="I2" s="2" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="3" ht="58.05" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>SSC-002</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="D3" s="11" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Equipment</t>
         </is>
       </c>
-      <c r="E3" s="11" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Every other located SSC entity</t>
         </is>
       </c>
-      <c r="F3" s="11" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>All 166 rec:locatedIn rows in SSC_Ontology_Ver0.6 name a real room entity - no entity:&lt;Location&gt; placeholders, no blank objects.</t>
         </is>
       </c>
-      <c r="G3" s="11" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Recorded the check; nothing to raise.</t>
         </is>
       </c>
-      <c r="H3" s="11" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Stated so the SSC sheet is not read as silent on the question that HQ fails. SSC has no equipment carrying points and no rec:locatedIn at all.</t>
         </is>
       </c>
-      <c r="I3" s="11" t="n">
+      <c r="I3" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="4" ht="58.05" customHeight="1">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>SSC-003</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="C4" s="15" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Equipment</t>
         </is>
       </c>
-      <c r="E4" s="11" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>DX-B-0001, DX-B-0002, DX-B-0004, DX-B-0006, DX-B-0007, DX-B-0008, DX-B-0009, DX-B-0010, CCU-B-0004, CCU-B-0007</t>
         </is>
       </c>
-      <c r="F4" s="11" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>The ontology room and the room the BMS serving-area leader points at differ on all ten. DX-B-0009 is B1.020 FM STORAGE in the ontology and B.002 HV ROOM on the screen; CCU-B-0007 is B1.017 MDF-2 against B.026 MDF/SER.1.</t>
         </is>
       </c>
-      <c r="G4" s="11" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Did not overwrite the ontology. Wrote the screen room beside it and flagged all ten in HQ_SSC_equipment_rooms.xlsx for the client to settle.</t>
         </is>
       </c>
-      <c r="H4" s="11" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Two as-built sources disagree. The screen is the live BMS graphic and the ontology room came from the register, so neither can be assumed correct - a guess written into the room column is indistinguishable from a reading.</t>
         </is>
       </c>
-      <c r="I4" s="11" t="n">
+      <c r="I4" s="2" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="5" ht="58.05" customHeight="1">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>SSC-004</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="C5" s="19" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>Source defect</t>
         </is>
       </c>
-      <c r="D5" s="11" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Equipment</t>
         </is>
       </c>
-      <c r="E5" s="11" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>DX-B-0001 to DX-B-0004; DX-B-0007 and DX-B-0008</t>
         </is>
       </c>
-      <c r="F5" s="11" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>DX-B-0001 to 0004 all carry B1.005 UPS; DX-B-0007 and DX-B-0008 both carry B1.019 FM STORAGE. The screens put them in B.022 SSP, B.022 SSP, B.005 UPS, B.008 VENT PLANT and in B.006 SERVICE AREA, B.008 VENT PLANT.</t>
         </is>
       </c>
-      <c r="G5" s="11" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Reported the pattern rather than correcting it.</t>
         </is>
       </c>
-      <c r="H5" s="11" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Four consecutive units sharing one room where the screens spread them across four rooms is the signature of a filled-down cell, not of four units in one plant room. Only DX-B-0003 matches - and it is the third of the four.</t>
         </is>
       </c>
-      <c r="I5" s="11" t="n">
+      <c r="I5" s="2" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="6" ht="58.05" customHeight="1">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>SSC-005</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>Scope</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Equipment</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>The SSC BMS screen pass</t>
         </is>
       </c>
-      <c r="F6" s="11" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Seven SSC floor-plan screens were supplied: BF-part1, BF-part2, FF-part1, FF-part2, Second Floor, TF-part1, TF-part2.</t>
         </is>
       </c>
-      <c r="G6" s="11" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>87 SSC units were read off those screens in the AHU/VAV/FCU pass, and a further 19 non-AHU/VAV/FCU units (DX, CRAC, exhaust fans) in the equipment pass. Every reading carries the screen it came from and an ok/check confidence. Units on no supplied screen were left blank with a reason.</t>
         </is>
       </c>
-      <c r="H6" s="11" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>A leader that could not be followed, or a marker landing on a wall, is recorded as blank-with-a-reason rather than filled in. Over-inclusion is worse than omission: a wrong room validates clean.</t>
         </is>
       </c>
-      <c r="I6" s="11" t="n">
+      <c r="I6" s="2" t="n">
         <v>106</v>
       </c>
     </row>
     <row r="7" ht="58.05" customHeight="1">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>SSC-006</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="C7" s="15" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="D7" s="11" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Equipment</t>
         </is>
       </c>
-      <c r="E7" s="11" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Screen findings across the three buildings reviewed - QNL, HQ, SSC</t>
         </is>
       </c>
-      <c r="F7" s="11" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>The same serving-area leaders were traced on all three buildings for which screens exist. RDC has never had screens supplied.</t>
         </is>
       </c>
-      <c r="G7" s="11" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>QNL: 230 of 551 register rows read across 17 screens, 78 raised for review (19 outright disagreements, 59 wanting a second look), 321 left blank each with a recorded reason. HQ: 19 units read in the AHU/VAV/FCU pass plus 9 in the equipment pass, over 31 screens. SSC: 87 plus 19, over 7 screens.</t>
         </is>
       </c>
-      <c r="H7" s="11" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>One method, three buildings, so the findings are comparable. The largest single finding is on QNL: 27 second-floor units (11 VAV-2F-S12, 16 VAV-2F-S14) carry first-floor rooms in the register.</t>
         </is>
       </c>
-      <c r="I7" s="11" t="n">
+      <c r="I7" s="2" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:I7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -935,519 +866,518 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8.21875" customWidth="1" min="1" max="1"/>
     <col width="10.33203125" customWidth="1" min="2" max="2"/>
     <col width="12.21875" customWidth="1" min="3" max="3"/>
     <col width="9.6640625" customWidth="1" min="4" max="4"/>
     <col width="32.77734375" customWidth="1" min="5" max="5"/>
-    <col width="46" customWidth="1" min="6" max="7"/>
+    <col width="46" customWidth="1" min="6" max="6"/>
     <col width="45" customWidth="1" min="7" max="7"/>
     <col width="52" customWidth="1" min="8" max="8"/>
     <col width="12.88671875" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="C1" s="9" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D1" s="9" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Layer</t>
         </is>
       </c>
-      <c r="E1" s="9" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Entity / Scope</t>
         </is>
       </c>
-      <c r="F1" s="9" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>What the source says</t>
         </is>
       </c>
-      <c r="G1" s="9" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>What we did</t>
         </is>
       </c>
-      <c r="H1" s="9" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Why / basis</t>
         </is>
       </c>
-      <c r="I1" s="9" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Rows affected</t>
         </is>
       </c>
     </row>
     <row r="2" ht="58.05" customHeight="1">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>HQ-001</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="C2" s="15" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="D2" s="11" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Equipment</t>
         </is>
       </c>
-      <c r="E2" s="11" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>52 equipment entities: 27 CEF car-park exhaust fans, 11 GEF general exhaust fans, 5 heat exchangers HEX01-HEX05, 4 chilled-water booster pumps CHW_CHWP01-04, 4 TEF toilet exhaust fans, CCU_B0005</t>
         </is>
       </c>
-      <c r="F2" s="11" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>Their rec:locatedIn object is the literal placeholder entity:&lt;Location&gt; - the template text was never replaced with a room.</t>
         </is>
       </c>
-      <c r="G2" s="11" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Left the rows as delivered and flagged all 52. One is settled by the screens: CCU-B-0005 leads into VIP Parking B.115 on HQ/Basment Floor/BF-2, alongside CCU-B-0006/0007/0008 which the ontology already puts there.</t>
         </is>
       </c>
-      <c r="H2" s="11" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>entity:&lt;Location&gt; is not a room. It converts to a dangling reference in the TTL and the front end has nothing to place the unit against. QNL-043 on the QNL sheet is the precedent for a fix - rec:locatedIn the building entity where no room is known - but that was a decision taken on an ontology we build, and HQ is a delivered model, so it is raised here rather than applied.</t>
         </is>
       </c>
-      <c r="I2" s="11" t="n">
+      <c r="I2" s="2" t="n">
         <v>52</v>
       </c>
     </row>
     <row r="3" ht="58.05" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>HQ-002</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="D3" s="11" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Equipment</t>
         </is>
       </c>
-      <c r="E3" s="11" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>HEX, DX_CP, DX_ODSB0101, DX_ODSB0102, DX_ODSB0201, DX_ODSB0202</t>
         </is>
       </c>
-      <c r="F3" s="11" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>The rec:locatedIn row exists but its object cell is empty.</t>
         </is>
       </c>
-      <c r="G3" s="11" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Left as delivered and flagged all six.</t>
         </is>
       </c>
-      <c r="H3" s="11" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>An empty object is a triple with two terms. It is a different defect from the placeholder above and needs a different fix, so it is logged apart.</t>
         </is>
       </c>
-      <c r="I3" s="11" t="n">
+      <c r="I3" s="2" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="4" ht="58.05" customHeight="1">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>HQ-003</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="C4" s="15" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Equipment</t>
         </is>
       </c>
-      <c r="E4" s="11" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>entity:HQ_ELEC_Gen2, entity:HQ_ELEC_Gen3</t>
         </is>
       </c>
-      <c r="F4" s="11" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Both generators carry brick:hasPoint rows but no rec:locatedIn row at all.</t>
         </is>
       </c>
-      <c r="G4" s="11" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Left as delivered and flagged both.</t>
         </is>
       </c>
-      <c r="H4" s="11" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>These are the only two top-level HQ entities carrying points with no location row. The other 95 hits are VFD and electrical-meter sub-entities that hang off a parent and are located with it, which is correct.</t>
         </is>
       </c>
-      <c r="I4" s="11" t="n">
+      <c r="I4" s="2" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="5" ht="58.05" customHeight="1">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>HQ-004</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="C5" s="15" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="D5" s="11" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Equipment</t>
         </is>
       </c>
-      <c r="E5" s="11" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>entity:HQ_FCU0097, entity:HQ_FCU00133</t>
         </is>
       </c>
-      <c r="F5" s="11" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Both carry rec:locatedIn entity:&lt;FCU-Ref_Location&gt; - a second, differently spelled placeholder.</t>
         </is>
       </c>
-      <c r="G5" s="11" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Reported. Outside the scope of the equipment pass, which excludes AHU, VAV and FCU, so these two are not in HQ_SSC_equipment_rooms.xlsx.</t>
         </is>
       </c>
-      <c r="H5" s="11" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Logged so a search for entity:&lt;Location&gt; is not mistaken for a complete list of unlocated HQ equipment. FCU0097 does have a screen reading from the earlier pass: B.512 IDF ROOM on HQ/Basment Floor/BF-2.</t>
         </is>
       </c>
-      <c r="I5" s="11" t="n">
+      <c r="I5" s="2" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="6" ht="58.05" customHeight="1">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>HQ-005</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>Scope</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Equipment</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>18 car-park fans: JF-B-0001 to JF-B-0010, IF-B-0001 to IF-B-0008</t>
         </is>
       </c>
-      <c r="F6" s="11" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>All 18 are drawn and tagged on the HQ car-park screens. The ontology has no entity for any of them - not unlocated, absent.</t>
         </is>
       </c>
-      <c r="G6" s="11" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Listed all 18 in HQ_SSC_equipment_rooms.xlsx with the screen they appear on.</t>
         </is>
       </c>
-      <c r="H6" s="11" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Jet fans and induction fans are the car park ventilation. They are monitored on the BMS, so the historian has their points, and an ontology that omits them leaves those points unreachable.</t>
         </is>
       </c>
-      <c r="I6" s="11" t="n">
+      <c r="I6" s="2" t="n">
         <v>18</v>
       </c>
     </row>
     <row r="7" ht="58.05" customHeight="1">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>HQ-006</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="C7" s="15" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="D7" s="11" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Equipment</t>
         </is>
       </c>
-      <c r="E7" s="11" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>The 27 CEF car-park exhaust fans of HQ-001</t>
         </is>
       </c>
-      <c r="F7" s="11" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Each CEF B-number maps to a car park deck screen, so the screens do say which deck the fan is on.</t>
         </is>
       </c>
-      <c r="G7" s="11" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>Recorded the deck against each fan; did not invent a room.</t>
         </is>
       </c>
-      <c r="H7" s="11" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>The car park decks carry no room names at all - bay numbers, Exit and Public Vehicle Out, nothing else. The deck is real information but it is not a room, so the 52 placeholders cannot be closed from these screens.</t>
         </is>
       </c>
-      <c r="I7" s="11" t="n">
+      <c r="I7" s="2" t="n">
         <v>27</v>
       </c>
     </row>
     <row r="8" ht="58.05" customHeight="1">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>HQ-007</t>
         </is>
       </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="C8" s="15" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="D8" s="11" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Equipment</t>
         </is>
       </c>
-      <c r="E8" s="11" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>DX-B-0011, DX-B-0016, DX-B-0003, CCU-B-0003A</t>
         </is>
       </c>
-      <c r="F8" s="11" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>The ontology room and the room the serving-area leader points at differ. DX-B-0011: B1.009 MV SWITCH ROOM against UPS Room B.26. DX-B-0016: B1.018 PA ROOM against AHU-3 B.022. CCU-B-0003A: B1.106 VVIP PARKING 6 CAR SPOTS against the Chauffer Room B.117 band. DX-B-0003 lands in an unlabelled cell east of Transformer Substation B.010.</t>
         </is>
       </c>
-      <c r="G8" s="11" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>Did not overwrite. Wrote the screen room beside the ontology room and flagged all four.</t>
         </is>
       </c>
-      <c r="H8" s="11" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Two as-built sources disagree and neither is provably right. DX-B-0003 is flagged for a different reason: the screen has no name for the cell the dot is in, so it cannot confirm the ontology room either way.</t>
         </is>
       </c>
-      <c r="I8" s="11" t="n">
+      <c r="I8" s="2" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="9" ht="58.05" customHeight="1">
-      <c r="A9" s="11" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>HQ-008</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="C9" s="15" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="D9" s="11" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Equipment</t>
         </is>
       </c>
-      <c r="E9" s="11" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>CCU-B-0005, CCU-B-0006, CCU-B-0007, CCU-B-0008</t>
         </is>
       </c>
-      <c r="F9" s="11" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>An earlier draft of this pass flagged eight HQ CRACs on the grounds that a CRAC located in a parking bay looked like a fill error.</t>
         </is>
       </c>
-      <c r="G9" s="11" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>Flag withdrawn. The screens show all four leaders running into VIP Parking B.115, which is what the ontology says for three of them.</t>
         </is>
       </c>
-      <c r="H9" s="11" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>That flag was an inference about what is plausible, not a reading off a screen. Once HQ.zip arrived the screens settled it, and a plausibility hunch that survives into the sheet is indistinguishable from evidence.</t>
         </is>
       </c>
-      <c r="I9" s="11" t="n">
+      <c r="I9" s="2" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="10" ht="58.05" customHeight="1">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>HQ-009</t>
         </is>
       </c>
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>Scope</t>
         </is>
       </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Equipment</t>
         </is>
       </c>
-      <c r="E10" s="11" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>The HQ BMS screen pass</t>
         </is>
       </c>
-      <c r="F10" s="11" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>31 HQ floor-plan screens were supplied, across the basement, ground, 1F-11F, the roof and the car park decks.</t>
         </is>
       </c>
-      <c r="G10" s="11" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>19 HQ units were read off them in the AHU/VAV/FCU pass and 9 in the equipment pass. HQ screens label rooms outside the room polygon, joined by their own dashed pointer, so each reading resolves the polygon first and then finds the label pointing into it.</t>
         </is>
       </c>
-      <c r="H10" s="11" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>Reading the nearest text instead of the polygon is what put VAV0026 in the lobby. Every HQ reading carries its screen and an ok/check confidence, and units the screens do not settle are left blank with a reason.</t>
         </is>
       </c>
-      <c r="I10" s="11" t="n">
+      <c r="I10" s="2" t="n">
         <v>28</v>
       </c>
     </row>
     <row r="11" ht="58.05" customHeight="1">
-      <c r="A11" s="11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>HQ-010</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="C11" s="15" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="D11" s="11" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Equipment</t>
         </is>
       </c>
-      <c r="E11" s="11" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>Screen findings across the three buildings reviewed - QNL, HQ, SSC</t>
         </is>
       </c>
-      <c r="F11" s="11" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>The same serving-area leaders were traced on all three buildings for which screens exist. RDC has never had screens supplied.</t>
         </is>
       </c>
-      <c r="G11" s="11" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>QNL: 230 of 551 register rows read across 17 screens, 78 raised for review (19 outright disagreements, 59 wanting a second look), 321 left blank each with a recorded reason. HQ: 19 plus 9 units over 31 screens. SSC: 87 plus 19 units over 7 screens.</t>
         </is>
       </c>
-      <c r="H11" s="11" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>One method, three buildings, so the findings are comparable. HQ is the only one of the three whose ontology leaves equipment unlocated - 52 placeholders, 6 empty objects, 2 with no location row and 18 units with no entity at all. SSC has none of that but has the DX fill-down; QNL's largest finding is 27 second-floor units carrying first-floor rooms.</t>
         </is>
       </c>
-      <c r="I11" s="11" t="n">
+      <c r="I11" s="2" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:I11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1459,1743 +1389,1702 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I37"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8.21875" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="10.33203125" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="12.21875" bestFit="1" customWidth="1" min="3" max="3"/>
-    <col width="9.6640625" bestFit="1" customWidth="1" min="4" max="4"/>
-    <col width="32.77734375" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="8.21875" customWidth="1" min="1" max="1"/>
+    <col width="10.33203125" customWidth="1" min="2" max="2"/>
+    <col width="12.21875" customWidth="1" min="3" max="3"/>
+    <col width="9.6640625" customWidth="1" min="4" max="4"/>
+    <col width="32.77734375" customWidth="1" min="5" max="5"/>
     <col width="46" customWidth="1" min="6" max="6"/>
-    <col width="45" bestFit="1" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="52" customWidth="1" min="8" max="8"/>
-    <col width="12.88671875" bestFit="1" customWidth="1" min="9" max="9"/>
+    <col width="12.88671875" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="C1" s="9" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D1" s="9" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Layer</t>
         </is>
       </c>
-      <c r="E1" s="9" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Entity / Scope</t>
         </is>
       </c>
-      <c r="F1" s="9" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>What the source says</t>
         </is>
       </c>
-      <c r="G1" s="9" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>What we did</t>
         </is>
       </c>
-      <c r="H1" s="9" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Why / basis</t>
         </is>
       </c>
-      <c r="I1" s="9" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Rows affected</t>
         </is>
       </c>
     </row>
     <row r="2" ht="58.05" customHeight="1">
-      <c r="A2" s="11" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>QNL-007</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="C2" s="12" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>Spelling</t>
         </is>
       </c>
-      <c r="D2" s="11" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Rooms</t>
         </is>
       </c>
-      <c r="E2" s="11" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>24 room names</t>
         </is>
       </c>
-      <c r="F2" s="11" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>Hand-typed schedule carries misspellings (CARRLES, VENTILATON, GREEM)</t>
         </is>
       </c>
-      <c r="G2" s="11" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Corrected whole tokens only, on the name segment</t>
         </is>
       </c>
-      <c r="H2" s="11" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Each settled against a sibling room that spells it correctly - never guessed. Names reach users through rdfs:label_en.</t>
         </is>
       </c>
-      <c r="I2" s="11" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
+      <c r="I2" s="2" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="3" ht="58.05" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>QNL-008</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="C3" s="12" t="inlineStr">
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>Spelling</t>
         </is>
       </c>
-      <c r="D3" s="11" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Rooms</t>
         </is>
       </c>
-      <c r="E3" s="11" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>11 room names</t>
         </is>
       </c>
-      <c r="F3" s="11" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Run-together words (REST_ROOMMEN, ABLUTIONMEN, INDIVISTUDY)</t>
         </is>
       </c>
-      <c r="G3" s="11" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Restored the separator only; wording unchanged</t>
         </is>
       </c>
-      <c r="H3" s="11" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Every sibling room writes the two tokens apart. No abbreviation was expanded.</t>
         </is>
       </c>
-      <c r="I3" s="11" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="I3" s="2" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="4" ht="58.05" customHeight="1">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>QNL-009</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="C4" s="12" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>Spelling</t>
         </is>
       </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Rooms</t>
         </is>
       </c>
-      <c r="E4" s="11" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>INDIVI_STUDY_ROOM (6 rooms), B046_ITT</t>
         </is>
       </c>
-      <c r="F4" s="11" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>INDIVI probably means INDIVIDUAL; ITT sits in the room-number segment</t>
         </is>
       </c>
-      <c r="G4" s="11" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Left as-is</t>
         </is>
       </c>
-      <c r="H4" s="11" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Expanding an abbreviation is a rewrite, not a correction; ITT may be a drawing code and a join key. Client's call.</t>
         </is>
       </c>
-      <c r="I4" s="11" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="I4" s="2" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="5" ht="58.05" customHeight="1">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>QNL-010</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="C5" s="12" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>Spelling</t>
         </is>
       </c>
-      <c r="D5" s="11" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Equipment</t>
         </is>
       </c>
-      <c r="E5" s="11" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>All asset tags</t>
         </is>
       </c>
-      <c r="F5" s="11" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Register tags may contain errors</t>
         </is>
       </c>
-      <c r="G5" s="11" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Left completely untouched</t>
         </is>
       </c>
-      <c r="H5" s="11" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Asset tags are the BMS join key. Only room names were corrected.</t>
         </is>
       </c>
-      <c r="I5" s="11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="I5" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6" ht="58.05" customHeight="1">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>QNL-011</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>20 brick:Electric_Power_Sensor points</t>
         </is>
       </c>
-      <c r="F6" s="11" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>IO list gives '%' on 20 of its 24 .kW tags, against a description reading 'Power'</t>
         </is>
       </c>
-      <c r="G6" s="11" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Overrode to unit:KiloW</t>
         </is>
       </c>
-      <c r="H6" s="11" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>A power sensor cannot read a percentage. Dar Cairo uses unit:KiloW on all 559 of its Electric_Power_Sensor points.</t>
         </is>
       </c>
-      <c r="I6" s="11" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
+      <c r="I6" s="2" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="7" ht="58.05" customHeight="1">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>QNL-012</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="C7" s="13" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
       </c>
-      <c r="D7" s="11" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
       </c>
-      <c r="E7" s="11" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>22 AHU air-flow points</t>
         </is>
       </c>
-      <c r="F7" s="11" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>IO list gives 'm/s' (a velocity) on Supply_/Return_Air_Flow_Sensor</t>
         </is>
       </c>
-      <c r="G7" s="11" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>Overrode to unit:L-PER-SEC</t>
         </is>
       </c>
-      <c r="H7" s="11" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Dar Cairo uses L-PER-SEC on all 51 air-flow sensors, SSC on all 118; unit:M-PER-SEC occurs 0 times in either model, and no point in the IO list is named 'velocity'.</t>
         </is>
       </c>
-      <c r="I7" s="11" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+      <c r="I7" s="2" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="8" ht="58.05" customHeight="1">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>QNL-013</t>
         </is>
       </c>
-      <c r="B8" s="11" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="C8" s="13" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
       </c>
-      <c r="D8" s="11" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
       </c>
-      <c r="E8" s="11" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>30 analog rows in the Selected sheet</t>
         </is>
       </c>
-      <c r="F8" s="11" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Humidity and temperature units transposed (AvgSpcHumd as degC, AvgSpcTemp as %rH)</t>
         </is>
       </c>
-      <c r="G8" s="11" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>Took units from the IO list instead</t>
         </is>
       </c>
-      <c r="H8" s="11" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>The IO list has both right. The Selected sheet is not used as the unit authority anywhere.</t>
         </is>
       </c>
-      <c r="I8" s="11" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
+      <c r="I8" s="2" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="9" ht="58.05" customHeight="1">
-      <c r="A9" s="11" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>QNL-014</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="C9" s="13" t="inlineStr">
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
       </c>
-      <c r="D9" s="11" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
       </c>
-      <c r="E9" s="11" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>64 brick:Relative_Humidity_Sensor points</t>
         </is>
       </c>
-      <c r="F9" s="11" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Dar Cairo uses unit:PERCENT on this class</t>
         </is>
       </c>
-      <c r="G9" s="11" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>Used unit:PERCENT_RH</t>
         </is>
       </c>
-      <c r="H9" s="11" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>Dar Cairo contradicts itself - its Return_ and Supply_Air_Humidity_Sensor both use PERCENT_RH. SSC and the IO list agree with PERCENT_RH.</t>
         </is>
       </c>
-      <c r="I9" s="11" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
+      <c r="I9" s="2" t="n">
+        <v>64</v>
       </c>
     </row>
     <row r="10" ht="58.05" customHeight="1">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>QNL-015</t>
         </is>
       </c>
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="C10" s="13" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
       </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
       </c>
-      <c r="E10" s="11" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>22 brick:Speed_Sensor points</t>
         </is>
       </c>
-      <c r="F10" s="11" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>SSC uses unit:RPM on this class</t>
         </is>
       </c>
-      <c r="G10" s="11" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>Used unit:PERCENT</t>
         </is>
       </c>
-      <c r="H10" s="11" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>SSC's are Motor_Speed_Fbk (shaft RPM); QNL's are fan VFD SpeedFbk in % of max. Dar Cairo's Speed_Command is PERCENT on all 88.</t>
         </is>
       </c>
-      <c r="I10" s="11" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+      <c r="I10" s="2" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="11" ht="58.05" customHeight="1">
-      <c r="A11" s="11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>QNL-016</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="C11" s="13" t="inlineStr">
+      <c r="C11" s="7" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
       </c>
-      <c r="D11" s="11" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
       </c>
-      <c r="E11" s="11" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>295 brick:Air_Flow_Sensor points</t>
         </is>
       </c>
-      <c r="F11" s="11" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>Dar Cairo uses unit:UNITLESS on this class</t>
         </is>
       </c>
-      <c r="G11" s="11" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>Used unit:L-PER-SEC</t>
         </is>
       </c>
-      <c r="H11" s="11" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>A flow is not dimensionless - Dar Cairo's value is a missing unit, not a convention. Its own specific flow classes all use L-PER-SEC.</t>
         </is>
       </c>
-      <c r="I11" s="11" t="inlineStr">
-        <is>
-          <t>295</t>
-        </is>
+      <c r="I11" s="2" t="n">
+        <v>295</v>
       </c>
     </row>
     <row r="12" ht="58.05" customHeight="1">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>QNL-017</t>
         </is>
       </c>
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="C12" s="13" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
       </c>
-      <c r="D12" s="11" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
       </c>
-      <c r="E12" s="11" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>14 brick:Damper_Position_Command points</t>
         </is>
       </c>
-      <c r="F12" s="11" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Dar Cairo is mixed: UNITLESS x28, PERCENT x1</t>
         </is>
       </c>
-      <c r="G12" s="11" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>Used unit:PERCENT</t>
         </is>
       </c>
-      <c r="H12" s="11" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>Dar Cairo's unitless ones read as binary open/close. Its Speed_Command is PERCENT on all 88 and Damper_Position_Sensor PERCENT on all 74.</t>
         </is>
       </c>
-      <c r="I12" s="11" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+      <c r="I12" s="2" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="13" ht="58.05" customHeight="1">
-      <c r="A13" s="11" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>QNL-018</t>
         </is>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="C13" s="14" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>Class</t>
         </is>
       </c>
-      <c r="D13" s="11" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
       </c>
-      <c r="E13" s="11" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>4 CHW temperature point signatures</t>
         </is>
       </c>
-      <c r="F13" s="11" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>brick:Chilled_Water_Supply/Return_Temperature_Sensor are deprecated in Brick 1.4</t>
         </is>
       </c>
-      <c r="G13" s="11" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>Kept the deprecated Dar Cairo class; recorded the replacement in the ledger note</t>
         </is>
       </c>
-      <c r="H13" s="11" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>Client directed - the class is the established join key. Each raises an expected W-TYP-4 naming the entering/leaving replacement.</t>
         </is>
       </c>
-      <c r="I13" s="11" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
+      <c r="I13" s="2" t="n">
+        <v>64</v>
       </c>
     </row>
     <row r="14" ht="58.05" customHeight="1">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>QNL-019</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="C14" s="14" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
         <is>
           <t>Class</t>
         </is>
       </c>
-      <c r="D14" s="11" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
       </c>
-      <c r="E14" s="11" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>22 fan trip-alarm points</t>
         </is>
       </c>
-      <c r="F14" s="11" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>SSC types its own _TripAlm points as the bare brick:Alarm</t>
         </is>
       </c>
-      <c r="G14" s="11" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>Coined para:Trip_Alarm (subClassOf brick:Alarm), defined in row 3</t>
         </is>
       </c>
-      <c r="H14" s="11" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>brick:Alarm is reserved for a literal general/summary alarm; SSC's bare typing makes trips indistinguishable from every other alarm.</t>
         </is>
       </c>
-      <c r="I14" s="11" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+      <c r="I14" s="2" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="15" ht="58.05" customHeight="1">
-      <c r="A15" s="11" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>QNL-021</t>
         </is>
       </c>
-      <c r="B15" s="11" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="C15" s="15" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="D15" s="11" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Equipment</t>
         </is>
       </c>
-      <c r="E15" s="11" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>entity:QNL_CAV_1F_S15_001, entity:QNL_VAV_B_S13_005</t>
         </is>
       </c>
-      <c r="F15" s="11" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>Named in the Selected points sheet but absent from the asset register - no room, no Fed By</t>
         </is>
       </c>
-      <c r="G15" s="11" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>Modelled both units and their 6 points WITHOUT rec:locatedIn, rec:feeds or rec:isFedBy</t>
         </is>
       </c>
-      <c r="H15" s="11" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>Rule 1: model the asset and its datapoints, assert nothing about position. Inventing a location would read as surveyed fact. Raises 2 E-FEED-1 and 2 W-GR-2, accepted here.</t>
         </is>
       </c>
-      <c r="I15" s="11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="I15" s="2" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="16" ht="58.05" customHeight="1">
-      <c r="A16" s="11" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>QNL-022</t>
         </is>
       </c>
-      <c r="B16" s="11" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="C16" s="16" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>Scope</t>
         </is>
       </c>
-      <c r="D16" s="11" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Points</t>
         </is>
       </c>
-      <c r="E16" s="11" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>entity:QNL_VAV_1F_S15_039S</t>
         </is>
       </c>
-      <c r="F16" s="11" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>In the asset register and the historian, but the Selected sheet lists no points for it</t>
         </is>
       </c>
-      <c r="G16" s="11" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>Added the 3 points its 245 siblings carry, taken from the historian</t>
         </is>
       </c>
-      <c r="H16" s="11" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>Rule 1: points exist in the historian, so they are modelled. The family's own selected signature decides which, so the unit matches its siblings. Its other 5 historian points are not selected on any sibling either.</t>
         </is>
       </c>
-      <c r="I16" s="11" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="I16" s="2" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="17" ht="58.05" customHeight="1">
-      <c r="A17" s="11" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>QNL-023</t>
         </is>
       </c>
-      <c r="B17" s="11" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="C17" s="17" t="inlineStr">
+      <c r="C17" s="9" t="inlineStr">
         <is>
           <t>Structure</t>
         </is>
       </c>
-      <c r="D17" s="11" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Metadata</t>
         </is>
       </c>
-      <c r="E17" s="11" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>12 equipment families (AHU, FCU, DX, HEX, pumps, CCU, EF, generator, pressurisation, climate)</t>
         </is>
       </c>
-      <c r="F17" s="11" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Manufacturer datasheets give properties per component (cooling coil, fans, motors, outdoor unit)</t>
         </is>
       </c>
-      <c r="G17" s="11" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>Added the 16 metadata predicates in the Dar Cairo/SSC/HQ row shapes: literals as props, quantities as &lt;blanknode&gt; value+unit; component properties on brick:hasPart sub-entities (CHW-Coil, SF, RF, Motor, OD) - all Brick 1.4 classes, no para: minted</t>
         </is>
       </c>
-      <c r="H17" s="11" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>The three reference models attach component metadata to sub-entities and write quantities as blanknodes</t>
         </is>
       </c>
-      <c r="I17" s="11" t="n">
+      <c r="I17" s="2" t="n">
         <v>977</v>
       </c>
     </row>
     <row r="18" ht="58.05" customHeight="1">
-      <c r="A18" s="11" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>QNL-024</t>
         </is>
       </c>
-      <c r="B18" s="11" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="C18" s="13" t="inlineStr">
+      <c r="C18" s="7" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
       </c>
-      <c r="D18" s="11" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Metadata</t>
         </is>
       </c>
-      <c r="E18" s="11" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>All quantity metadata rows</t>
         </is>
       </c>
-      <c r="F18" s="11" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>QF HQ v0.4 carries several wrong brick:hasUnit (air flow as unit:V, cooling capacity as unit:HZ)</t>
         </is>
       </c>
-      <c r="G18" s="11" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>Took brick:value and brick:hasUnit from the workbook's 'Value (Dar Cairo)' / 'Unit (QUDT)' columns, never HQ's</t>
         </is>
       </c>
-      <c r="H18" s="11" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>Dar Cairo is the unit authority; HQ's own README documents its units as wrong</t>
         </is>
       </c>
-      <c r="I18" s="11" t="n">
+      <c r="I18" s="2" t="n">
         <v>882</v>
       </c>
     </row>
     <row r="19" ht="58.05" customHeight="1">
-      <c r="A19" s="11" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>QNL-025</t>
         </is>
       </c>
-      <c r="B19" s="11" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="C19" s="18" t="inlineStr">
+      <c r="C19" s="10" t="inlineStr">
         <is>
           <t>Identifier</t>
         </is>
       </c>
-      <c r="D19" s="11" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Metadata</t>
         </is>
       </c>
-      <c r="E19" s="11" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>Heat exchangers, pumps, generator</t>
         </is>
       </c>
-      <c r="F19" s="11" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>Datasheets tag them PHX/B/01-05, CHWP/B/01-04, 'GENERATOR SET'; the ontology has HEX01-05, CHW_P01-04, ELEC_Gen</t>
         </is>
       </c>
-      <c r="G19" s="11" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>Joined HEX by index (PHX/B/0n -&gt; HEX0n, user-confirmed), pumps CHWP/B/0n -&gt; CHW_P0n, generator -&gt; ELEC_Gen</t>
         </is>
       </c>
-      <c r="H19" s="11" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>Prefixes differ but the units correspond 1:1 by number/position</t>
         </is>
       </c>
-      <c r="I19" s="11" t="n">
+      <c r="I19" s="2" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="20" ht="58.05" customHeight="1">
-      <c r="A20" s="11" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>QNL-026</t>
         </is>
       </c>
-      <c r="B20" s="11" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="C20" s="16" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>Scope</t>
         </is>
       </c>
-      <c r="D20" s="11" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Metadata</t>
         </is>
       </c>
-      <c r="E20" s="11" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>FCU family - 94 of 137 units</t>
         </is>
       </c>
-      <c r="F20" s="11" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>FCU datasheets are 28 Euroclima selection sheets keyed by position (B/03,04; 1F/04-54), one model per group</t>
         </is>
       </c>
-      <c r="G20" s="11" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>Expanded each selection-sheet tag to the FCUs it names and wrote its model/capacity/flow/power to every unit in the group</t>
         </is>
       </c>
-      <c r="H20" s="11" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>The selection sheet groups identical units under one model; the group tag names them explicitly</t>
         </is>
       </c>
-      <c r="I20" s="11" t="n">
+      <c r="I20" s="2" t="n">
         <v>94</v>
       </c>
     </row>
     <row r="21" ht="58.05" customHeight="1">
-      <c r="A21" s="11" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>QNL-027</t>
         </is>
       </c>
-      <c r="B21" s="11" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="C21" s="16" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>Scope</t>
         </is>
       </c>
-      <c r="D21" s="11" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Metadata</t>
         </is>
       </c>
-      <c r="E21" s="11" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>FCU 2F 06-33; closed control units; climate &amp; pressurisation units; out-of-range CAV/VAV/EF</t>
         </is>
       </c>
-      <c r="F21" s="11" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>Their datasheet tags do not correspond to any ontology entity (2F numbers 06-33 vs 034-062; CC/B vs CCU_808n; no MCG/PU entity; units absent from the register)</t>
         </is>
       </c>
-      <c r="G21" s="11" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>Left them without metadata and reported every tag in QNL_metadata_join_report.csv; did not guess a join</t>
         </is>
       </c>
-      <c r="H21" s="11" t="inlineStr">
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>User confirmed FCU 2F 06-33 are different units, not a numbering offset; the rest have no matching entity - do not assume metadata a source cannot place</t>
         </is>
       </c>
-      <c r="I21" s="11" t="n">
+      <c r="I21" s="2" t="n">
         <v>94</v>
       </c>
     </row>
     <row r="22" ht="58.05" customHeight="1">
-      <c r="A22" s="11" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>QNL-028</t>
         </is>
       </c>
-      <c r="B22" s="11" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="C22" s="18" t="inlineStr">
+      <c r="C22" s="10" t="inlineStr">
         <is>
           <t>Identifier</t>
         </is>
       </c>
-      <c r="D22" s="11" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>All layers</t>
         </is>
       </c>
-      <c r="E22" s="11" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>Every subject/object identifier</t>
         </is>
       </c>
-      <c r="F22" s="11" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Points were named as BMS tokens (AvgSpcHumd_PV, RunSts); equipment/rooms used '_' between word-parts</t>
         </is>
       </c>
-      <c r="G22" s="11" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>Aligned to Dar Cairo: datapoints renamed to dashed English from label or class (Return-Temperature, Run-Status); equipment/part tags kept their industry codes (AHU, SF, CHW-Coil) with '_'-&gt;'-' within the tag; 277 room name-words dashed. ref:hasTimeseriesId/para:hasEntityId untouched; crosswalk written</t>
         </is>
       </c>
-      <c r="H22" s="11" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>Client asked to match Dar Cairo's naming convention; camelCase 71%-&gt;0%, join keys preserved via the crosswalk</t>
         </is>
       </c>
-      <c r="I22" s="11" t="n">
+      <c r="I22" s="2" t="n">
         <v>3753</v>
       </c>
     </row>
     <row r="23" ht="58.05" customHeight="1">
-      <c r="A23" s="11" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>QNL-029</t>
         </is>
       </c>
-      <c r="B23" s="11" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="C23" s="17" t="inlineStr">
+      <c r="C23" s="9" t="inlineStr">
         <is>
           <t>Structure</t>
         </is>
       </c>
-      <c r="D23" s="11" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Metadata</t>
         </is>
       </c>
-      <c r="E23" s="11" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>FCU/AHU/HEX control valves; FCU 2F 034-062 and 1F 059-065</t>
         </is>
       </c>
-      <c r="F23" s="11" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>The BAS valve schedule (BAS_QNL_Assets.pdf) gives each unit's CHW control-valve model, FCU actuator model and design flow</t>
         </is>
       </c>
-      <c r="G23" s="11" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>Added a brick:Cooling_Valve part to every FCU/AHU/HEX with rec:modelNumber (FCU valves+actuators Honeywell; AHU/HEX valves ITQ, make not stated); FCU actuator as a para:Valve_Actuator sub-part; gap-filled para:ratedChilledWaterFlowrate on the 43 FCUs that had none (all of 2F 034-062, 1F 059-065)</t>
         </is>
       </c>
-      <c r="H23" s="11" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>The BAS is a valid as-built source; brick:Cooling_Valve is Dar Cairo's CHW-valve class (76 uses); para:Valve_Actuator minted (no Brick/Dar Cairo/SSC class for a valve actuator)</t>
         </is>
       </c>
-      <c r="I23" s="11" t="n">
+      <c r="I23" s="2" t="n">
         <v>334</v>
       </c>
     </row>
     <row r="24" ht="58.05" customHeight="1">
-      <c r="A24" s="11" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>QNL-030</t>
         </is>
       </c>
-      <c r="B24" s="11" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="C24" s="13" t="inlineStr">
+      <c r="C24" s="7" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
       </c>
-      <c r="D24" s="11" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Metadata</t>
         </is>
       </c>
-      <c r="E24" s="11" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>FCU 1F-002, 1F-003, 2F-005 chilled-water flow</t>
         </is>
       </c>
-      <c r="F24" s="11" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>The BAS valve schedule gives 0.36 L/s where the Euroclima selection sheet gave 0.27 L/s</t>
         </is>
       </c>
-      <c r="G24" s="11" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>Kept the Euroclima value; did not overwrite. Flagged for the supplier. The other 91 of 94 shared FCUs agree within +/-0.02 L/s, verifying the metadata</t>
         </is>
       </c>
-      <c r="H24" s="11" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>Two sources, minor disagreement on 3 units; the Euroclima selection sheet is the equipment nameplate, the BAS the valve sizing - a supplier question, not ours to resolve</t>
         </is>
       </c>
-      <c r="I24" s="11" t="n">
+      <c r="I24" s="2" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="25" ht="58.05" customHeight="1">
-      <c r="A25" s="11" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>QNL-031</t>
         </is>
       </c>
-      <c r="B25" s="11" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="C25" s="17" t="inlineStr">
+      <c r="C25" s="9" t="inlineStr">
         <is>
           <t>Structure</t>
         </is>
       </c>
-      <c r="D25" s="11" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Metering</t>
         </is>
       </c>
-      <c r="E25" s="11" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>virtual metering layer, 1,460 meters</t>
         </is>
       </c>
-      <c r="F25" s="11" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>No metering layer existed. A hand-built workbook (VirtualMeters_QNL_manual_v1.xlsm) proposed one from a 9-class x 3-tier matrix.</t>
         </is>
       </c>
-      <c r="G25" s="11" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>Regenerated the layer from that tier matrix against the live ontology rather than importing the workbook, and archived the workbook under projects/QNL/sources/.</t>
         </is>
       </c>
-      <c r="H25" s="11" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>None of the workbook's 353 room identifiers matched the live sheet - it was built before align_naming ran. Regenerating makes the identifiers agree by construction instead of by remap.</t>
         </is>
       </c>
-      <c r="I25" s="11" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>8,760</t>
         </is>
       </c>
     </row>
     <row r="26" ht="58.05" customHeight="1">
-      <c r="A26" s="11" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>QNL-032</t>
         </is>
       </c>
-      <c r="B26" s="11" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="C26" s="18" t="inlineStr">
+      <c r="C26" s="10" t="inlineStr">
         <is>
           <t>Identifier</t>
         </is>
       </c>
-      <c r="D26" s="11" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Metering</t>
         </is>
       </c>
-      <c r="E26" s="11" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>353 room-tier meters</t>
         </is>
       </c>
-      <c r="F26" s="11" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Workbook rooms read QNL_B_001A_BREAK-OUT-AREA; the ontology reads QNL_B-001A_Break-Out-Area.</t>
         </is>
       </c>
-      <c r="G26" s="11" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>Used the ontology form. Zero identifiers changed in the ontology.</t>
         </is>
       </c>
-      <c r="H26" s="11" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>A fuzzy key (case, separators, leading zeros) matched 353 of 353, so the two name the same rooms; the ontology form is the one the rest of the sheet and the crosswalk already use.</t>
         </is>
       </c>
-      <c r="I26" s="11" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
     </row>
     <row r="27" ht="58.05" customHeight="1">
-      <c r="A27" s="11" t="inlineStr">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>QNL-033</t>
         </is>
       </c>
-      <c r="B27" s="11" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="C27" s="16" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>Scope</t>
         </is>
       </c>
-      <c r="D27" s="11" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Metering</t>
         </is>
       </c>
-      <c r="E27" s="11" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>entity:QNL_L1-145_ILL-Director</t>
         </is>
       </c>
-      <c r="F27" s="11" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>The workbook metered 353 rooms; the ontology has 354.</t>
         </is>
       </c>
-      <c r="G27" s="11" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>Gave it the same four room-tier meters as its siblings.</t>
         </is>
       </c>
-      <c r="H27" s="11" t="inlineStr">
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>The room was added by the room-retarget pass (QNL_room_retarget_changes.csv, "new room") after the workbook was built. Note the open question from that pass: if 144 and 145 are one room, 144 should be retired and its meters with it.</t>
         </is>
       </c>
-      <c r="I27" s="11" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
+      <c r="I27" s="2" t="n">
+        <v>32</v>
       </c>
     </row>
     <row r="28" ht="58.05" customHeight="1">
-      <c r="A28" s="11" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>QNL-034</t>
         </is>
       </c>
-      <c r="B28" s="11" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="C28" s="13" t="inlineStr">
+      <c r="C28" s="7" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
       </c>
-      <c r="D28" s="11" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Metering</t>
         </is>
       </c>
-      <c r="E28" s="11" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>732 thermal meter points</t>
         </is>
       </c>
-      <c r="F28" s="11" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>The workbook gave CHW and HW thermal points unit:KiloW and unit:KiloW-HR, the same tokens as the electrical meters. Dar Cairo splits: brick:Thermal_Power_Meter uses para:KiloWt/para:KiloWt-HR, its own para:CHW_Meter is 70 rows kW against 2 kWt.</t>
         </is>
       </c>
-      <c r="G28" s="11" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>Used para:KiloWt and para:KiloWt-HR, and declared both as qudt:Unit rows.</t>
         </is>
       </c>
-      <c r="H28" s="11" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>Client decision. Thermal kW written as unit:KiloW is indistinguishable from electrical kW, so any building rollup that sums demand double-counts. Diverges from the 7 pre-existing QNL thermal rows on unit:KiloW - those are left alone and listed for a later pass.</t>
         </is>
       </c>
-      <c r="I28" s="11" t="inlineStr">
-        <is>
-          <t>732</t>
-        </is>
+      <c r="I28" s="2" t="n">
+        <v>732</v>
       </c>
     </row>
     <row r="29" ht="58.05" customHeight="1">
-      <c r="A29" s="11" t="inlineStr">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>QNL-035</t>
         </is>
       </c>
-      <c r="B29" s="11" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="C29" s="17" t="inlineStr">
+      <c r="C29" s="9" t="inlineStr">
         <is>
           <t>Structure</t>
         </is>
       </c>
-      <c r="D29" s="11" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Metering</t>
         </is>
       </c>
-      <c r="E29" s="11" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>2,920 meter points</t>
         </is>
       </c>
-      <c r="F29" s="11" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>Dar Cairo populates every virtual-meter point with a ref:TimeseriesReference. The QNL historian (QNL_Historian_IO_list_CP2.xlsx) carries no calculated tags at all - zero *_CALC, zero ContributionFraction.</t>
         </is>
       </c>
-      <c r="G29" s="11" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>Wrote the points with no reference row, and listed all 2,920 in QNL_virtual_meter_timeseries_pending.csv with the Dar Cairo tsid proposed and entityId blank.</t>
         </is>
       </c>
-      <c r="H29" s="11" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>The workbook wrote 2,912 reference rows with both keys blank. A half-filled blank node looks finished and reads as a working telemetry link; an absent one is visible as W-PT-1 and tracked in a file.</t>
         </is>
       </c>
-      <c r="I29" s="11" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>2,920 (W-PT-1)</t>
         </is>
       </c>
     </row>
     <row r="30" ht="58.05" customHeight="1">
-      <c r="A30" s="11" t="inlineStr">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>QNL-036</t>
         </is>
       </c>
-      <c r="B30" s="11" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="C30" s="17" t="inlineStr">
+      <c r="C30" s="9" t="inlineStr">
         <is>
           <t>Structure</t>
         </is>
       </c>
-      <c r="D30" s="11" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Metering</t>
         </is>
       </c>
-      <c r="E30" s="11" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>297 AHU-fed terminal units</t>
         </is>
       </c>
-      <c r="F30" s="11" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Client asked for para:contributionFraction on every unit fed by an AHU, skipping units in shafts or risers.</t>
         </is>
       </c>
-      <c r="G30" s="11" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>Added it to all 297 (246 VAV + 51 CAV) with tsid ContributionFraction and the entityId each unit's existing points already carry.</t>
         </is>
       </c>
-      <c r="H30" s="11" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>The shaft rule matched nothing: QNL's shaft-dwelling assets are 62 FCUs and 2 exhaust fans, and no AHU feeds any of them. The rule is implemented for the next building. entity:QNL_CAV-B-S13-050 carries no points, so its entityId was derived - the derivation matches all 296 units that do have one.</t>
         </is>
       </c>
-      <c r="I30" s="11" t="inlineStr">
-        <is>
-          <t>594</t>
-        </is>
+      <c r="I30" s="2" t="n">
+        <v>594</v>
       </c>
     </row>
     <row r="31" ht="58.05" customHeight="1">
-      <c r="A31" s="11" t="inlineStr">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>QNL-037</t>
         </is>
       </c>
-      <c r="B31" s="11" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="C31" s="14" t="inlineStr">
+      <c r="C31" s="8" t="inlineStr">
         <is>
           <t>Class</t>
         </is>
       </c>
-      <c r="D31" s="11" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Metering</t>
         </is>
       </c>
-      <c r="E31" s="11" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>entity:QNL_Utility-Virtual-Meter vs entity:QNL_Total-Energy</t>
         </is>
       </c>
-      <c r="F31" s="11" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>QNL already carries entity:QNL_Total-Energy typed para:Utility_Meter, with a real historian tag QNL_TotalEnergy.Energy. The tier matrix asks for a building-tier Utility_Meter as well.</t>
         </is>
       </c>
-      <c r="G31" s="11" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t>Suppressed the virtual one. A virtual meter only fills a gap where no physical meter exists, and Total-Energy is the physical utility meter.</t>
         </is>
       </c>
-      <c r="H31" s="11" t="inlineStr">
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>Client rule, confirmed 2026-09-03: virtual meters are created only for actual meters that do not exist. The generator now carries an ALREADY_METERED list, each entry naming the physical meter that justifies the suppression.</t>
         </is>
       </c>
-      <c r="I31" s="11" t="inlineStr">
+      <c r="I31" s="2" t="inlineStr">
         <is>
           <t>0 (6 not written)</t>
         </is>
       </c>
     </row>
     <row r="32" ht="58.05" customHeight="1">
-      <c r="A32" s="11" t="inlineStr">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>QNL-038</t>
         </is>
       </c>
-      <c r="B32" s="11" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="C32" s="19" t="inlineStr">
+      <c r="C32" s="4" t="inlineStr">
         <is>
           <t>Source defect</t>
         </is>
       </c>
-      <c r="D32" s="11" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Metering</t>
         </is>
       </c>
-      <c r="E32" s="11" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>brick:Electrical_Meter family</t>
         </is>
       </c>
-      <c r="F32" s="11" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>14 pre-existing physical meters (MFM, VCB) share brick:Electrical_Meter with the 360 new virtual ones, so check_consistency compares them as one family.</t>
         </is>
       </c>
-      <c r="G32" s="11" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>Left the class as-is; 25 E-CON errors are accepted and named here.</t>
         </is>
       </c>
-      <c r="H32" s="11" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>Dar Cairo does the same - brick:Electrical_Meter covers both its physical and virtual meters. Splitting the virtual ones under a para: subclass would depart from the primary reference to quiet a checker.</t>
         </is>
       </c>
-      <c r="I32" s="11" t="inlineStr">
+      <c r="I32" s="2" t="inlineStr">
         <is>
           <t>25 (E-CON-1/2)</t>
         </is>
       </c>
     </row>
     <row r="33" ht="58.05" customHeight="1">
-      <c r="A33" s="11" t="inlineStr">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>QNL-039</t>
         </is>
       </c>
-      <c r="B33" s="11" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="C33" s="19" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>Source defect</t>
         </is>
       </c>
-      <c r="D33" s="11" t="inlineStr">
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Metering</t>
         </is>
       </c>
-      <c r="E33" s="11" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>all 16 pre-existing physical meters</t>
         </is>
       </c>
-      <c r="F33" s="11" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>None carries a brick:meters row. Each is brick:isPartOf entity:Electrical_System with points, and nothing says what it measures.</t>
         </is>
       </c>
-      <c r="G33" s="11" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>Left them as they are; recorded the gap and hand-listed the one suppression it blocked.</t>
         </is>
       </c>
-      <c r="H33" s="11" t="inlineStr">
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>The "virtual only where physical does not exist" rule cannot be evaluated from the graph while this holds - it needs a human to say what each meter covers. Adding the brick:meters rows is the durable fix and is proposed in the handover.</t>
         </is>
       </c>
-      <c r="I33" s="11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="I33" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34" ht="58.05" customHeight="1">
-      <c r="A34" s="11" t="inlineStr">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>QNL-040</t>
         </is>
       </c>
-      <c r="B34" s="11" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="C34" s="16" t="inlineStr">
+      <c r="C34" s="5" t="inlineStr">
         <is>
           <t>Scope</t>
         </is>
       </c>
-      <c r="D34" s="11" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Metering</t>
         </is>
       </c>
-      <c r="E34" s="11" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>entity:QNL_CHWS-MAIN-LOOP_Energy-Meter vs the building-tier para:CHW_Meter</t>
         </is>
       </c>
-      <c r="F34" s="11" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>QNL carries a brick:Building_Chilled_Water_Meter on the main CHW loop with 7 live points, among them CHW-Consumption-KW and CHW-CHW-Energy-PV.</t>
         </is>
       </c>
-      <c r="G34" s="11" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>Kept entity:QNL_CHW-Power-Thermal-Virtual-Meter for now and raised the overlap.</t>
         </is>
       </c>
-      <c r="H34" s="11" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>OPEN. By the same rule that removed the Utility virtual meter, this pair looks like a duplicate - the loop meter measures the building's chilled water. Different classes, so no checker will catch it. Needs confirmation that the loop meter covers the whole building.</t>
         </is>
       </c>
-      <c r="I34" s="11" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="I34" s="2" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="35" ht="58.05" customHeight="1">
-      <c r="A35" s="11" t="inlineStr">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>QNL-041</t>
         </is>
       </c>
-      <c r="B35" s="11" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="C35" s="19" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>Source defect</t>
         </is>
       </c>
-      <c r="D35" s="11" t="inlineStr">
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Metadata</t>
         </is>
       </c>
-      <c r="E35" s="11" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>VAV 1F-S15-006 to 009 and B-S15-001 to 004</t>
         </is>
       </c>
-      <c r="F35" s="11" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Two MEP drawings schedule the same boxes and disagree on air flow. 1F: 290 l/s on the S11/S15 drawing against 220 l/s on the second 1F drawing. Basement: 261 l/s on the heating-capacity drawing against 251 l/s on the model-and-make drawing. QNL_Full_Metadata.xlsx recorded both and its Open Items sheet marks each "Unresolved".</t>
         </is>
       </c>
-      <c r="G35" s="11" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr">
         <is>
           <t>Kept 290 l/s and 251 l/s; dropped the other eight rows.</t>
         </is>
       </c>
-      <c r="H35" s="11" t="inlineStr">
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>Client decision 2026-09-03, on one rule: where two drawings of the same schedule disagree, keep the one that names the box model, since the flow has to match the box selected. 290 comes with model NBOQOB250 and makes boxes 005-009 one consistent run; 251 comes with model NBOQE03. Title blocks are cropped on every drawing image, so no revision date could settle it instead. Reversible - both values remain in QNL_Full_Metadata.xlsx.</t>
         </is>
       </c>
-      <c r="I35" s="11" t="inlineStr">
+      <c r="I35" s="2" t="inlineStr">
         <is>
           <t>8 dropped</t>
         </is>
       </c>
     </row>
     <row r="36" ht="58.05" customHeight="1">
-      <c r="A36" s="11" t="inlineStr">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>QNL-042</t>
         </is>
       </c>
-      <c r="B36" s="11" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="C36" s="19" t="inlineStr">
+      <c r="C36" s="4" t="inlineStr">
         <is>
           <t>Source defect</t>
         </is>
       </c>
-      <c r="D36" s="11" t="inlineStr">
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>References</t>
         </is>
       </c>
-      <c r="E36" s="11" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>all 564 ref:IFCReference rows</t>
         </is>
       </c>
-      <c r="F36" s="11" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Every row declares para:IFC_ID with a blank value; ref:ifcName carries the entity identifier. No reference model carries a real IFC GUID either - across Dar Cairo, SSC, HQ and QNL, none of 2,133 values matches the 22-character IfcGloballyUniqueId shape.</t>
         </is>
       </c>
-      <c r="G36" s="11" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>Filled all 564 para:IFC_ID cells with the entity identifier, the same string ref:ifcName already carried. QF SSC's shape.</t>
         </is>
       </c>
-      <c r="H36" s="11" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>Client decision 2026-09-03. SSC writes the identifier into both columns on all 165 of its IFC rows; QNL was already built to that shape but left IFC_ID empty. Note that no delivered model carries a real IFC GUID - across Dar Cairo, SSC, HQ and QNL none of 2,133 values matches the 22-character IfcGloballyUniqueId shape - so para:IFC_ID holds the asset tag, not the BIM GUID that CLAUDE.md describes. If real GUIDs are exported later they overwrite these in one pass.</t>
         </is>
       </c>
-      <c r="I36" s="11" t="inlineStr">
+      <c r="I36" s="2" t="inlineStr">
         <is>
           <t>564 (574 errors -&gt; 10)</t>
         </is>
       </c>
     </row>
     <row r="37" ht="58.05" customHeight="1">
-      <c r="A37" s="11" t="inlineStr">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>QNL-043</t>
         </is>
       </c>
-      <c r="B37" s="11" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="C37" s="15" t="inlineStr">
+      <c r="C37" s="3" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="D37" s="11" t="inlineStr">
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Equipment</t>
         </is>
       </c>
-      <c r="E37" s="11" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>26 standalone assets with no room</t>
         </is>
       </c>
-      <c r="F37" s="11" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>The asset register gives no room for 6 CRACs, 2 DX units, 1 CAV, 1 VAV, 1 booster pump and 15 electrical meters. Earlier practice was to write no rec:locatedIn at all rather than invent one.</t>
         </is>
       </c>
-      <c r="G37" s="11" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr">
         <is>
           <t>Wrote rec:locatedIn entity:QNL (rec:Building) on all 26. Every one already carried brick:isPartOf its system, so no system row was needed.</t>
         </is>
       </c>
-      <c r="H37" s="11" t="inlineStr">
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>PROJECT ASSUMPTION FOR QNL ONLY - not a house rule, and deliberately not written into the skill. An asset with no room is still certainly in the building and certainly on its system, so both are asserted rather than nothing. rec:feeds is still not written - the served space is the part nobody knows. Dar Cairo has precedent, locating 36 entities at a rec:Building. Excludes the 174 parts that also lack a location (137 CHW valves, 22 fans, 10 HEX valves, 2 breakers, 2 pumps): a part inherits its parent's location and Dar Cairo locates only 19 of its 801 parts separately. Clears 26 W-GR-2; the 10 E-FEED-1 stand.</t>
         </is>
       </c>
-      <c r="I37" s="11" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
+      <c r="I37" s="2" t="n">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:I37"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3207,84 +3096,83 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8.21875" customWidth="1" min="1" max="1"/>
     <col width="10.33203125" customWidth="1" min="2" max="2"/>
     <col width="12.21875" customWidth="1" min="3" max="3"/>
     <col width="9.6640625" customWidth="1" min="4" max="4"/>
     <col width="32.77734375" customWidth="1" min="5" max="5"/>
-    <col width="46" customWidth="1" min="6" max="7"/>
+    <col width="46" customWidth="1" min="6" max="6"/>
     <col width="45" customWidth="1" min="7" max="7"/>
     <col width="52" customWidth="1" min="8" max="8"/>
     <col width="12.88671875" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="C1" s="9" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D1" s="9" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Layer</t>
         </is>
       </c>
-      <c r="E1" s="9" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Entity / Scope</t>
         </is>
       </c>
-      <c r="F1" s="9" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>What the source says</t>
         </is>
       </c>
-      <c r="G1" s="9" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>What we did</t>
         </is>
       </c>
-      <c r="H1" s="9" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Why / basis</t>
         </is>
       </c>
-      <c r="I1" s="9" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Rows affected</t>
         </is>
       </c>
     </row>
     <row r="2" ht="58.05" customHeight="1">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="11" t="inlineStr">
         <is>
           <t>(no entries yet)</t>
         </is>
       </c>
-      <c r="B2" s="11" t="n"/>
-      <c r="C2" s="11" t="n"/>
-      <c r="D2" s="11" t="n"/>
-      <c r="E2" s="11" t="n"/>
-      <c r="F2" s="11" t="n"/>
-      <c r="G2" s="11" t="n"/>
-      <c r="H2" s="11" t="n"/>
-      <c r="I2" s="11" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:I2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/projects/Assumption_Log.xlsx
+++ b/projects/Assumption_Log.xlsx
@@ -760,7 +760,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="8.21875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -2473,27 +2473,74 @@
       </c>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t>26 standalone assets with no room</t>
+          <t>27 standalone assets with no room</t>
         </is>
       </c>
       <c r="F37" s="11" t="inlineStr">
         <is>
-          <t>The asset register gives no room for 6 CRACs, 2 DX units, 1 CAV, 1 VAV, 1 booster pump and 15 electrical meters. Earlier practice was to write no rec:locatedIn at all rather than invent one.</t>
+          <t>The asset register gives no room for 6 CRACs, 2 DX units, 1 CAV, 1 VAV, 1 booster pump, 15 electrical meters and the CHW loop energy meter. Earlier practice was to write no rec:locatedIn at all rather than invent one.</t>
         </is>
       </c>
       <c r="G37" s="11" t="inlineStr">
         <is>
-          <t>Wrote rec:locatedIn entity:QNL (rec:Building) on all 26. Every one already carried brick:isPartOf its system, so no system row was needed.</t>
+          <t>Wrote rec:locatedIn at the most specific level the evidence supports: the FLOOR where the floor is identifiable, the BUILDING where it is not. 4 resolved to a floor, 23 to the building. Every one already carried brick:isPartOf its system, so no system row was needed.</t>
         </is>
       </c>
       <c r="H37" s="11" t="inlineStr">
         <is>
-          <t>PROJECT ASSUMPTION FOR QNL ONLY - not a house rule, and deliberately not written into the skill. An asset with no room is still certainly in the building and certainly on its system, so both are asserted rather than nothing. rec:feeds is still not written - the served space is the part nobody knows. Dar Cairo has precedent, locating 36 entities at a rec:Building. Excludes the 174 parts that also lack a location (137 CHW valves, 22 fans, 10 HEX valves, 2 breakers, 2 pumps): a part inherits its parent's location and Dar Cairo locates only 19 of its 801 parts separately. Clears 26 W-GR-2; the 10 E-FEED-1 stand.</t>
+          <t>PROJECT ASSUMPTION FOR QNL ONLY - not a house rule, and deliberately not written into the skill. Assert the most specific containment that is actually known: an asset whose floor is identifiable goes on that floor, one whose floor is not goes on the building. rec:feeds is still not written - the served space is the part nobody knows. Dar Cairo has precedent for building-level location (36 entities). Excludes the 173 parts that also lack a location (137 CHW valves, 22 fans, 10 HEX valves, 2 breakers, 2 pumps), each of whose parent is already located in a named room: a part inherits its parent's location, and writing the building on it would replace a precise inherited location with a vaguer asserted one. CHWS-MAIN-LOOP_Energy-Meter is the one part that was located, because its parent loop is itself at the building. Clears 27 W-GR-2; the 10 E-FEED-1 stand.</t>
         </is>
       </c>
       <c r="I37" s="11" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="11" t="inlineStr">
+        <is>
+          <t>QNL-044</t>
+        </is>
+      </c>
+      <c r="B38" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C38" s="13" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="D38" s="11" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="E38" s="11" t="inlineStr">
+        <is>
+          <t>4 assets retargeted from the building to a floor</t>
+        </is>
+      </c>
+      <c r="F38" s="11" t="inlineStr">
+        <is>
+          <t>No room in the register, but a floor is identifiable from other evidence.</t>
+        </is>
+      </c>
+      <c r="G38" s="11" t="inlineStr">
+        <is>
+          <t>entity:QNL_CAV-1F-S15-001 -&gt; entity:QNL_L1; entity:QNL_VAV-B-S13-005 -&gt; entity:QNL_B; entity:QNL_DX-RP21 -&gt; entity:QNL_P; entity:QNL_CHWPU-P02 -&gt; entity:QNL_B.</t>
+        </is>
+      </c>
+      <c r="H38" s="11" t="inlineStr">
+        <is>
+          <t>Evidence per asset. CAV-1F-S15-001: the 1F tag token, which resolves to Level 1 on 134 of the 135 located assets that carry it. VAV-B-S13-005: the B token, 202 of 202. DX-RP21: QNL_Full_Metadata.xlsx states Level "Roof level" and room served "PLC 8 / IDF ROOF PLANT"; entity:QNL_P is labelled "Roof Plant". CHWPU-P02 is the weakest of the four and is INFERRED, not sourced: its pair CHWPU-P01 is in entity:QNL_B-220_Plant-Room-04, and a duty/standby pump pair shares a plant room. Confirm on site.</t>
+        </is>
+      </c>
+      <c r="I38" s="11" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
     </row>

--- a/projects/Assumption_Log.xlsx
+++ b/projects/Assumption_Log.xlsx
@@ -2520,7 +2520,7 @@
       </c>
       <c r="E38" s="11" t="inlineStr">
         <is>
-          <t>4 assets retargeted from the building to a floor</t>
+          <t>3 assets retargeted from the building to a floor</t>
         </is>
       </c>
       <c r="F38" s="11" t="inlineStr">
@@ -2530,17 +2530,17 @@
       </c>
       <c r="G38" s="11" t="inlineStr">
         <is>
-          <t>entity:QNL_CAV-1F-S15-001 -&gt; entity:QNL_L1; entity:QNL_VAV-B-S13-005 -&gt; entity:QNL_B; entity:QNL_DX-RP21 -&gt; entity:QNL_P; entity:QNL_CHWPU-P02 -&gt; entity:QNL_B.</t>
+          <t>entity:QNL_CAV-1F-S15-001 -&gt; entity:QNL_L1; entity:QNL_VAV-B-S13-005 -&gt; entity:QNL_B; entity:QNL_DX-RP21 -&gt; entity:QNL_P. entity:QNL_CHWPU-P02 was considered and deliberately LEFT at the building.</t>
         </is>
       </c>
       <c r="H38" s="11" t="inlineStr">
         <is>
-          <t>Evidence per asset. CAV-1F-S15-001: the 1F tag token, which resolves to Level 1 on 134 of the 135 located assets that carry it. VAV-B-S13-005: the B token, 202 of 202. DX-RP21: QNL_Full_Metadata.xlsx states Level "Roof level" and room served "PLC 8 / IDF ROOF PLANT"; entity:QNL_P is labelled "Roof Plant". CHWPU-P02 is the weakest of the four and is INFERRED, not sourced: its pair CHWPU-P01 is in entity:QNL_B-220_Plant-Room-04, and a duty/standby pump pair shares a plant room. Confirm on site.</t>
+          <t>Evidence per asset, and only where a source states it. CAV-1F-S15-001: the 1F tag token, which resolves to Level 1 on 134 of the 135 located assets that carry it. VAV-B-S13-005: the B token, 202 of 202. DX-RP21: QNL_Full_Metadata.xlsx states Level "Roof level" and room served "PLC 8 / IDF ROOF PLANT"; entity:QNL_P is labelled "Roof Plant". CHWPU-P02 was NOT moved: the only basis was that its pair CHWPU-P01 sits in entity:QNL_B-220_Plant-Room-04, which is inference from a sibling rather than a source. Client decision 2026-09-03 - hold it at the building until the floor is confirmed on site.</t>
         </is>
       </c>
       <c r="I38" s="11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
     </row>

--- a/projects/Assumption_Log.xlsx
+++ b/projects/Assumption_Log.xlsx
@@ -760,7 +760,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="8.21875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -2191,27 +2191,27 @@
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>entity:QNL_Utility-Virtual-Meter vs entity:QNL_Total-Energy</t>
+          <t>entity:QNL_Utility-Virtual-Meter and entity:QNL_CHW-Power-Thermal-Virtual-Meter</t>
         </is>
       </c>
       <c r="F31" s="11" t="inlineStr">
         <is>
-          <t>QNL already carries entity:QNL_Total-Energy typed para:Utility_Meter, with a real historian tag QNL_TotalEnergy.Energy. The tier matrix asks for a building-tier Utility_Meter as well.</t>
+          <t>QNL already carries entity:QNL_Total-Energy (para:Utility_Meter, live historian tag QNL_TotalEnergy.Energy) and entity:QNL_CHWS-MAIN-LOOP_Energy-Meter (brick:Building_Chilled_Water_Meter, 7 live points). The tier matrix asks for a building-tier Utility Meter and CHW Meter as well.</t>
         </is>
       </c>
       <c r="G31" s="11" t="inlineStr">
         <is>
-          <t>Suppressed the virtual one. A virtual meter only fills a gap where no physical meter exists, and Total-Energy is the physical utility meter.</t>
+          <t>Kept both virtual meters. entity:QNL_Utility-Virtual-Meter was suppressed on 2026-09-03 and RESTORED the same day.</t>
         </is>
       </c>
       <c r="H31" s="11" t="inlineStr">
         <is>
-          <t>Client rule, confirmed 2026-09-03: virtual meters are created only for actual meters that do not exist. The generator now carries an ALREADY_METERED list, each entry naming the physical meter that justifies the suppression.</t>
+          <t>Client direction 2026-09-03, reversing an earlier decision in this same log: a physical meter does not duplicate a virtual one. The physical meter reads what is actually imported at one point in the plant; the virtual meter is a calculated roll-up over a space. The gap between them is losses and unmetered load, and seeing that gap is the point. The generator now REPORTS overlaps (PHYSICAL_OVERLAP) rather than skipping them. Restores the meter count to 1,460.</t>
         </is>
       </c>
       <c r="I31" s="11" t="inlineStr">
         <is>
-          <t>0 (6 not written)</t>
+          <t>6 restored</t>
         </is>
       </c>
     </row>
@@ -2541,6 +2541,53 @@
       <c r="I38" s="11" t="inlineStr">
         <is>
           <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="11" t="inlineStr">
+        <is>
+          <t>QNL-045</t>
+        </is>
+      </c>
+      <c r="B39" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C39" s="13" t="inlineStr">
+        <is>
+          <t>Source defect</t>
+        </is>
+      </c>
+      <c r="D39" s="11" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="E39" s="11" t="inlineStr">
+        <is>
+          <t>entity:QNL_TEF_B01, _B02, _B03</t>
+        </is>
+      </c>
+      <c r="F39" s="11" t="inlineStr">
+        <is>
+          <t>The BMS controls the basement toilet exhaust fans as three duty/standby SETS - QNL_TEF_B01, B02, B03 - each with 13 group-level points including ChOverSel and ChOverHrsSP (changeover select and hours), OccSchedule, FireAlm, EnableDisableCmd, RuntimeMtr, StartsCtr and TripCtr. The ontology models only the six individual fans TEF-B01A/B, B02A/B, B03A/B.</t>
+        </is>
+      </c>
+      <c r="G39" s="11" t="inlineStr">
+        <is>
+          <t>Recorded, not changed in this pass.</t>
+        </is>
+      </c>
+      <c r="H39" s="11" t="inlineStr">
+        <is>
+          <t>OPEN, and two separate problems. (1) The three set entities exist in the sheet as entity:QNL_TEF_B01, _B02 and _B03 typed para:Local_Status - a POINT class - sitting directly under entity:HVAC as if they were equipment, each carrying one timeseries (LocSts) and no brick:hasPoint owner. They are orphan points wearing an equipment shape. (2) Their other 36 group-level points are absent from the sheet entirely. (3) The A/B split contradicts the changeover logic: TEF-B01A feeds B-046 Rest Room Men and TEF-B01B feeds B-047 Rest Room Women, but a duty/standby pair alternates on ONE duty, so either both fans extract from both toilets or the ChOver points do not belong to this pair. Same for B02 (B-032/B-033) and B03 (B-146/B-147). Needs the BMS drawings to settle.</t>
+        </is>
+      </c>
+      <c r="I39" s="11" t="inlineStr">
+        <is>
+          <t>6 rows, 36 points missing</t>
         </is>
       </c>
     </row>

--- a/projects/Assumption_Log.xlsx
+++ b/projects/Assumption_Log.xlsx
@@ -2557,7 +2557,7 @@
       </c>
       <c r="C39" s="13" t="inlineStr">
         <is>
-          <t>Source defect</t>
+          <t>Structure</t>
         </is>
       </c>
       <c r="D39" s="11" t="inlineStr">
@@ -2572,22 +2572,22 @@
       </c>
       <c r="F39" s="11" t="inlineStr">
         <is>
-          <t>The BMS controls the basement toilet exhaust fans as three duty/standby SETS - QNL_TEF_B01, B02, B03 - each with 13 group-level points including ChOverSel and ChOverHrsSP (changeover select and hours), OccSchedule, FireAlm, EnableDisableCmd, RuntimeMtr, StartsCtr and TripCtr. The ontology models only the six individual fans TEF-B01A/B, B02A/B, B03A/B.</t>
+          <t>The BMS controls the basement toilet exhaust fans as three sets - QNL_TEF_B01, B02, B03 - each with 13 group-level points including ChOverSel and ChOverHrsSP (changeover select and hours). The ontology modelled only the six individual fans TEF-B01A/B, B02A/B, B03A/B, each feeding one toilet, and carried the three set entities as subjects typed para:Local_Status - a POINT class - sitting under entity:HVAC as if they were equipment, owned by nothing.</t>
         </is>
       </c>
       <c r="G39" s="11" t="inlineStr">
         <is>
-          <t>Recorded, not changed in this pass.</t>
+          <t>RESOLVED. Each set is now entity:QNL_TEF-B0n typed brick:Exhaust_Fan, carrying rec:locatedIn the plant room, rec:feeds BOTH toilets, brick:hasPart its two fans, and the LocSts point. The fans lost their isPartOf, locatedIn and single feeds rows - they inherit from the unit - and kept their five run/trip/command points and their own para:ratedExhaustAirFlowrate. The three para:Local_Status pseudo-equipment rows are gone. 24 rows dropped, 24 added.</t>
         </is>
       </c>
       <c r="H39" s="11" t="inlineStr">
         <is>
-          <t>OPEN, and two separate problems. (1) The three set entities exist in the sheet as entity:QNL_TEF_B01, _B02 and _B03 typed para:Local_Status - a POINT class - sitting directly under entity:HVAC as if they were equipment, each carrying one timeseries (LocSts) and no brick:hasPoint owner. They are orphan points wearing an equipment shape. (2) Their other 36 group-level points are absent from the sheet entirely. (3) The A/B split contradicts the changeover logic: TEF-B01A feeds B-046 Rest Room Men and TEF-B01B feeds B-047 Rest Room Women, but a duty/standby pair alternates on ONE duty, so either both fans extract from both toilets or the ChOver points do not belong to this pair. Same for B02 (B-032/B-033) and B03 (B-146/B-147). Needs the BMS drawings to settle.</t>
+          <t>Four independent sources agree these are TWIN-FAN units, not two fans serving a toilet each. (1) The O&amp;M manual states twin fans A and B. (2) The HVAC drawing shows one duct reaching TEF/B/01, with one riser splitting to serve both toilet blocks. (3) The BMS carries ChOverSel and ChOverHrsSP on the base tag - changeover between the twins. (4) The sheet's own nameplate data: one Nuaire model number per pair (AXT80P-413A, AXT71P-413A, AXT35M-211A) and IDENTICAL rated flow within each pair (1538/1538, 970/970, 400/400) - each fan sized for the full duty, which is duty/standby, not two rooms. The old model also invited a 2x airflow double-count, since A and B sat as sibling equipment each rated for the whole unit. Rated flow stays on the fans only, by client direction, so the unit total is not restated. The 36 remaining group-level points (ChOver, OccSchedule, FireAlm, RuntimeMtr, StartsCtr, TripCtr, Priority1/2, RemSts, ResetCmd, EnableDisableCmd) are still absent and remain open.</t>
         </is>
       </c>
       <c r="I39" s="11" t="inlineStr">
         <is>
-          <t>6 rows, 36 points missing</t>
+          <t>24 dropped, 24 added</t>
         </is>
       </c>
     </row>

--- a/projects/Assumption_Log.xlsx
+++ b/projects/Assumption_Log.xlsx
@@ -760,7 +760,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="8.21875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -2577,17 +2577,111 @@
       </c>
       <c r="G39" s="11" t="inlineStr">
         <is>
-          <t>RESOLVED. Each set is now entity:QNL_TEF-B0n typed brick:Exhaust_Fan, carrying rec:locatedIn the plant room, rec:feeds BOTH toilets, brick:hasPart its two fans, and the LocSts point. The fans lost their isPartOf, locatedIn and single feeds rows - they inherit from the unit - and kept their five run/trip/command points and their own para:ratedExhaustAirFlowrate. The three para:Local_Status pseudo-equipment rows are gone. 24 rows dropped, 24 added.</t>
+          <t>RESOLVED. Each set is now entity:QNL_TEF-B0n typed brick:Exhaust_Fan, carrying rec:locatedIn the plant room, rec:feeds BOTH toilets, brick:hasPart its two fans, and the LocSts point. The fans lost their isPartOf, locatedIn and single feeds rows - they inherit from the unit - and kept their five run/trip/command points and their own para:ratedExhaustAirFlowrate. The three para:Local_Status pseudo-equipment rows are gone. 24 rows dropped, 24 added. The 36 remaining group-level points were then added too (12 per set), so all 39 historian tags on the base TEF_B0n keys now resolve.</t>
         </is>
       </c>
       <c r="H39" s="11" t="inlineStr">
         <is>
-          <t>Four independent sources agree these are TWIN-FAN units, not two fans serving a toilet each. (1) The O&amp;M manual states twin fans A and B. (2) The HVAC drawing shows one duct reaching TEF/B/01, with one riser splitting to serve both toilet blocks. (3) The BMS carries ChOverSel and ChOverHrsSP on the base tag - changeover between the twins. (4) The sheet's own nameplate data: one Nuaire model number per pair (AXT80P-413A, AXT71P-413A, AXT35M-211A) and IDENTICAL rated flow within each pair (1538/1538, 970/970, 400/400) - each fan sized for the full duty, which is duty/standby, not two rooms. The old model also invited a 2x airflow double-count, since A and B sat as sibling equipment each rated for the whole unit. Rated flow stays on the fans only, by client direction, so the unit total is not restated. The 36 remaining group-level points (ChOver, OccSchedule, FireAlm, RuntimeMtr, StartsCtr, TripCtr, Priority1/2, RemSts, ResetCmd, EnableDisableCmd) are still absent and remain open.</t>
+          <t>Four independent sources agree these are TWIN-FAN units, not two fans serving a toilet each. (1) The O&amp;M manual states twin fans A and B. (2) The HVAC drawing shows one duct reaching TEF/B/01, with one riser splitting to serve both toilet blocks. (3) The BMS carries ChOverSel and ChOverHrsSP on the base tag - changeover between the twins. (4) The sheet's own nameplate data: one Nuaire model number per pair (AXT80P-413A, AXT71P-413A, AXT35M-211A) and IDENTICAL rated flow within each pair (1538/1538, 970/970, 400/400) - each fan sized for the full duty, which is duty/standby, not two rooms. The old model also invited a 2x airflow double-count, since A and B sat as sibling equipment each rated for the whole unit. Rated flow stays on the fans only, by client direction, so the unit total is not restated. All 39 group-level tags are now modelled.</t>
         </is>
       </c>
       <c r="I39" s="11" t="inlineStr">
         <is>
-          <t>24 dropped, 24 added</t>
+          <t>24 dropped, 96 added</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="11" t="inlineStr">
+        <is>
+          <t>QNL-046</t>
+        </is>
+      </c>
+      <c r="B40" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C40" s="13" t="inlineStr">
+        <is>
+          <t>Class</t>
+        </is>
+      </c>
+      <c r="D40" s="11" t="inlineStr">
+        <is>
+          <t>Points</t>
+        </is>
+      </c>
+      <c r="E40" s="11" t="inlineStr">
+        <is>
+          <t>4 new para: classes for the TEF group points</t>
+        </is>
+      </c>
+      <c r="F40" s="11" t="inlineStr">
+        <is>
+          <t>Twelve group-level points per twin-fan set needed classes. Eight resolved on the ladder; four had no match anywhere.</t>
+        </is>
+      </c>
+      <c r="G40" s="11" t="inlineStr">
+        <is>
+          <t>Coined para:Remote_Status (subClassOf brick:Status), para:Duty_Priority (brick:Parameter), para:Start_Count and para:Trip_Count (both brick:Point).</t>
+        </is>
+      </c>
+      <c r="H40" s="11" t="inlineStr">
+        <is>
+          <t>Ladder results, in order. Dar Cairo: brick:Fire_Alarm (54 uses). QNL itself: para:Changeover_Hours_Setpoint (15), brick:Reset_Command (4). Previous projects: brick:Occupancy_Status, on SSC 248 times and HQ 1522 - which is why OccSchedule is a Status and not brick:Occupancy_Command. Brick: brick:Lead_Lag_Command for ChOverSel (Brick defines it as enabling lead/lag operation, and the point reads Disable/Enable), brick:Enable_Command, and brick:On_Timer_Sensor for RuntimeMtr - the PREFERRED form, where Dar Cairo uses the brick:Run_Time_Sensor alias. The four coinages have no precedent in any of the four models. para:Start_Count and para:Trip_Count take brick:Point to match QNL's own para:Required_Units_Count and its four hours-duration classes; para:Remote_Status mirrors para:Local_Status.</t>
+        </is>
+      </c>
+      <c r="I40" s="11" t="inlineStr">
+        <is>
+          <t>4 declarations</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="11" t="inlineStr">
+        <is>
+          <t>QNL-047</t>
+        </is>
+      </c>
+      <c r="B41" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C41" s="13" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="D41" s="11" t="inlineStr">
+        <is>
+          <t>Points</t>
+        </is>
+      </c>
+      <c r="E41" s="11" t="inlineStr">
+        <is>
+          <t>50 per-fan historian tags on the TEFs</t>
+        </is>
+      </c>
+      <c r="F41" s="11" t="inlineStr">
+        <is>
+          <t>The historian carries 131 TEF tags. After the group-point pass, 81 resolve and 50 do not: FTSP, FTST, FltRst, RuntimeMtr, StartsCtr and TripCtr on each of the six twin fans and on TEF-101C and TEF-102C, plus RemSts on the two standalone fans.</t>
+        </is>
+      </c>
+      <c r="G41" s="11" t="inlineStr">
+        <is>
+          <t>Not added. Recorded as a scope question.</t>
+        </is>
+      </c>
+      <c r="H41" s="11" t="inlineStr">
+        <is>
+          <t>OPEN. These are per-FAN points, a different set from the 36 group points that were asked for and added. Under the skill's own rule an IO row with no point is a scope call, not a defect - the client decides whether the model needs them. Note FTSP and FTST are unexplained abbreviations; they want decoding before any class is chosen.</t>
+        </is>
+      </c>
+      <c r="I41" s="11" t="inlineStr">
+        <is>
+          <t>0 (50 pending)</t>
         </is>
       </c>
     </row>

--- a/projects/Assumption_Log.xlsx
+++ b/projects/Assumption_Log.xlsx
@@ -163,7 +163,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -215,6 +215,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -760,7 +763,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="8.21875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -2671,17 +2674,64 @@
       </c>
       <c r="G41" s="11" t="inlineStr">
         <is>
-          <t>Not added. Recorded as a scope question.</t>
+          <t>RESOLVED. All 50 added, with no new classes needed: FTSP -&gt; para:Fail_Stop_Alarm, FTST -&gt; para:Fail_Start_Alarm, FltRst -&gt; brick:Fault_Reset_Command, RuntimeMtr -&gt; brick:On_Timer_Sensor (unit:HR), StartsCtr -&gt; para:Start_Count, TripCtr -&gt; para:Trip_Count, RemSts -&gt; para:Remote_Status. All 131 historian TEF tags now resolve.</t>
         </is>
       </c>
       <c r="H41" s="11" t="inlineStr">
         <is>
-          <t>OPEN. These are per-FAN points, a different set from the 36 group points that were asked for and added. Under the skill's own rule an IO row with no point is a scope call, not a defect - the client decides whether the model needs them. Note FTSP and FTST are unexplained abbreviations; they want decoding before any class is chosen.</t>
+          <t>Client direction 2026-09-03. The two "unexplained" abbreviations were explained by the historian's own Description column, which had not been read closely enough: FTSP is "Fail to Stop Alarm" and FTST is "Fail to Start Alarm", both of which SSC had already coined para: classes for. The remaining five resolved on the ladder without coining anything new. These sit on the individual fans rather than the set, because the historian scopes them per fan: a runtime meter or starts counter is the evidence for duty/standby changeover, so averaging it at set level would destroy the one thing it is for.</t>
         </is>
       </c>
       <c r="I41" s="11" t="inlineStr">
         <is>
-          <t>0 (50 pending)</t>
+          <t>50 points, 200 rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="19" t="inlineStr">
+        <is>
+          <t>QNL-048</t>
+        </is>
+      </c>
+      <c r="B42" s="19" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C42" s="19" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="D42" s="19" t="inlineStr">
+        <is>
+          <t>Points</t>
+        </is>
+      </c>
+      <c r="E42" s="19" t="inlineStr">
+        <is>
+          <t>1,314 historian tags across 28 other equipment families</t>
+        </is>
+      </c>
+      <c r="F42" s="19" t="inlineStr">
+        <is>
+          <t>The cross-check that closed QNL-047 was run against the whole historian, not just the TEFs. The same seven suffixes (FTSP, FTST, FltRst, RuntimeMtr, StartsCtr, TripCtr, RemSts) appear on 28 other equipment families and are not modelled: VAV 247, AHU 146, ELE 145, FCU 137, EF 136, DX 120, CCU 62, SEF 62, CAV 51, SurfaceWtr 45, CHW 29, KEF 28, and the rest in ones and twos.</t>
+        </is>
+      </c>
+      <c r="G42" s="19" t="inlineStr">
+        <is>
+          <t>Not added. Recorded as a scope question for the client.</t>
+        </is>
+      </c>
+      <c r="H42" s="19" t="inlineStr">
+        <is>
+          <t>OPEN, and the largest remaining gap in the sheet - 1,314 points, roughly 2,628 rows, against the 19,546 the sheet holds today. Every class is already settled by QNL-046 and QNL-047, so adding them is mechanical rather than a modelling exercise. It is left out deliberately, not by oversight: the skill treats an IO row with no point as a scope call for the client, and adding 2,628 rows on our own initiative would be a material widening of what was asked for.</t>
+        </is>
+      </c>
+      <c r="I42" s="19" t="inlineStr">
+        <is>
+          <t>0 (1,314 pending)</t>
         </is>
       </c>
     </row>

--- a/projects/Assumption_Log.xlsx
+++ b/projects/Assumption_Log.xlsx
@@ -763,7 +763,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I42"/>
+  <dimension ref="A1:I44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="8.21875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -2627,17 +2627,17 @@
       </c>
       <c r="G40" s="11" t="inlineStr">
         <is>
-          <t>Coined para:Remote_Status (subClassOf brick:Status), para:Duty_Priority (brick:Parameter), para:Start_Count and para:Trip_Count (both brick:Point).</t>
+          <t>REVERSED. All four classes were coined for TEF group points that are not on Selected_PARA_OS_Data_Points_v4.0, so the points and the four declarations were removed together. No para: class was left orphaned.</t>
         </is>
       </c>
       <c r="H40" s="11" t="inlineStr">
         <is>
-          <t>Ladder results, in order. Dar Cairo: brick:Fire_Alarm (54 uses). QNL itself: para:Changeover_Hours_Setpoint (15), brick:Reset_Command (4). Previous projects: brick:Occupancy_Status, on SSC 248 times and HQ 1522 - which is why OccSchedule is a Status and not brick:Occupancy_Command. Brick: brick:Lead_Lag_Command for ChOverSel (Brick defines it as enabling lead/lag operation, and the point reads Disable/Enable), brick:Enable_Command, and brick:On_Timer_Sensor for RuntimeMtr - the PREFERRED form, where Dar Cairo uses the brick:Run_Time_Sensor alias. The four coinages have no precedent in any of the four models. para:Start_Count and para:Trip_Count take brick:Point to match QNL's own para:Required_Units_Count and its four hours-duration classes; para:Remote_Status mirrors para:Local_Status.</t>
+          <t>Client direction 2026-09-04: the sheet's points must match the selected datapoint list. The ladder work stands and is recorded here in case the client later adds these tags to the selection - the classes would be re-declared exactly as coined.</t>
         </is>
       </c>
       <c r="I40" s="11" t="inlineStr">
         <is>
-          <t>4 declarations</t>
+          <t>4 declarations added then removed</t>
         </is>
       </c>
     </row>
@@ -2674,17 +2674,17 @@
       </c>
       <c r="G41" s="11" t="inlineStr">
         <is>
-          <t>RESOLVED. All 50 added, with no new classes needed: FTSP -&gt; para:Fail_Stop_Alarm, FTST -&gt; para:Fail_Start_Alarm, FltRst -&gt; brick:Fault_Reset_Command, RuntimeMtr -&gt; brick:On_Timer_Sensor (unit:HR), StartsCtr -&gt; para:Start_Count, TripCtr -&gt; para:Trip_Count, RemSts -&gt; para:Remote_Status. All 131 historian TEF tags now resolve.</t>
+          <t>REVERSED. The 50 were added, then removed: none of the seven suffixes (FTSP, FTST, FltRst, RuntimeMtr, StartsCtr, TripCtr, RemSts) appears on Selected_PARA_OS_Data_Points_v4.0. The selected list carries 45 TEF tags; the sheet had grown to 131.</t>
         </is>
       </c>
       <c r="H41" s="11" t="inlineStr">
         <is>
-          <t>Client direction 2026-09-03. The two "unexplained" abbreviations were explained by the historian's own Description column, which had not been read closely enough: FTSP is "Fail to Stop Alarm" and FTST is "Fail to Start Alarm", both of which SSC had already coined para: classes for. The remaining five resolved on the ladder without coining anything new. These sit on the individual fans rather than the set, because the historian scopes them per fan: a runtime meter or starts counter is the evidence for duty/standby changeover, so averaging it at set level would destroy the one thing it is for.</t>
+          <t>Client direction 2026-09-04. The historian is an inventory of what the BMS publishes; the selected list is what the integration was asked to deliver. They are not the same document and the second one is the scope authority. This should have been checked before the points were added, not after. The twin-fan structure itself is unaffected and is confirmed by the selected list, which names QNL_TEF_B01A and QNL_TEF_B01B as separate tag sets with QNL_TEF_B01.LocSts at the set.</t>
         </is>
       </c>
       <c r="I41" s="11" t="inlineStr">
         <is>
-          <t>50 points, 200 rows</t>
+          <t>50 added then removed</t>
         </is>
       </c>
     </row>
@@ -2721,17 +2721,111 @@
       </c>
       <c r="G42" s="19" t="inlineStr">
         <is>
-          <t>Not added. Recorded as a scope question for the client.</t>
+          <t>CLOSED - not needed. None of the 1,314 tags appears on Selected_PARA_OS_Data_Points_v4.0, so none is in scope. No rows added.</t>
         </is>
       </c>
       <c r="H42" s="19" t="inlineStr">
         <is>
-          <t>OPEN, and the largest remaining gap in the sheet - 1,314 points, roughly 2,628 rows, against the 19,546 the sheet holds today. Every class is already settled by QNL-046 and QNL-047, so adding them is mechanical rather than a modelling exercise. It is left out deliberately, not by oversight: the skill treats an IO row with no point as a scope call for the client, and adding 2,628 rows on our own initiative would be a material widening of what was asked for.</t>
+          <t>Client direction 2026-09-04. Verified by reconciling every timeseries id in the sheet against the selected list: 2,754 of 2,754 selected tags are present, and nothing selected is missing. The 1,314 are historian tags the integration was not asked to deliver.</t>
         </is>
       </c>
       <c r="I42" s="19" t="inlineStr">
         <is>
-          <t>0 (1,314 pending)</t>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="19" t="inlineStr">
+        <is>
+          <t>QNL-049</t>
+        </is>
+      </c>
+      <c r="B43" s="19" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C43" s="19" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="D43" s="19" t="inlineStr">
+        <is>
+          <t>Points</t>
+        </is>
+      </c>
+      <c r="E43" s="19" t="inlineStr">
+        <is>
+          <t>149 points pruned to match the selected datapoint list</t>
+        </is>
+      </c>
+      <c r="F43" s="19" t="inlineStr">
+        <is>
+          <t>Selected_PARA_OS_Data_Points_v4.0.xlsx carries 2,769 rows / 2,754 unique tags, all marked "Must Have". The sheet carried 149 points beyond it: 86 TEF (QNL-046 and QNL-047), 60 ELEC MFM daily/monthly rollups (KWDaily, KWMonthly, MWDaily, MWMonthly, kWhpreviousdatadaily, kWhpreviousdatamonthly on 10 MFM units, where the list selects only .KW and .KWh), and 3 on VAV_1F_S15_039S.</t>
+        </is>
+      </c>
+      <c r="G43" s="19" t="inlineStr">
+        <is>
+          <t>Removed all 149, plus the 4 para: class declarations left with no user. The sheet now reconciles exactly: 2,754 of 2,754 selected tags present, nothing selected missing, and one unselected id remaining by design.</t>
+        </is>
+      </c>
+      <c r="H43" s="19" t="inlineStr">
+        <is>
+          <t>Client direction 2026-09-04: the points must match the selected datapoints and nothing beyond. ContributionFraction is the one deliberate exception - it is an internal container the backend fills by calculation, so its absence from a list of BMS tags is expected rather than a selection gap. The MFM rollups are a second reason to drop rather than a reluctant one: daily and monthly kW/kWh are derived from the .KW and .KWh the list does select, and the virtual metering layer computes exactly those rollups, so carrying them as raw points would put two answers to the same question in the graph. Removals are listed in QNL_pruned_points.csv; the pruning is reproducible via projects/QNL/prune_to_selected.py.</t>
+        </is>
+      </c>
+      <c r="I43" s="19" t="inlineStr">
+        <is>
+          <t>149 points, 302 rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="19" t="inlineStr">
+        <is>
+          <t>QNL-050</t>
+        </is>
+      </c>
+      <c r="B44" s="19" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C44" s="19" t="inlineStr">
+        <is>
+          <t>Source conflict</t>
+        </is>
+      </c>
+      <c r="D44" s="19" t="inlineStr">
+        <is>
+          <t>Points</t>
+        </is>
+      </c>
+      <c r="E44" s="19" t="inlineStr">
+        <is>
+          <t>entity:QNL_VAV-1F-S15-039S - 3 points dropped, likely a gap in the selection</t>
+        </is>
+      </c>
+      <c r="F44" s="19" t="inlineStr">
+        <is>
+          <t>The asset register lists VAV_1F_S15_039S as a box in its own right, serving L1-048 Staff Office, distinct from VAV_1F_S15_039 which serves L1-002A Green Room. The historian carries 5 tags for it. Selected_PARA_OS_Data_Points_v4.0 carries none - it selects QNL_VAV_1F_S15_039.DmprPos / .DuctAirFlow / .EffectiveSP but no 039S equivalent.</t>
+        </is>
+      </c>
+      <c r="G44" s="19" t="inlineStr">
+        <is>
+          <t>Dropped the 3 points under QNL-049. The equipment entity is kept, with its location, feeds, isFedBy and IFC reference intact.</t>
+        </is>
+      </c>
+      <c r="H44" s="19" t="inlineStr">
+        <is>
+          <t>OPEN - flagged for the client rather than resolved. This looks like an omission in the selection, not a decision: the box is real, it serves a room no other box serves, and the near-identical 039 is selected. The consequence of leaving it as-is is that Staff Office L1-048 has no VAV telemetry in the delivered graph. Restoring the 3 points is a one-line change if the client confirms.</t>
+        </is>
+      </c>
+      <c r="I44" s="19" t="inlineStr">
+        <is>
+          <t>3 points dropped (restorable)</t>
         </is>
       </c>
     </row>

--- a/projects/Assumption_Log.xlsx
+++ b/projects/Assumption_Log.xlsx
@@ -2778,7 +2778,7 @@
       </c>
       <c r="I43" s="19" t="inlineStr">
         <is>
-          <t>149 points, 302 rows</t>
+          <t>146 points, 296 rows net (149 removed, 3 restored under QNL-050)</t>
         </is>
       </c>
     </row>
@@ -2815,17 +2815,17 @@
       </c>
       <c r="G44" s="19" t="inlineStr">
         <is>
-          <t>Dropped the 3 points under QNL-049. The equipment entity is kept, with its location, feeds, isFedBy and IFC reference intact.</t>
+          <t>Dropped the 3 points under QNL-049, then RESTORED them on client confirmation the same day. The equipment entity was kept intact throughout. prune_to_selected.py now exempts the three tags by name, so a re-run does not strip them again.</t>
         </is>
       </c>
       <c r="H44" s="19" t="inlineStr">
         <is>
-          <t>OPEN - flagged for the client rather than resolved. This looks like an omission in the selection, not a decision: the box is real, it serves a room no other box serves, and the near-identical 039 is selected. The consequence of leaving it as-is is that Staff Office L1-048 has no VAV telemetry in the delivered graph. Restoring the 3 points is a one-line change if the client confirms.</t>
+          <t>RESOLVED. Client direction 2026-09-04, confirming this was an omission in the selection rather than a decision: the box is real in the asset register, it serves a room no other box serves, and the near-identical 039 is selected. Leaving it out would have left Staff Office L1-048 with no VAV telemetry in the delivered graph. The sheet now carries four unselected ids, all exempt by name and for stated reasons: ContributionFraction plus these three.</t>
         </is>
       </c>
       <c r="I44" s="19" t="inlineStr">
         <is>
-          <t>3 points dropped (restorable)</t>
+          <t>3 points restored, 6 rows</t>
         </is>
       </c>
     </row>

--- a/projects/Assumption_Log.xlsx
+++ b/projects/Assumption_Log.xlsx
@@ -763,7 +763,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I44"/>
+  <dimension ref="A1:I45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="8.21875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -2627,12 +2627,12 @@
       </c>
       <c r="G40" s="11" t="inlineStr">
         <is>
-          <t>REVERSED. All four classes were coined for TEF group points that are not on Selected_PARA_OS_Data_Points_v4.0, so the points and the four declarations were removed together. No para: class was left orphaned.</t>
+          <t>RESTORED. The four classes are back with the group points they type: para:Duty_Priority, para:Remote_Status, para:Start_Count, para:Trip_Count.</t>
         </is>
       </c>
       <c r="H40" s="11" t="inlineStr">
         <is>
-          <t>Client direction 2026-09-04: the sheet's points must match the selected datapoint list. The ladder work stands and is recorded here in case the client later adds these tags to the selection - the classes would be re-declared exactly as coined.</t>
+          <t>Client direction 2026-09-04, overriding the selected list for the TEF family only (QNL-051). The ladder work recorded here was never in doubt - only whether the points it typed were in scope.</t>
         </is>
       </c>
       <c r="I40" s="11" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="G41" s="11" t="inlineStr">
         <is>
-          <t>REVERSED. The 50 were added, then removed: none of the seven suffixes (FTSP, FTST, FltRst, RuntimeMtr, StartsCtr, TripCtr, RemSts) appears on Selected_PARA_OS_Data_Points_v4.0. The selected list carries 45 TEF tags; the sheet had grown to 131.</t>
+          <t>RESTORED. All 50 per-fan points are back on the six twin fans and the two standalone fans.</t>
         </is>
       </c>
       <c r="H41" s="11" t="inlineStr">
         <is>
-          <t>Client direction 2026-09-04. The historian is an inventory of what the BMS publishes; the selected list is what the integration was asked to deliver. They are not the same document and the second one is the scope authority. This should have been checked before the points were added, not after. The twin-fan structure itself is unaffected and is confirmed by the selected list, which names QNL_TEF_B01A and QNL_TEF_B01B as separate tag sets with QNL_TEF_B01.LocSts at the set.</t>
+          <t>Client direction 2026-09-04 (QNL-051). The class resolutions stand as recorded: FTSP -&gt; para:Fail_Stop_Alarm, FTST -&gt; para:Fail_Start_Alarm, FltRst -&gt; brick:Fault_Reset_Command, RuntimeMtr -&gt; brick:On_Timer_Sensor (unit:HR), StartsCtr -&gt; para:Start_Count, TripCtr -&gt; para:Trip_Count, RemSts -&gt; para:Remote_Status. All 131 historian TEF tags resolve again.</t>
         </is>
       </c>
       <c r="I41" s="11" t="inlineStr">
@@ -2778,7 +2778,7 @@
       </c>
       <c r="I43" s="19" t="inlineStr">
         <is>
-          <t>146 points, 296 rows net (149 removed, 3 restored under QNL-050)</t>
+          <t>60 points, 120 rows net (149 removed; 3 restored under QNL-050, 86 under QNL-051)</t>
         </is>
       </c>
     </row>
@@ -2826,6 +2826,53 @@
       <c r="I44" s="19" t="inlineStr">
         <is>
           <t>3 points restored, 6 rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="19" t="inlineStr">
+        <is>
+          <t>QNL-051</t>
+        </is>
+      </c>
+      <c r="B45" s="19" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="C45" s="19" t="inlineStr">
+        <is>
+          <t>Structure</t>
+        </is>
+      </c>
+      <c r="D45" s="19" t="inlineStr">
+        <is>
+          <t>Equipment / Points</t>
+        </is>
+      </c>
+      <c r="E45" s="19" t="inlineStr">
+        <is>
+          <t>entity:QNL_TEF-B01, -B02, -B03 and their six fans</t>
+        </is>
+      </c>
+      <c r="F45" s="19" t="inlineStr">
+        <is>
+          <t>The twin fans were typed brick:Exhaust_Fan - the same class as the unit they are part of - so a twin-fan set read as an exhaust fan containing two exhaust fans. Separately, 86 of the 131 historian TEF points had been pruned under QNL-049 for not being on the selected datapoint list.</t>
+        </is>
+      </c>
+      <c r="G45" s="19" t="inlineStr">
+        <is>
+          <t>Two changes, both TEF-only. (1) The six twin fans are retyped brick:Fan, on their own rows and as the objectType of the parent's brick:hasPart row - 84 rows. TEF-101C and TEF-102C are single standalone fans and stay brick:Exhaust_Fan units. (2) All 86 pruned points are restored with their 4 para: class declarations, so the TEFs carry all 131 historian tags again.</t>
+        </is>
+      </c>
+      <c r="H45" s="19" t="inlineStr">
+        <is>
+          <t>Client direction 2026-09-04. On the class: the ladder gives brick:Fan. Dar Cairo has no brick:Fan - its fan parts are an AHU's supply and exhaust fans, which is a different concept from a fan as a component. Brick 1.4 carries brick:Fan as a preferred term. QF HQ already uses exactly this shape - entity:HQ_CCU_B0001 brick:CRAC brick:hasPart entity:HQ_CCU_B0001_Fan brick:Fan, with the part carrying its own points - so it is step 3 precedent, not a coinage. On the points: this overrides the selected list for one family. The selected list keeps 45 TEF tags and drops the changeover setpoint, duty priorities, runtime meters and counters - which are precisely the evidence that a duty/standby pair is rotating, so a twin-fan set without them cannot be read at all. Every other family still matches the selection exactly. The override is enforced in prune_to_selected.py as a named family exemption, so a re-run does not strip them again. The consistency checker now reports more findings on brick:Exhaust_Fan (76, up from 46) because the five TEF units carry far more points than their 22 EF and KEF siblings - that is the family-uniformity check reporting a deliberate difference, not a defect.</t>
+        </is>
+      </c>
+      <c r="I45" s="19" t="inlineStr">
+        <is>
+          <t>86 points restored, 176 rows; 84 rows retyped</t>
         </is>
       </c>
     </row>

--- a/projects/Assumption_Log.xlsx
+++ b/projects/Assumption_Log.xlsx
@@ -16,7 +16,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'SSC'!$A$1:$I$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'HQ'!$A$1:$I$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'QNL'!$A$1:$I$37</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'RDC'!$A$1:$I$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'RDC'!$A$1:$I$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -25,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -37,10 +37,6 @@
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <color rgb="FF808080"/>
     </font>
   </fonts>
   <fills count="11">
@@ -122,7 +118,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -152,9 +148,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3095,7 +3088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8.21875" customWidth="1" min="1" max="1"/>
@@ -3157,22 +3150,592 @@
       </c>
     </row>
     <row r="2" ht="58.05" customHeight="1">
-      <c r="A2" s="11" t="inlineStr">
-        <is>
-          <t>(no entries yet)</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="n"/>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="n"/>
-      <c r="G2" s="2" t="n"/>
-      <c r="H2" s="2" t="n"/>
-      <c r="I2" s="2" t="n"/>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>RDC-001</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>All layers</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>The RDC BMS screen pass</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>RDC had no BMS screens and no drawings for the whole of this project - the reason its sheet stood empty. 47 screens have now been supplied, covering the North building, the South building, the Utility building and the pedestrian walkway between north and south.</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Traced every serving-area leader on all 47 and read the room each one ends in. 1,033 unit widgets were found; 410 of their leaders reach a dot. 305 of the 1,759 register rows now carry a reading - 90 agree with the register, 49 name a different room, 12 are the same room written two ways and 154 want a second look.</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>The screens are the live BMS graphic and the only as-built source RDC has. The tracer says where to look; every room was named by reading the screen.</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="3" ht="58.05" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>RDC-002</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>1,454 register rows with no reading</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Most RDC assets are not drawn as their own widget on any screen.</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Left column J empty and put the reason in column M, row by row: 1,373 have no screen covering them at all (the 644 AT air terminals are the bulk), 21 end in floor the screen does not name, 14 end on a wall between two rooms, 12 are in the unnamed penthouse and 1 leader could not be followed.</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>A blank with a reason is a question for the client. A guessed room is indistinguishable from a read one once it is in the sheet, and nobody can tell them apart afterwards.</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>1454</v>
+      </c>
+    </row>
+    <row r="4" ht="58.05" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>RDC-003</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>SB-AHU8031, 8032, 8033, 8034, 8035 and 8037</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>All six carry COMPUTER RESEARCH LAB S-1112 in the register.</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Did not overwrite. Recorded Mech S-0136 beside each and flagged all six.</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>All six leaders run into Mech S-0136, and they do so on two different screens - South GF-5 and South GF-7. Six units sharing one room where two independent screens put them in the plant room reads as a filled-down cell, not as six readings. SB-AHU8037 is the exception within the group: its leader goes to Cyber Server S-0138.</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" ht="58.05" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>RDC-004</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>49 units whose screen room differs from the register</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>The register room and the room the leader ends in name different places. 30 are in the north building, 17 in the south, 2 in the utility building.</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Did not overwrite. Wrote the screen room in column J and flagged the row.</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Two as-built sources disagree and neither is provably right - the screen is the live graphic, the register room came from the drawings. Both are recorded so the client can settle it.</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6" ht="58.05" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>RDC-005</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>154 units read with a caveat</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>The leader reaches a dot, but the dot sits on a wall between two rooms, or in open floor that carries a room name without a wall around it.</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Recorded the room and said in column M exactly what the caveat is.</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>These are readings, not guesses, but a reviewer should see the caveat rather than take the room on trust. They are filled green with the disagreements.</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="7" ht="58.05" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>RDC-006</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>Identifier</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Rooms</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>12 rooms named two ways</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>The register writes a first-floor room N-1143 where the screen writes N-143, and S-1159 where the screen writes S-0159 - the level digit differs and the number does not. The names are abbreviated differently too: Conf against Conference, Workstation against Work Station, TC3 against Tissue Culture 3, Mscopy1 against Mscope Room.</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Scored these CONVENTION rather than DIFF and flagged them. No room was changed.</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>They are the same room, not a disagreement about which room - reporting them as conflicts would have been wrong, and they did read as conflicts until the room number was compared apart from the level prefix. The ontology still has to use one spelling, which is why they are flagged.</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" ht="58.05" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>RDC-007</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Source defect</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Rooms</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>entity room name HY Room N-1404J</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>The register spells it HY Room; the BMS screen spells it HV Room.</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Left the register text as-is and raised it.</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>HV - high voltage - is the reading the screen supports and the one the rest of the estate uses. A single-letter difference in a room name is the kind of defect that survives every validator.</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" ht="58.05" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>RDC-008</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>Identifier</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Constant-volume terminals</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>The screens label them CAV and the register labels them AT. The register carries one CAV row against 510 AT rows.</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Joined CAV readings to AT rows on the unit number, and said so in column M on every row joined that way.</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>One CAV row against 510 AT rows says AT is the register word for the same thing. It is still an inference rather than a reading, so it is stated on the row rather than left to look like a plain match.</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" ht="58.05" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>RDC-009</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>Identifier</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>AHU tags, and RDC_NB_2F_2F_AHU8513</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>AHU tags carry no level segment where every other family does - RDC_UB_AHU8601, not RDC_UB_MF_AHU8601. One tag carries its level twice: RDC_NB_2F_2F_AHU8513.</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Made the join accept a level-less form, and left both tag shapes untouched.</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Asset tags are the BMS join key and are not ours to reshape. The doubled level segment is a typo in the register worth correcting at source.</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" ht="58.05" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>RDC-010</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Exhaust fans - the whole family</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>The register has no EF rows at all.</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Listed the nine read off the screens - SB-EF-8041 to 8044 and UB-EF-8642 to 8646 - with the room each serves, in the project README. They have no row in the sheet to carry a reading.</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>They are drawn and tagged on the BMS, so the historian has their points, and a register that omits them leaves those points unreachable. NB-EF-8553, NB-EF-8554 and the second-floor ERU units are absent for the same reason.</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" ht="58.05" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>RDC-011</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>CAV/CEV pairs 7590/7591, 7610/7611, 7760/7761</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Each pair is one widget on the screen. The register carries the CEV half and no CAV row.</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Recorded the reading against the CEV row and said so in column M.</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Losing the reading because half the pair is missing would hide both the reading and the gap.</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" ht="58.05" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>RDC-012</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Source defect</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Rooms</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>The second-floor penthouse screens</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>North SF-1 to SF-4 name only their electrical rooms and IDFs - Normal Elec. N-2107, Emer. Elec. N-2108, IDF N-2110 and their neighbours. The penthouse floor itself carries no room name at all.</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Left 12 units blank with that reason rather than inventing a name.</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>The leaders are clear and the dots are unambiguous; it is the room name that does not exist on the drawing. This is a question for the client, not a tracing failure.</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" ht="58.05" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>RDC-013</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>Structure</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Rooms</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>The double-height high bay spaces</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>CSP High Bay N-0215B, Machine Shop N-0215C and the Level 0 high bay labs are drawn on the ground floor screen and again on the first floor one.</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Took the register level rather than the screen level where the screen level matches no tag, and noted it on each row.</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>They run through both levels, so both screens show them; the units are ground floor units and the register has no first floor twin. Taking the level from the screen would have invented a tag that matches nothing and dropped the reading without a word.</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>7</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I2"/>
+  <autoFilter ref="A1:I14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/projects/Assumption_Log.xlsx
+++ b/projects/Assumption_Log.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'SSC'!$A$1:$I$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'HQ'!$A$1:$I$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'QNL'!$A$1:$I$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'QNL'!$A$1:$I$46</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'RDC'!$A$1:$I$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1388,7 +1388,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I45"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8.21875" customWidth="1" min="1" max="1"/>
@@ -3455,8 +3455,55 @@
         </is>
       </c>
     </row>
+    <row r="46" ht="58.05" customHeight="1">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>QNL-052</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="C46" s="8" t="inlineStr">
+        <is>
+          <t>Class</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Points</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>six Air Terminal contribution points on all 299 VAV and CAV</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>The client supplied six calculated points for every air terminal - cooling, heating and electrical, power demand and energy consumption - with timeseries ids AT_CWPWR_KWT_CALC, AT_CWPWR_KWHT_CALC, AT_HEATPWR_KWT_CALC, AT_HEATPWR_KWTH_CALC, AT_ELEC_KW_CALC and AT_ELEC_KWH_CALC. None of the six appears anywhere in the historian IO list (11,617 rows) or in Selected_PARA_OS_Data_Points_v4.0 (2,769 rows) - no exact match and no AT_, _CALC, CWPWR or HEATPWR pattern at all. The spec typed the two cooling points as brick:Electric_Power_Sensor and brick:Electrical_Energy_Usage_Sensor while giving both a thermal unit.</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>Added all six to all 299 terminals (247 VAV, 52 CAV) - 1,794 points, 3,588 rows. The cooling pair is corrected to brick:Thermal_Power_Sensor / para:KiloWt and brick:Thermal_Energy_Usage_Sensor / para:KiloWt-HR, matching the heating pair. The other four are as specified. Each point carries the fixed timeseries id and the terminal's own para:hasEntityId, the same shape para:contributionFraction already uses.</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>Client direction 2026-09-07. On the absence from the IO list: these are calculated, not published - the _CALC suffix says so - and the skill's rule is that a calculated point's key comes from the calculation engine's register, not the IO list, exactly as ContributionFraction already does. The six ids are exempt by name in prune_to_selected.py so a re-run does not strip them. On the cooling classes: cooling is a thermal quantity and the tags themselves say so - CW is chilled water and KWT is thermal kW - while the heating pair beside them already used the thermal classes. Left as specified, a rollup filtering on class would have summed every terminal's chilled-water demand into the building's electrical demand, and been wrong with nothing to flag it - the inverse of the trap the skill already documents. Corrected on client direction. One thing NOT corrected: AT_CWPWR_KWHT_CALC and AT_HEATPWR_KWTH_CALC spell the same suffix two ways, KWHT against KWTH. One is almost certainly a typo, but both are join keys, so they are written verbatim as supplied and flagged rather than normalised.</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>1,794 points, 3,588 rows</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I45"/>
+  <autoFilter ref="A1:I46"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/projects/Assumption_Log.xlsx
+++ b/projects/Assumption_Log.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'SSC'!$A$1:$I$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'HQ'!$A$1:$I$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'QNL'!$A$1:$I$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'QNL'!$A$1:$I$48</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'RDC'!$A$1:$I$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1388,7 +1388,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I46"/>
+  <dimension ref="A1:I48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8.21875" customWidth="1" min="1" max="1"/>
@@ -3483,17 +3483,17 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>The client supplied six calculated points for every air terminal - cooling, heating and electrical, power demand and energy consumption - with timeseries ids AT_CWPWR_KWT_CALC, AT_CWPWR_KWHT_CALC, AT_HEATPWR_KWT_CALC, AT_HEATPWR_KWTH_CALC, AT_ELEC_KW_CALC and AT_ELEC_KWH_CALC. None of the six appears anywhere in the historian IO list (11,617 rows) or in Selected_PARA_OS_Data_Points_v4.0 (2,769 rows) - no exact match and no AT_, _CALC, CWPWR or HEATPWR pattern at all. The spec typed the two cooling points as brick:Electric_Power_Sensor and brick:Electrical_Energy_Usage_Sensor while giving both a thermal unit.</t>
+          <t>The client supplied six calculated points for every air terminal - cooling, heating and electrical, power demand and energy consumption - with timeseries ids AT_CWPWR_KWT_CALC, AT_CWPWR_KWHT_CALC, AT_HEATPWR_KWT_CALC, AT_HEATPWR_KWHT_CALC, AT_ELEC_KW_CALC and AT_ELEC_KWH_CALC. None of the six appears anywhere in the historian IO list (11,617 rows) or in Selected_PARA_OS_Data_Points_v4.0 (2,769 rows) - no exact match and no AT_, _CALC, CWPWR or HEATPWR pattern at all. The spec typed the two cooling points as brick:Electric_Power_Sensor and brick:Electrical_Energy_Usage_Sensor while giving both a thermal unit.</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Added all six to all 299 terminals (247 VAV, 52 CAV) - 1,794 points, 3,588 rows. The cooling pair is corrected to brick:Thermal_Power_Sensor / para:KiloWt and brick:Thermal_Energy_Usage_Sensor / para:KiloWt-HR, matching the heating pair. The other four are as specified. Each point carries the fixed timeseries id and the terminal's own para:hasEntityId, the same shape para:contributionFraction already uses.</t>
+          <t>Added all six to all 299 terminals (247 VAV, 52 CAV) - 1,794 points, 3,588 rows. The cooling pair is corrected to brick:Thermal_Power_Sensor / para:KiloWt and brick:Thermal_Energy_Usage_Sensor / para:KiloWt-HR, matching the heating pair. AT_HEATPWR_KWTH_CALC is corrected to AT_HEATPWR_KWHT_CALC. Each point carries the fixed timeseries id and the terminal's own para:hasEntityId, the same shape para:contributionFraction already uses.</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>Client direction 2026-09-07. On the absence from the IO list: these are calculated, not published - the _CALC suffix says so - and the skill's rule is that a calculated point's key comes from the calculation engine's register, not the IO list, exactly as ContributionFraction already does. The six ids are exempt by name in prune_to_selected.py so a re-run does not strip them. On the cooling classes: cooling is a thermal quantity and the tags themselves say so - CW is chilled water and KWT is thermal kW - while the heating pair beside them already used the thermal classes. Left as specified, a rollup filtering on class would have summed every terminal's chilled-water demand into the building's electrical demand, and been wrong with nothing to flag it - the inverse of the trap the skill already documents. Corrected on client direction. One thing NOT corrected: AT_CWPWR_KWHT_CALC and AT_HEATPWR_KWTH_CALC spell the same suffix two ways, KWHT against KWTH. One is almost certainly a typo, but both are join keys, so they are written verbatim as supplied and flagged rather than normalised.</t>
+          <t>Client direction 2026-09-07. On the absence from the IO list: these are calculated, not published - the _CALC suffix says so - and the skill's rule is that a calculated point's key comes from the calculation engine's register, not the IO list, exactly as ContributionFraction already does. The six ids are exempt by name in prune_to_selected.py so a re-run does not strip them. On the cooling classes: cooling is a thermal quantity and the tags themselves say so - CW is chilled water and KWT is thermal kW - while the heating pair beside them already used the thermal classes. Left as specified, a rollup filtering on class would have summed every terminal's chilled-water demand into the building's electrical demand, and been wrong with nothing to flag it - the inverse of the trap the skill already documents. On the units: all four are Dar Cairo's own - unit:KiloW (2,426 uses), unit:KiloW-HR (889), para:KiloWt (295), para:KiloWt-HR (318). The thermal pair is a para: extension rather than a QUDT unit because QUDT has no thermal kilowatt - a kilowatt is a kilowatt - and Dar Cairo coined the pair precisely so a demand rollup cannot add chilled-water kW to electrical kW. Brick does not define units at all; it points at QUDT, and QUDT's KiloW and KiloW-HR are unchanged between Brick 1.4 and the 1.5 release candidate.</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
@@ -3502,8 +3502,102 @@
         </is>
       </c>
     </row>
+    <row r="47" ht="58.05" customHeight="1">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>QNL-053</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>Source defect</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Points</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>AT_HEATPWR_KWTH_CALC, and the same misspelling in the virtual meter layer</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>Two timeseries ids spelled the same suffix two ways: AT_CWPWR_KWHT_CALC against AT_HEATPWR_KWTH_CALC. The same KWTH spelling had also been used in the virtual metering layer's proposed keys - CWPWR_KWTH_CALC and HWPWR_KWTH_CALC on the CHW and HW meters.</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>Corrected every occurrence to KWHT: 299 rows in the ontology (the air terminal heating energy point), 366 proposed keys in QNL_virtual_meter_timeseries_pending.csv, and the generators add_air_terminal_points.py and add_virtual_meters.py.</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>Client confirmation 2026-09-07 that KWHT is the correct spelling. The scope was wider than the point that raised it: the virtual metering layer had independently used KWTH for its CHW and HW consumption keys, so fixing only the air terminal point would have left the two layers disagreeing on the same suffix. Those 366 are proposed keys awaiting the calculation engine's register, not live join keys, so correcting them costs nothing and prevents the register being built against a misspelling.</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>299 ontology rows, 366 proposed keys</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="58.05" customHeight="1">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>QNL-054</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Points</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>entity:QNL_CAV-1F-S15-001 and entity:QNL_VAV-B-S13-005 - the two terminals with no contributionFraction</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>297 of the 299 air terminals carried para:contributionFraction; these two did not. Both are the assets retargeted from the building to a floor under QNL-044: the register gives them no room, so they carry rec:locatedIn a Level rather than a Room and no rec:isFedBy at all.</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>Added contributionFraction to both, at the head of their calculated block. All 299 terminals now carry it.</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>Client direction 2026-09-07. The omission was a side effect of how the contributionFraction pass was keyed - on equipment fedBy an AHU - and these two name no AHU because no source says which one serves them. That is a gap in the location and feeds data, not a reason to leave the point off: the backend apportions by calculation and does not read the isFedBy row, so a terminal with an unknown AHU still has a contribution to record. Leaving it off would have made two real terminals invisible to every apportioning view while looking complete. Both are real: the historian carries five tags for each.</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>2 points, 4 rows</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I46"/>
+  <autoFilter ref="A1:I48"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/projects/Assumption_Log.xlsx
+++ b/projects/Assumption_Log.xlsx
@@ -3488,12 +3488,12 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Added all six to all 299 terminals (247 VAV, 52 CAV) - 1,794 points, 3,588 rows. The cooling pair is corrected to brick:Thermal_Power_Sensor / para:KiloWt and brick:Thermal_Energy_Usage_Sensor / para:KiloWt-HR, matching the heating pair. AT_HEATPWR_KWTH_CALC is corrected to AT_HEATPWR_KWHT_CALC. Each point carries the fixed timeseries id and the terminal's own para:hasEntityId, the same shape para:contributionFraction already uses.</t>
+          <t>Added all six to all 299 terminals (247 VAV, 52 CAV) - 1,794 points, 3,588 rows. The cooling pair is corrected to brick:Thermal_Power_Sensor / para:KiloWt and brick:Thermal_Energy_Usage_Sensor / para:KiloWt-HR, matching the heating pair. AT_HEATPWR_KWTH_CALC is corrected to AT_HEATPWR_KWHT_CALC. Every name carries the Air Terminal prefix - entity:&lt;terminal&gt;_Air-Terminal-Cooling-Power-Demand-Contribution, labelled "Air Terminal Cooling Power Demand Contribution". Each point carries the fixed timeseries id and the terminal's own para:hasEntityId, the same shape para:contributionFraction already uses.</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>Client direction 2026-09-07. On the absence from the IO list: these are calculated, not published - the _CALC suffix says so - and the skill's rule is that a calculated point's key comes from the calculation engine's register, not the IO list, exactly as ContributionFraction already does. The six ids are exempt by name in prune_to_selected.py so a re-run does not strip them. On the cooling classes: cooling is a thermal quantity and the tags themselves say so - CW is chilled water and KWT is thermal kW - while the heating pair beside them already used the thermal classes. Left as specified, a rollup filtering on class would have summed every terminal's chilled-water demand into the building's electrical demand, and been wrong with nothing to flag it - the inverse of the trap the skill already documents. On the units: all four are Dar Cairo's own - unit:KiloW (2,426 uses), unit:KiloW-HR (889), para:KiloWt (295), para:KiloWt-HR (318). The thermal pair is a para: extension rather than a QUDT unit because QUDT has no thermal kilowatt - a kilowatt is a kilowatt - and Dar Cairo coined the pair precisely so a demand rollup cannot add chilled-water kW to electrical kW. Brick does not define units at all; it points at QUDT, and QUDT's KiloW and KiloW-HR are unchanged between Brick 1.4 and the 1.5 release candidate.</t>
+          <t>Client direction 2026-09-07. On the absence from the IO list: these are calculated, not published - the _CALC suffix says so - and the skill's rule is that a calculated point's key comes from the calculation engine's register, not the IO list, exactly as ContributionFraction already does. The six ids are exempt by name in prune_to_selected.py so a re-run does not strip them. On the cooling classes: cooling is a thermal quantity and the tags themselves say so - CW is chilled water and KWT is thermal kW - while the heating pair beside them already used the thermal classes. Left as specified, a rollup filtering on class would have summed every terminal's chilled-water demand into the building's electrical demand, and been wrong with nothing to flag it - the inverse of the trap the skill already documents. On the units: all four are Dar Cairo's own - unit:KiloW (2,426 uses), unit:KiloW-HR (889), para:KiloWt (295), para:KiloWt-HR (318). The thermal pair is a para: extension rather than a QUDT unit because QUDT has no thermal kilowatt - a kilowatt is a kilowatt - and Dar Cairo coined the pair precisely so a demand rollup cannot add chilled-water kW to electrical kW. Brick does not define units at all; it points at QUDT, and QUDT's KiloW and KiloW-HR are unchanged between Brick 1.4 and the 1.5 release candidate. On the names: the same six quantities exist at other layers - an AHU's cooling demand, the building's - so a point called only "Cooling Power Demand Contribution" does not say which layer a chart legend or tile is showing. The client's "AT" is written out as "Air Terminal" because an abbreviation in a point name becomes an abbreviation in the label a user reads, which intake exists to prevent. Identifier and label are generated from one map in add_air_terminal_points.py so the two cannot drift.</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">

--- a/projects/Assumption_Log.xlsx
+++ b/projects/Assumption_Log.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'SSC'!$A$1:$I$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'HQ'!$A$1:$I$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'QNL'!$A$1:$I$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'QNL'!$A$1:$I$50</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'RDC'!$A$1:$I$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1381,7 +1381,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I48"/>
+  <dimension ref="A1:I50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8.21875" customWidth="1" min="1" max="1"/>
@@ -3589,8 +3589,102 @@
         </is>
       </c>
     </row>
+    <row r="49" ht="58.05" customHeight="1">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>QNL-055</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="C49" s="8" t="inlineStr">
+        <is>
+          <t>Class</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Points</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>four para: subclasses on the 299 VAV/CAV air terminals</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>Brick gives cooling and heating the same two classes - brick:Thermal_Power_Sensor and brick:Thermal_Energy_Usage_Sensor - so on the air terminals the distinction survived only in the entity name and the timeseries id, where no query can reach it. None of the four proposed names exists in Dar Cairo, SSC V03, HQ 0.4 or the para registry.</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>Declared para:Cooling_Thermal_Power_Sensor and para:Heating_Thermal_Power_Sensor under brick:Thermal_Power_Sensor, and para:Cooling_Thermal_Energy_Usage_Sensor and para:Heating_Thermal_Energy_Usage_Sensor under brick:Thermal_Energy_Usage_Sensor. Retyped 1,196 points - 2,392 cells, since each point carries its class twice, as objectType on the parent's hasPoint row and as subjectType on its own reference row. Units unchanged: para:KiloWt / para:KiloWt-HR.</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>PROJECT OVERRIDE FOR QNL ONLY - client direction 2026-09-09, and deliberately not written into the skill. All three reference models use the plain Brick classes and the skill still says so; known-issues records the divergence as conflict 17. Scope is the air terminals alone, on the client's instruction: the 732 CHW/HW virtual meter points and the 7 points on entity:QNL_CHWS-MAIN-LOOP_Energy-Meter keep the Brick classes, so the sheet is half-migrated by design. The consequence is worth knowing before someone reports it as a defect: a query for para:Cooling_Thermal_Power_Sensor returns the terminals and not the CHW meters.</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>1,196 points, 2,392 cells; 4 declarations</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="58.05" customHeight="1">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>QNL-056</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>Source defect</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Points</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>the 2,920 virtual meter points had no ref:hasExternalReference row at all</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>Every ...-Virtual-Meter-Consumption and -Demand point existed only as the object of a brick:hasPoint row and was the subject of nothing - no reference row, no timeseries id, no entity id. All 2,920 proposed keys sat in QNL_virtual_meter_timeseries_pending.csv with the hasEntityId column blank on every one.</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>Wrote the missing 2,920 rows, one per point, and made the generator emit them so the block is eight rows rather than six. ref:hasTimeseriesId is Dar Cairo's token for the meter class; para:hasEntityId is the space the meter meters, underscored - QNL, QNL_L1, QNL_B_001A_Break_Out_Area - derived by the same helper the air terminal layer uses so the two cannot drift. The pending file survives as the calculation-engine team's checklist with both halves filled.</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>Client direction 2026-09-09. The cause was a wrong premise in the skill, which said the entityId 'is the historian's key for the space and nothing in the ontology can derive it', so the points shipped with no reference row. Dar Cairo disproves it: entity:Dar-Cairo_UPS-Util-Electrical-Virtual-Meter-Consumption carries UPS_KWH_CALC with para:hasEntityId 'Smart Village'. Dar Cairo's single site constant does not generalise - it has one meter per class, while QNL has 360 room-tier CHW meters that would all collide on one key - so the metered space is used instead. The keys are DERIVED, not confirmed against a register. A trap this created and closed in the same change: prune_to_selected.py matches on ref:hasTimeseriesId, so the meter points were invisible to it only while they had no key; a dry run after the rows landed removed 2,920 points and 5,840 rows. All 18 meter tokens are now exempt by name.</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>2,920 rows</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I48"/>
+  <autoFilter ref="A1:I50"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/projects/Assumption_Log.xlsx
+++ b/projects/Assumption_Log.xlsx
@@ -13,7 +13,7 @@
     <sheet name="RDC" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'SSC'!$A$1:$I$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'SSC'!$A$1:$I$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'HQ'!$A$1:$I$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'QNL'!$A$1:$I$50</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'RDC'!$A$1:$I$14</definedName>
@@ -515,7 +515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8.21875" customWidth="1" min="1" max="1"/>
@@ -846,8 +846,55 @@
         <v>0</v>
       </c>
     </row>
+    <row r="8" ht="58.05" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>SSC-007</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Source defect</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>References</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>QF_SSC_Ontology_V04.xlsx - 1,994 rdfs:label_en values</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>V04 arrived identical to V03 in every row, column, entity, class, predicate and unit. The only difference was 1,994 object-side rdfs:label_en values with their spaces deleted: Chilled Water Coil -&gt; ChilledWaterCoil, Qatar Foundation -&gt; QatarFoundation, Pre Filter and Bag Filter -&gt; PreFilterandBagFilter. 1,720 sat on brick:hasPoint rows, 273 on brick:hasPart, 1 on rec:isPartOf. Not one object-side label kept its spaces.</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Took V04 as the reference model and restored all 1,994 labels from V03, so the repo copy is content-identical to V03 under the new name. V03 removed. Every live pointer moved to V04 - CLAUDE.md, README.md, SKILL.md, class-resolution.md, known-issues.md and three project scripts - while the SSC project's own historical records keep saying V03, because they describe what was true when they were written. The vocab files were regenerated.</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Client direction 2026-09-09. Every changed value was exactly the V03 text minus spaces, which is a blind find-and-replace rather than a naming convention - a deliberate CamelCase would have capitalised the 'and' in PreFilterandBagFilter. rdfs:label_en is what the front end shows a user, and SSC is the house reference for the verbatim label style, so shipping it would have taught every future building to strip spaces from point names. THE REPO COPY THEREFORE DIVERGES FROM THE FILE AS SUPPLIED - raise it with whoever produces the SSC export, and expect a fresh export to carry the defect again until they fix it upstream.</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>1,994 labels restored</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I7"/>
+  <autoFilter ref="A1:I8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/projects/Assumption_Log.xlsx
+++ b/projects/Assumption_Log.xlsx
@@ -13,7 +13,7 @@
     <sheet name="RDC" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'SSC'!$A$1:$I$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'SSC'!$A$1:$I$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'HQ'!$A$1:$I$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'QNL'!$A$1:$I$50</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'RDC'!$A$1:$I$14</definedName>
@@ -68,6 +68,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00DEEAF6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
@@ -79,11 +84,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E4DFEC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00DEEAF6"/>
       </patternFill>
     </fill>
     <fill>
@@ -515,7 +515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8.21875" customWidth="1" min="1" max="1"/>
@@ -893,8 +893,243 @@
         </is>
       </c>
     </row>
+    <row r="9" ht="58.05" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>SSC-008</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Structure</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Metering</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>virtual metering layer, 696 meters</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>SSC carried no space-tier metering. Its 45 existing meters are equipment-tier - attached as brick:hasPart of a host AHU coil valve, FCU or CHW pump - and none of them says what space it covers.</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Generated the layer against the live sheet from a tier matrix: building only for Utility; building and floor for SPWR and Common-Util; building, floor and room for CHW, HVAC, LTG and Electrical. 1 building, 4 levels, 166 rooms gives 696 meters, 1,392 points and 5,568 rows, plus 13 class and unit declarations. Sheet 5,083 -&gt; 10,664 rows.</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Client direction 2026-09-09, after an input audit against SSC_Historian_IO_list_CP2.xlsx (5,751 tags) rather than the ontology alone - the sheet carries 46 electrical points where the IO list carries 398 power/energy tags. Evidence per class: Utility from SSC_MV_InACB, SSC_ELEC_MFM_MV_OG_I3.kW/.kWh and SSC_EnergyConsumptionCalc.kW; CHW from SSC_CHWConsumption.KWh plus 20 thermal points; HVAC from 22 AHU, 8 CHW pump and 49 MCC power tags; Electrical from 100 SMDB kW, 100 SMDB MWh and 110 MV tags. TWO CLASSES ARE BUILT WITHOUT SETTLED INPUTS AND ARE NOT DEFECTS TO BE REPORTED LATER: para:SPWR_Meter and para:Common_Util_Meter both draw on the 12 SMDB boards, and which board feeds small power or common areas needs the electrical schedule, which the client does not yet have. para:LTG_Meter HAS NO ENERGY INPUT AT ALL - SSC's 55 SSC_LCPB_* lighting circuits are every one an On/Off status with no kW or kWh - and was built at the client's direction to match QNL, which is in the same position; all 171 render empty until a lighting energy tag exists. para:HW_Meter was ELIMINATED: SSC's heating is electric (5 AHU heater commands, 14 CRAC heater statuses), there is no hot-water loop and no hot-water tag in 5,751 IO rows. A note on SPWR while it is fresh: it is SMALL POWER, not solar - Dar Cairo labels it 'Small Power Electrical Meter' - and auditing it as solar tests the wrong thing entirely.</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>696 meters, 5,568 rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58.05" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>SSC-009</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>Structure</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Metering</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>two metering conventions now coexist in one sheet</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>SSC attaches a meter as brick:hasPart of its host equipment. brick:meters appears 0 times in the delivered sheet, brick:isVirtualMeter 0 times, and there was no entity:Metering node - the string 'Metering' did not appear anywhere.</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>The new space-tier meters use the QNL / Dar Cairo convention instead: each meter is its own entity carrying brick:meters at the space it measures, brick:isVirtualMeter TRUE, and brick:isPartOf a newly declared entity:Metering. The 45 existing equipment-tier meters are left exactly as delivered.</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Client direction 2026-09-09. SSC's hasPart style cannot express 'meters this floor' - a space is not equipment - and the front end's metering tree needs a root, which entity:Metering supplies. The two conventions answer different questions and are not duplicates: the existing 45 meter equipment, the new 696 meter spaces. Anyone reading the sheet should expect both and not reconcile them.</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>696 meters on the new convention</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58.05" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>SSC-010</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Source defect</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Labels</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>5 rdfs:label_en values with trailing whitespace</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Rows 171, 300, 429, 560 and 691 carried 'Cooling Load Consumption ' with a trailing space, on the five AHU cooling-thermal meters. The validator reported them as E-WS-1, and they were present in the delivered sheet before any of this work.</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Stripped, as a side effect rather than a decision: the .xlsx reader added for this pass strips every cell on the way in. Errors fell from 10 to 5.</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Recorded because it is a change to delivered content that nobody asked for. It fixes a genuine error and the remaining 5 errors are all pre-existing and unrelated (one E-FEED-1 on entity:SSC_VAV0063, four E-TYP-3 for para: properties the registry does not define), but a silent edit to a reference model is exactly the thing that should be written down rather than discovered later.</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>5 labels</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58.05" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>SSC-011</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Metering</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>room-tier coverage, and para:contributionFraction</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>166 rooms now carry four room-tier meters each. But only 12 rooms contain a metered asset, and 82 rooms have no equipment inside them and none serving them. Of the 82 rooms that are served, 61 are served by a VAV, 9 by an FCU and 16 by a DX unit, CRAC or exhaust fan only.</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Built the room tier as instructed. para:contributionFraction was NOT added - the generator now takes it as a per-building flag and SSC's is off.</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>OPEN. contributionFraction is a separate question the client has to be asked, not a side effect of asking for meters. It is also the thing that would make the room tier real: SSC has 108 VAVs fed by an AHU and feeding 61 rooms, so adding it would give those 61 rooms an apportioned chilled-water share and turn their CHW meters into something that returns a number. It cannot rescue room-tier HVAC or Electrical, because SSC's VAVs carry no electrical point at all. The 16 rooms served only by DX, CRAC or exhaust fans cannot be rescued either - none of those classes carries a power or energy point in this building.</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>664 room-tier meters, 0 contributionFraction</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58.05" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>SSC-012</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Points</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>the electrical distribution layer is absent from the ontology</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>The IO list carries 398 power/energy tags; the ontology carries 46 electrical points. Missing entirely: the MV switchboard (SSC_MV_InACB and ~20 outgoing MCCBs), 12 SMDB boards with 100 kW and 100 MWh tags between them, and 10 MCCs. The only electrical equipment entity in the sheet is entity:SSC_MV_Generator.</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Not modelled. Recorded as the largest remaining gap.</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>OPEN. This is what the Utility, SPWR, Common-Util and Electrical meters would actually sum, so modelling it is what turns four of the new meter families from structurally correct into numerically meaningful. It would also give the floor tier real inputs - today Level-02 has no metered asset at all. Roughly 350 unmodelled power/energy tags, before counting the alarms and statuses on the same boards.</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>0 (398 tags, 46 modelled)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I8"/>
+  <autoFilter ref="A1:I13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1500,7 +1735,7 @@
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>Spelling</t>
         </is>
@@ -1545,7 +1780,7 @@
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="7" t="inlineStr">
         <is>
           <t>Spelling</t>
         </is>
@@ -1590,7 +1825,7 @@
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>Spelling</t>
         </is>
@@ -1635,7 +1870,7 @@
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>Spelling</t>
         </is>
@@ -1680,7 +1915,7 @@
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
@@ -1725,7 +1960,7 @@
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
@@ -1770,7 +2005,7 @@
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
@@ -1815,7 +2050,7 @@
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
@@ -1860,7 +2095,7 @@
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
@@ -1905,7 +2140,7 @@
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
@@ -1950,7 +2185,7 @@
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
@@ -1995,7 +2230,7 @@
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C13" s="9" t="inlineStr">
         <is>
           <t>Class</t>
         </is>
@@ -2040,7 +2275,7 @@
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
+      <c r="C14" s="9" t="inlineStr">
         <is>
           <t>Class</t>
         </is>
@@ -2175,7 +2410,7 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="C17" s="9" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>Structure</t>
         </is>
@@ -2220,7 +2455,7 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="C18" s="8" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
@@ -2445,7 +2680,7 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="C23" s="9" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
         <is>
           <t>Structure</t>
         </is>
@@ -2490,7 +2725,7 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="C24" s="7" t="inlineStr">
+      <c r="C24" s="8" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
@@ -2535,7 +2770,7 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="C25" s="9" t="inlineStr">
+      <c r="C25" s="6" t="inlineStr">
         <is>
           <t>Structure</t>
         </is>
@@ -2674,7 +2909,7 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr">
+      <c r="C28" s="8" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
@@ -2719,7 +2954,7 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="C29" s="9" t="inlineStr">
+      <c r="C29" s="6" t="inlineStr">
         <is>
           <t>Structure</t>
         </is>
@@ -2766,7 +3001,7 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="C30" s="9" t="inlineStr">
+      <c r="C30" s="6" t="inlineStr">
         <is>
           <t>Structure</t>
         </is>
@@ -2811,7 +3046,7 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="C31" s="8" t="inlineStr">
+      <c r="C31" s="9" t="inlineStr">
         <is>
           <t>Class</t>
         </is>
@@ -3179,7 +3414,7 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="C39" s="9" t="inlineStr">
+      <c r="C39" s="6" t="inlineStr">
         <is>
           <t>Structure</t>
         </is>
@@ -3226,7 +3461,7 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="C40" s="8" t="inlineStr">
+      <c r="C40" s="9" t="inlineStr">
         <is>
           <t>Class</t>
         </is>
@@ -3459,7 +3694,7 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="C45" s="9" t="inlineStr">
+      <c r="C45" s="6" t="inlineStr">
         <is>
           <t>Structure</t>
         </is>
@@ -3506,7 +3741,7 @@
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="C46" s="8" t="inlineStr">
+      <c r="C46" s="9" t="inlineStr">
         <is>
           <t>Class</t>
         </is>
@@ -3647,7 +3882,7 @@
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="C49" s="8" t="inlineStr">
+      <c r="C49" s="9" t="inlineStr">
         <is>
           <t>Class</t>
         </is>
@@ -4354,7 +4589,7 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>Structure</t>
         </is>

--- a/projects/Assumption_Log.xlsx
+++ b/projects/Assumption_Log.xlsx
@@ -916,7 +916,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>virtual metering layer, 696 meters</t>
+          <t>virtual metering layer, 695 meters</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Generated the layer against the live sheet from a tier matrix: building only for Utility; building and floor for SPWR and Common-Util; building, floor and room for CHW, HVAC, LTG and Electrical. 1 building, 4 levels, 166 rooms gives 696 meters, 1,392 points and 5,568 rows, plus 13 class and unit declarations. Sheet 5,083 -&gt; 10,664 rows.</t>
+          <t>Generated the layer against the live sheet from a tier matrix: building only for Utility; building and floor for SPWR and Common-Util; building, floor and room for CHW, HVAC, LTG and Electrical. 1 building, 4 levels, 166 rooms gives 695 meters, 1,390 points and 5,560 rows, plus 12 class and unit declarations. Sheet 5,083 -&gt; 10,655 rows.</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>696 meters, 5,568 rows</t>
+          <t>695 meters, 5,560 rows</t>
         </is>
       </c>
     </row>
@@ -978,12 +978,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Client direction 2026-09-09. SSC's hasPart style cannot express 'meters this floor' - a space is not equipment - and the front end's metering tree needs a root, which entity:Metering supplies. The two conventions answer different questions and are not duplicates: the existing 45 meter equipment, the new 696 meter spaces. Anyone reading the sheet should expect both and not reconcile them.</t>
+          <t>Client direction 2026-09-09. SSC's hasPart style cannot express 'meters this floor' - a space is not equipment - and the front end's metering tree needs a root, which entity:Metering supplies. The two conventions answer different questions and are not duplicates: the existing 45 meter equipment, the new 695 meter spaces. Anyone reading the sheet should expect both and not reconcile them.</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>696 meters on the new convention</t>
+          <t>695 meters on the new convention</t>
         </is>
       </c>
     </row>
@@ -2782,7 +2782,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>virtual metering layer, 1,460 meters</t>
+          <t>virtual metering layer, 1,459 meters</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -2802,7 +2802,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,760</t>
+          <t>11,672</t>
         </is>
       </c>
     </row>
@@ -3073,7 +3073,7 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Client direction 2026-09-03, reversing an earlier decision in this same log: a physical meter does not duplicate a virtual one. The physical meter reads what is actually imported at one point in the plant; the virtual meter is a calculated roll-up over a space. The gap between them is losses and unmetered load, and seeing that gap is the point. The generator now REPORTS overlaps (PHYSICAL_OVERLAP) rather than skipping them. Restores the meter count to 1,460.</t>
+          <t>Client direction 2026-09-03, reversing an earlier decision in this same log: a physical meter does not duplicate a virtual one. The physical meter reads what is actually imported at one point in the plant; the virtual meter is a calculated roll-up over a space. The gap between them is losses and unmetered load, and seeing that gap is the point. The generator now REPORTS overlaps (PHYSICAL_OVERLAP) rather than skipping them. Restores the meter count to 1,459.</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">

--- a/projects/Assumption_Log.xlsx
+++ b/projects/Assumption_Log.xlsx
@@ -13,7 +13,7 @@
     <sheet name="RDC" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'SSC'!$A$1:$I$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'SSC'!$A$1:$I$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'HQ'!$A$1:$I$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'QNL'!$A$1:$I$50</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'RDC'!$A$1:$I$14</definedName>
@@ -515,7 +515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8.21875" customWidth="1" min="1" max="1"/>
@@ -1128,8 +1128,55 @@
         </is>
       </c>
     </row>
+    <row r="14" ht="58.05" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>SSC-013</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>Structure</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Points</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>para:contributionFraction on all 108 VAVs</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>SSC has no per-terminal chilled water point. Its 108 VAVs carry air-side points only - flow, damper, temperature - so a room's share of its AHU's cooling load is not readable from the sheet, and the 171 room-tier CHW meters added with the metering layer had nothing to sum.</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Wrote para:contributionFraction on every one of the 108 VAVs, two rows each: the brick:hasPoint row carrying rdfs:label_en 'Contribution Fraction' and brick:hasUnit unit:UNITLESS, and a ref:hasExternalReference row carrying ref:hasTimeseriesId 'ContributionFraction' with para:hasEntityId read off the unit's own existing points. 216 rows, sheet 10,655 -&gt; 10,871. Generated with add_virtual_meters.py --code SSC --only-contribution, a flag added in the same commit so the points can be added to a sheet whose metering layer already landed.</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Client direction 2026-09-09, the same decision taken on QNL (QNL-036). It is a CONTAINER point, not a measurement: the backend replaces the ContributionFraction series with its own calculation apportioning the AHU's load across the units it feeds, which is what makes the room-tier CHW meters resolve to something. SSC needed none of QNL's exceptions - all 108 terminals are VAVs (there is no CAV), every one is fed by an AHU, every one has a rec:locatedIn, none sits in a shaft or riser, and every one already carried exactly one para:hasEntityId, so no id had to be derived and nothing was skipped. Coverage is still partial by design and should not be read as complete: 108 VAVs serve 61 of SSC's 166 rooms, so the room-tier CHW meters on the other 105 rooms remain empty, and the room-tier HVAC and Electrical meters cannot be rescued this way at all because SSC's VAVs carry no electrical point.</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>216 rows</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I13"/>
+  <autoFilter ref="A1:I14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/projects/Assumption_Log.xlsx
+++ b/projects/Assumption_Log.xlsx
@@ -13,9 +13,9 @@
     <sheet name="RDC" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'SSC'!$A$1:$I$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'SSC'!$A$1:$I$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'HQ'!$A$1:$I$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'QNL'!$A$1:$I$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'QNL'!$A$1:$I$51</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'RDC'!$A$1:$I$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -515,7 +515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8.21875" customWidth="1" min="1" max="1"/>
@@ -926,7 +926,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Generated the layer against the live sheet from a tier matrix: building only for Utility; building and floor for SPWR and Common-Util; building, floor and room for CHW, HVAC, LTG and Electrical. 1 building, 4 levels, 166 rooms gives 695 meters, 1,390 points and 5,560 rows, plus 12 class and unit declarations. Sheet 5,083 -&gt; 10,655 rows.</t>
+          <t>Generated the layer against the live sheet from a tier matrix: building only for Utility; building and floor for SPWR and Common-Util; building, floor and room for CHW, HVAC, LTG and Electrical. 1 building, 4 levels, 166 rooms gives 695 meters, 1,390 points and 5,560 rows, plus 11 class and unit declarations. Sheet 5,083 -&gt; 10,654 rows.</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Wrote para:contributionFraction on every one of the 108 VAVs, two rows each: the brick:hasPoint row carrying rdfs:label_en 'Contribution Fraction' and brick:hasUnit unit:UNITLESS, and a ref:hasExternalReference row carrying ref:hasTimeseriesId 'ContributionFraction' with para:hasEntityId read off the unit's own existing points. 216 rows, sheet 10,655 -&gt; 10,871. Generated with add_virtual_meters.py --code SSC --only-contribution, a flag added in the same commit so the points can be added to a sheet whose metering layer already landed.</t>
+          <t>Wrote para:contributionFraction on every one of the 108 VAVs, two rows each: the brick:hasPoint row carrying rdfs:label_en 'Contribution Fraction' and brick:hasUnit unit:UNITLESS, and a ref:hasExternalReference row carrying ref:hasTimeseriesId 'ContributionFraction' with para:hasEntityId read off the unit's own existing points. 216 rows, sheet 10,654 -&gt; 10,870. Generated with add_virtual_meters.py --code SSC --only-contribution, a flag added in the same commit so the points can be added to a sheet whose metering layer already landed.</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1175,8 +1175,149 @@
         </is>
       </c>
     </row>
+    <row r="15" ht="58.05" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>SSC-014</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Source defect</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Metering</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>a dangling para:HW_Meter class declaration</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>SSC's tier matrix never included para:HW_Meter - its heating is electric and 5,751 IO rows carry no hot-water tag - yet the sheet held a para:HW_Meter owl:Class row with no meter under it.</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Removed the declaration (1 row, sheet 10,871 -&gt; 10,870) and fixed the cause: build_declarations() now takes the building's tier matrix and emits only the classes that matrix uses, plus para:Metering_System, plus para:contributionFraction when the building asked for it, and the two thermal units only when the matrix has a THERMAL row.</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>This was the SECOND instance of one bug, not a one-off. build_declarations() emitted every entry in DECLARATIONS the sheet did not already declare, regardless of whether the matrix used it, so the same leak had already put a para:UPS_Meter declaration in a sheet whose matrix never asked for one. A dangling class reads to any reviewer as a deliberate modelling decision and is really an accident. The matrix is now the authority.</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>1 row</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58.05" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>SSC-015</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>Structure</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Points</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>the 20 delivered thermal meters collapsed onto their host, and heating added on the 5 AHU coils</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>SSC's 20 delivered thermal meters sat in a three-level chain - host --brick:hasPart--&gt; a Thermal_Power_Meter node --brick:hasPoint--&gt; the load points. All 20 are cooling: 5 on AHU cooling valves, 4 on CHW booster pumps, 11 on FCUs. The AHUs heat ELECTRICALLY, and their 5 brick:Heating_Coil entities carried nothing but a Heater_Command in unit:PERCENT.</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Collapsed the 20 meter nodes: the host now carries the points directly with brick:hasPoint, and the 20 brick:hasPart rows are gone (-20 rows). The 36 points were rehosted in place and retyped to para:Cooling_Thermal_Power_Sensor / para:Cooling_Thermal_Energy_Usage_Sensor (72 cells); their ref:hasExternalReference rows are subjected on the points, so every series carried over untouched and no point was renamed. Declared the four para: thermal subclasses, copied verbatim from QNL. Added Heating-Load-Demand and Heating-Load-Consumption on each of the 5 heating coils in the same collapsed shape - 10 points, 20 rows, each point with its reference row. Also corrected the 16 delivered CWPWR_KWTH_CALC keys to CWPWR_KWHT_CALC.</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Client direction 2026-09-09. Brick gives cooling and heating the same two classes - Thermal_Power_Sensor and Thermal_Energy_Usage_Sensor - so with both in one sheet the distinction survived only in the entity name and the tsid, where no query can reach it; the para: subclasses put it where a query can. FOUR THINGS A LATER READER SHOULD NOT TRY TO TIDY. (1) The 25 delivered ELECTRICAL meters keep their hasPart meter node - the collapse was scoped to thermal at the client's direction - so the sheet deliberately holds two shapes. (2) The 4 CHW-pump meters carry a power point only, no energy point. (3) Those 4 power points sit on LIVE historian tags (SSC_CHW_CHWP0N.ThermLoadFan), not _CALC keys. (4) The heating tokens HEATPWR_KWHT_CALC / HEATPWR_KWT_CALC are COINED: Dar Cairo has no heating token at all, neither HEATPWR nor HWPWR, so they mirror the client's own Air Terminal tags minus the AT_ prefix and are listed in the pending file for the calculation engine to confirm. THE HEATING METERS HAVE NO INPUT YET: the only heating point is a PERCENT command and there is no nameplate rating, so percent x rating is the whole formula and the AHU heater kW should be requested from the datasheets. The KWTH correction closed a split this project introduced - Dar Cairo and the 16 delivered rows write KWTH, the 171 space-tier rows generated here wrote KWHT - and KWHT everywhere is the client's standing decision.</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>24 rows, 72 cells retyped, 16 tokens corrected</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58.05" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>SSC-016</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>Structure</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Points</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>the six Air Terminal contribution points on all 108 VAVs</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>SSC's VAVs carried air-side points only - supply air flow, temperature, two setpoints, on/off, occupancy, operation hours and para:contributionFraction - and no container for the cooling, heating or electrical load apportioned down to them.</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Added the same six points QNL carries, on the same classes, units and client-supplied tokens: Air-Terminal-{Cooling,Heating}-{Power-Demand,Energy-Consumption}-Contribution on the para: thermal subclasses with para:KiloWt / para:KiloWt-HR, and the Electrical pair on brick:Electric_Power_Sensor / brick:Electrical_Energy_Usage_Sensor with unit:KiloW / unit:KiloW-HR. 108 units x 6 points x 2 rows = 1,296 rows, sheet 10,874 -&gt; 12,170. The POINTS table and the entity-id derivation are imported from projects/QNL/add_air_terminal_points.py rather than copied.</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Client direction 2026-09-09: all six, matching QNL, so one front-end template serves both buildings. SSC needed none of QNL's exceptions - all 108 terminals are VAVs (there is no CAV), and every one already carried exactly one para:hasEntityId, so no id was derived and nothing was skipped. STATE THIS IN THE HANDOVER RATHER THAN LEAVING IT TO BE FOUND: SSC's VAVs carry NO electrical point of any kind, so the Electrical pair are containers with nothing behind them until the backend calculates them. QNL is in the same position. All six are calculated points, so the IO-list cross-check does not reach them; every one carries its ref:hasExternalReference row, which is what stops them shipping inert.</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>1,296 rows</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I14"/>
+  <autoFilter ref="A1:I17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1710,7 +1851,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8.21875" customWidth="1" min="1" max="1"/>
@@ -2829,7 +2970,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>virtual metering layer, 1,459 meters</t>
+          <t>virtual metering layer, 1,453 meters</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -2849,7 +2990,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,672</t>
+          <t>11,624</t>
         </is>
       </c>
     </row>
@@ -3120,7 +3261,7 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Client direction 2026-09-03, reversing an earlier decision in this same log: a physical meter does not duplicate a virtual one. The physical meter reads what is actually imported at one point in the plant; the virtual meter is a calculated roll-up over a space. The gap between them is losses and unmetered load, and seeing that gap is the point. The generator now REPORTS overlaps (PHYSICAL_OVERLAP) rather than skipping them. Restores the meter count to 1,459.</t>
+          <t>Client direction 2026-09-03, reversing an earlier decision in this same log: a physical meter does not duplicate a virtual one. The physical meter reads what is actually imported at one point in the plant; the virtual meter is a calculated roll-up over a space. The gap between them is losses and unmetered load, and seeing that gap is the point. The generator now REPORTS overlaps (PHYSICAL_OVERLAP) rather than skipping them. Restores the meter count to 1,453.</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -4012,8 +4153,55 @@
         </is>
       </c>
     </row>
+    <row r="51" ht="58.05" customHeight="1">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>QNL-057</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>Structure</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Metering</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>para:HW_Meter, 6 building and floor tier meters</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>The tier matrix ticked para:HW_Meter at building and floor, so 6 meters and 12 points were generated. HW is DOMESTIC HOT WATER. QNL's ontology carries no hot-water equipment at all, and its historian carries one DHW asset - a calorifier, with QNL_Calorifier_HiTempFlt.Alm, QNL_Calorifier_LowWtrFlt.Alm and QNL_Calorifier_SupTemp.PV. Two alarms and a temperature.</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>Removed all 6 meters, their 12 points and the para:HW_Meter class declaration - 49 rows, sheet 25,933 -&gt; 25,884, meters 1,459 -&gt; 1,453. Dropped the class from METER_TYPES and DECLARATIONS, and HWPWR_KWHT_CALC / HWPWR_KWT_CALC from the pruner's exemptions. The 12 keys came out of the pending file so the calculation engine is not asked to build a series for a meter that is gone.</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>Client direction 2026-09-09. The reason matters more than the removal: the equipment EXISTS, it just has no energy point. A thermal meter needs kW or kWh, or flow and delta-T; two alarms and a supply temperature cannot be summed into one. The calorifier is also absent from Selected_PARA_OS_Data_Points_v4.0.xlsx, so it is correctly absent from the ontology - the selected list outranks the IO list on scope. These 6 meters had been summing nothing since the day they were generated. A HW meter becomes real here only if a calorifier energy point is added to the selected scope. TWO TRAPS IN THE REMOVAL, both of which validate clean afterwards: CHW-Power-Thermal-Virtual-Meter CONTAINS the substring HW-Power, so a substring match deletes all 360 CHW meters; and the two ref:hasExternalReference rows are subjected on the POINT, whose class column reads brick:Thermal_Power_Sensor, so matching on para:HW_Meter alone drops six rows of eight and orphans two. remove_meter_class.py anchors the suffix on the separator and keys on exact subjects.</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>49 rows</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I50"/>
+  <autoFilter ref="A1:I51"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/projects/Assumption_Log.xlsx
+++ b/projects/Assumption_Log.xlsx
@@ -13,7 +13,7 @@
     <sheet name="RDC" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'SSC'!$A$1:$I$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'SSC'!$A$1:$I$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'HQ'!$A$1:$I$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'QNL'!$A$1:$I$51</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'RDC'!$A$1:$I$14</definedName>
@@ -515,7 +515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8.21875" customWidth="1" min="1" max="1"/>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Client direction 2026-09-09. Brick gives cooling and heating the same two classes - Thermal_Power_Sensor and Thermal_Energy_Usage_Sensor - so with both in one sheet the distinction survived only in the entity name and the tsid, where no query can reach it; the para: subclasses put it where a query can. FOUR THINGS A LATER READER SHOULD NOT TRY TO TIDY. (1) The 25 delivered ELECTRICAL meters keep their hasPart meter node - the collapse was scoped to thermal at the client's direction - so the sheet deliberately holds two shapes. (2) The 4 CHW-pump meters carry a power point only, no energy point. (3) Those 4 power points sit on LIVE historian tags (SSC_CHW_CHWP0N.ThermLoadFan), not _CALC keys. (4) The heating tokens HEATPWR_KWHT_CALC / HEATPWR_KWT_CALC are COINED: Dar Cairo has no heating token at all, neither HEATPWR nor HWPWR, so they mirror the client's own Air Terminal tags minus the AT_ prefix and are listed in the pending file for the calculation engine to confirm. THE HEATING METERS HAVE NO INPUT YET: the only heating point is a PERCENT command and there is no nameplate rating, so percent x rating is the whole formula and the AHU heater kW should be requested from the datasheets. The KWTH correction closed a split this project introduced - Dar Cairo and the 16 delivered rows write KWTH, the 171 space-tier rows generated here wrote KWHT - and KWHT everywhere is the client's standing decision.</t>
+          <t>Client direction 2026-09-09. Brick gives cooling and heating the same two classes - Thermal_Power_Sensor and Thermal_Energy_Usage_Sensor - so with both in one sheet the distinction survived only in the entity name and the tsid, where no query can reach it; the para: subclasses put it where a query can. FOUR THINGS A LATER READER SHOULD NOT TRY TO TIDY. (1) The 25 delivered ELECTRICAL meters kept their hasPart meter node in this pass, because the collapse was scoped to thermal; SSC-017 finished them the same day, so the two shapes did NOT become permanent - do not cite this entry as evidence that they coexist. (2) The 4 CHW-pump meters carry a power point only, no energy point. (3) Those 4 power points sit on LIVE historian tags (SSC_CHW_CHWP0N.ThermLoadFan), not _CALC keys. (4) The heating tokens HEATPWR_KWHT_CALC / HEATPWR_KWT_CALC are COINED: Dar Cairo has no heating token at all, neither HEATPWR nor HWPWR, so they mirror the client's own Air Terminal tags minus the AT_ prefix and are listed in the pending file for the calculation engine to confirm. THE HEATING METERS HAVE NO INPUT YET: the only heating point is a PERCENT command and there is no nameplate rating, so percent x rating is the whole formula and the AHU heater kW should be requested from the datasheets. The KWTH correction closed a split this project introduced - Dar Cairo and the 16 delivered rows write KWTH, the 171 space-tier rows generated here wrote KWHT - and KWHT everywhere is the client's standing decision.</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1316,8 +1316,149 @@
         </is>
       </c>
     </row>
+    <row r="18" ht="58.05" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>SSC-017</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>Structure</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Points</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>the remaining 25 electrical meter nodes collapsed, and why the FCUs get no heating meter</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>SSC-015 collapsed the 20 thermal meter nodes but was scoped to thermal, leaving 25 electrical meter nodes in the three-level host --hasPart--&gt; meter --hasPoint--&gt; point chain: 11 on FCUs, 10 on fan and pump Motors, 4 on CHW booster pumps. Separately, the question was raised of giving the FCUs the AHU treatment.</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Collapsed all 25: the host now carries the points directly, -25 rows, sheet 12,170 -&gt; 12,145. Electrical points stay on their host - FCU, Motor or pump - and were NOT pushed down to a sub-part, because an FCU's electrical draw is the whole unit rather than its coil. Their ref:hasExternalReference rows are subjected on the points, so every series carried over untouched. NO heating meter was built for the FCUs.</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Client direction 2026-09-09. The sheet now holds ONE shape: every meter point hangs off the equipment it measures, and no brick:hasPart row anywhere points at a Meter class. WHY THE FCUs GET NO HEATING METER, recorded so it is not re-litigated: an SSC FCU has exactly three parts - CHW-Coil (which carries CHW-Coil_Valve), SF (which carries SF_Motor), and its electrical meter. There is no heating coil and no heater command, unlike the 5 AHUs which each carry a real brick:Heating_Coil with a Heater_Command. The IO list carries 165 FCU tags and NOT ONE of them is a heating tag - the signature is RmTemp, EffectiveSP, OccCoolSP, StartCmd, alarms and calculated hours. SSC's FCUs are cooling only. A heating meter here would attach to nothing.</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>-25 rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58.05" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>SSC-018</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>Structure</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Points</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>FCU cooling load points moved onto their valve, and unit:KiloWHR corrected</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>After the thermal collapse the cooling load sat on three different hosts: an AHU's on its CHW-Coil_Valve, an FCU's on the FCU itself, a CHW pump's on the pump. FCUs have the identical CHW-Coil -&gt; CHW-Coil_Valve structure as AHUs, so the difference was an artefact of where each delivered meter had been attached. Separately, 12 rows carried brick:hasUnit unit:KiloWHR.</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Re-subjected the 22 FCU Cooling-Load-Consumption / -Demand hasPoint rows from entity:SSC_FCU000N to entity:SSC_FCU000N_CHW-Coil_Valve (brick:Cooling_Valve) - 22 cells, no row-count change - so cooling load points now sit on Cooling_Valve (32) and Chilled_Water_Booster_Pump (4), and no longer on Fan_Coil_Unit. Corrected unit:KiloWHR to unit:KiloW-HR on 12 rows.</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>Client direction 2026-09-09. One rule now holds across the sheet: the cooling load lives on the valve that meters it. POINT IDENTIFIERS WERE NOT CHANGED - they are already named off the unit (entity:SSC_FCU0001_Cooling-Load-Demand), and renaming them would break the para:hasEntityId join for no gain. Those 11 valve entities existed only as the object of their coil's hasPart row, subjects of nothing; this gives them their first content. On the unit: KiloWHR is not a QUDT unit, so it resolves to nothing and the converter has nothing to map. It was 12 rows, not the 11 first counted - the 11 FCU ElectricalConsumption points plus entity:SSC_MV_Generator_Energy, found while confirming the count. This clears part of the standing W-CON-19 finding, which now reads 2 units rather than 3; THE 10 unit:MegaW-HR ROWS IN THE SAME FINDING ARE A SEPARATE QUESTION AND WERE NOT TOUCHED.</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>22 cells re-subjected, 12 units corrected</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58.05" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>SSC-019</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>Source defect</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Points</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>6 timeseries references naming a point that is never declared</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>entity:SSC_AHUB0002_SA_P-Static-1, -2 and the same pair on AHUB0003 and AHUB0004 are each the SUBJECT of a ref:hasExternalReference row carrying a real historian tag (SSC_AHUB000N_SupAirDuctPrsRmt1.PV / Rmt2.PV) and the OBJECT of no brick:hasPoint row. Those three AHUs each publish two remote supply-air duct pressure tags but declare only one SA_P-Static point.</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>REPORTED, NOT FIXED. Found by a guard added to finish_meter_collapse.py, which asserts the collapse creates no new orphan and printed the 6 that were already there. The guard compares before against after rather than asserting zero, so the pre-existing 6 do not block the work and cannot grow unnoticed.</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Present in the delivered V04 and unchanged by any pass in this project - verified against the sheet as it stood before the metering layer landed. This is the MIRROR of the QNL-056 defect: there, points existed with no reference row and rendered empty tiles; here, references exist with no point, so a real historian tag is attached to nothing the graph can show. The fix is to declare the missing SA_P-Static-1 / -2 points on AHUB0002, 0003 and 0004 with brick:Static_Pressure_Sensor and unit:PA, matching AHUB0001's and AHUB0005's shape - but that is adding points, which needs client direction and an IO-list check, so it is left for them to call.</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>0 - reported only</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I17"/>
+  <autoFilter ref="A1:I20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/projects/Assumption_Log.xlsx
+++ b/projects/Assumption_Log.xlsx
@@ -13,7 +13,7 @@
     <sheet name="RDC" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'SSC'!$A$1:$I$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'SSC'!$A$1:$I$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'HQ'!$A$1:$I$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'QNL'!$A$1:$I$51</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'RDC'!$A$1:$I$14</definedName>
@@ -515,7 +515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8.21875" customWidth="1" min="1" max="1"/>
@@ -1443,7 +1443,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>REPORTED, NOT FIXED. Found by a guard added to finish_meter_collapse.py, which asserts the collapse creates no new orphan and printed the 6 that were already there. The guard compares before against after rather than asserting zero, so the pre-existing 6 do not block the work and cannot grow unnoticed.</t>
+          <t>Reported when found; FIXED the same day by SSC-020, which declares all six. Found by a guard added to finish_meter_collapse.py, which asserts the collapse creates no new orphan and printed the 6 that were already there. The guard compares before against after rather than asserting zero, so the pre-existing 6 do not block the work and cannot grow unnoticed.</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1457,8 +1457,55 @@
         </is>
       </c>
     </row>
+    <row r="21" ht="58.05" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>SSC-020</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Source defect</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Points</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>the 6 missing SA_P-Static-1 / -2 points declared on AHUB0002, 0003 and 0004</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>The defect SSC-019 recorded: each of those three AHUs carried a ref:hasExternalReference row subjected on entity:SSC_AHUB000N_SA_P-Static-1 and -2 with a real historian tag, and no brick:hasPoint row declared either point, so six live tags were attached to nothing the graph could show.</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>Declared all six, 6 rows, sheet 12,145 -&gt; 12,151. Each takes the class its OWN reference row already names - para:Static_Pressure_Sensor_01 / _02, both already declared in the sheet and both from Dar Cairo - with unit:PA and the delivered label convention 'Supply Air Duct Remote Pressure 01 / 02'. Orphan reference rows now 0. Validator warnings 1,013 -&gt; 1,007, the six W-PT-1 that cleared.</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>Client direction 2026-09-09. THE IO LIST SETTLES WHICH AHUs HAVE TWO SENSORS AND WHICH HAVE ONE, so nothing was guessed: AHUB0001 and AHUB0005 publish SupAirDuctPrsRmt1 only and their single SA_P-Static is already correct; AHUB0002, 0003 and 0004 publish Rmt1 AND Rmt2. The class had to match the reference row rather than be chosen on merit - the hasPoint row's objectType and the reference row's subjectType are the same point's class, and disagreeing would give it two. THREE THINGS FOUND WHILE DOING THIS AND DELIBERATELY NOT CHANGED, because each edits or deletes delivered data and is the client's call. (1) The bare entity:SSC_AHUB000N_SA_P-Static on those same three AHUs now duplicates the pair: three points for two sensors, and the bare one has no reference row at all - it is what W-CON-9 reports, and it will render a dead tile. (2) SSC declares para:Static_Pressure_Sensor_Remote_01 and _Remote_02, labelled 'Static Pressure Remote Sensor 01 / 02', and NOTHING uses them; they look like what these points were meant to carry, since the point labels read 'Supply Air Duct REMOTE Pressure', but switching means editing the subjectType on six delivered reference rows. (3) A SEPARATE AND MORE SERIOUS DEFECT: entity:SSC_AHUB0003_RA_P-Static and entity:SSC_AHUB0004_RA_P-Static both carry ref:hasTimeseriesId SSC_AHUB0001_RtnAirDuctPrs.PV - ANOTHER AHU'S SENSOR - under their own para:hasEntityId. AHUB0003 has its own SSC_AHUB0003_RtnAirDuctPrs.PV in the IO list and should point at it; AHUB0004 has no plain RtnAirDuctPrs tag at all, only RtnAirDuctPrs1 and 2, which its RA_P-Static_01 and _02 points already carry correctly, so its bare RA_P-Static has no tag of its own to point at. Left as delivered pending client direction: fixing (3) means rewriting a live join key.</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>6 rows</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I20"/>
+  <autoFilter ref="A1:I21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/projects/Assumption_Log.xlsx
+++ b/projects/Assumption_Log.xlsx
@@ -13,7 +13,7 @@
     <sheet name="RDC" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'SSC'!$A$1:$I$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'SSC'!$A$1:$I$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'HQ'!$A$1:$I$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'QNL'!$A$1:$I$51</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'RDC'!$A$1:$I$14</definedName>
@@ -515,7 +515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8.21875" customWidth="1" min="1" max="1"/>
@@ -1495,7 +1495,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Client direction 2026-09-09. THE IO LIST SETTLES WHICH AHUs HAVE TWO SENSORS AND WHICH HAVE ONE, so nothing was guessed: AHUB0001 and AHUB0005 publish SupAirDuctPrsRmt1 only and their single SA_P-Static is already correct; AHUB0002, 0003 and 0004 publish Rmt1 AND Rmt2. The class had to match the reference row rather than be chosen on merit - the hasPoint row's objectType and the reference row's subjectType are the same point's class, and disagreeing would give it two. THREE THINGS FOUND WHILE DOING THIS AND DELIBERATELY NOT CHANGED, because each edits or deletes delivered data and is the client's call. (1) The bare entity:SSC_AHUB000N_SA_P-Static on those same three AHUs now duplicates the pair: three points for two sensors, and the bare one has no reference row at all - it is what W-CON-9 reports, and it will render a dead tile. (2) SSC declares para:Static_Pressure_Sensor_Remote_01 and _Remote_02, labelled 'Static Pressure Remote Sensor 01 / 02', and NOTHING uses them; they look like what these points were meant to carry, since the point labels read 'Supply Air Duct REMOTE Pressure', but switching means editing the subjectType on six delivered reference rows. (3) A SEPARATE AND MORE SERIOUS DEFECT: entity:SSC_AHUB0003_RA_P-Static and entity:SSC_AHUB0004_RA_P-Static both carry ref:hasTimeseriesId SSC_AHUB0001_RtnAirDuctPrs.PV - ANOTHER AHU'S SENSOR - under their own para:hasEntityId. AHUB0003 has its own SSC_AHUB0003_RtnAirDuctPrs.PV in the IO list and should point at it; AHUB0004 has no plain RtnAirDuctPrs tag at all, only RtnAirDuctPrs1 and 2, which its RA_P-Static_01 and _02 points already carry correctly, so its bare RA_P-Static has no tag of its own to point at. Left as delivered pending client direction: fixing (3) means rewriting a live join key.</t>
+          <t>Client direction 2026-09-09. THE IO LIST SETTLES WHICH AHUs HAVE TWO SENSORS AND WHICH HAVE ONE, so nothing was guessed: AHUB0001 and AHUB0005 publish SupAirDuctPrsRmt1 only and their single SA_P-Static is already correct; AHUB0002, 0003 and 0004 publish Rmt1 AND Rmt2. The class had to match the reference row rather than be chosen on merit - the hasPoint row's objectType and the reference row's subjectType are the same point's class, and disagreeing would give it two. THREE THINGS FOUND WHILE DOING THIS AND NOT CHANGED IN THAT PASS. Items (1) and (3) were acted on the same day by SSC-021 - do not cite this entry as evidence they still stand. Only item (2), the unused _Remote_ classes, remains open. (1) The bare entity:SSC_AHUB000N_SA_P-Static on those same three AHUs now duplicates the pair: three points for two sensors, and the bare one has no reference row at all - it is what W-CON-9 reports, and it will render a dead tile. (2) SSC declares para:Static_Pressure_Sensor_Remote_01 and _Remote_02, labelled 'Static Pressure Remote Sensor 01 / 02', and NOTHING uses them; they look like what these points were meant to carry, since the point labels read 'Supply Air Duct REMOTE Pressure', but switching means editing the subjectType on six delivered reference rows. (3) A SEPARATE AND MORE SERIOUS DEFECT: entity:SSC_AHUB0003_RA_P-Static and entity:SSC_AHUB0004_RA_P-Static both carry ref:hasTimeseriesId SSC_AHUB0001_RtnAirDuctPrs.PV - ANOTHER AHU'S SENSOR - under their own para:hasEntityId. AHUB0003 has its own SSC_AHUB0003_RtnAirDuctPrs.PV in the IO list and should point at it; AHUB0004 has no plain RtnAirDuctPrs tag at all, only RtnAirDuctPrs1 and 2, which its RA_P-Static_01 and _02 points already carry correctly, so its bare RA_P-Static has no tag of its own to point at. Left as delivered pending client direction: fixing (3) means rewriting a live join key.</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -1504,8 +1504,55 @@
         </is>
       </c>
     </row>
+    <row r="22" ht="58.05" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>SSC-021</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>Source defect</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Points</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>AHU duct pressure points reconciled 1:1 against the IO list</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>The client supplied the 14 duct static-pressure PV tags the SSC historian carries. The sheet held 18 P-Static points against them: 13 covered a tag, 3 covered nothing, and 2 named ANOTHER AHU's tag. SSC_AHUB0003_RtnAirDuctPrs.PV was covered by nothing at all.</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Repointed entity:SSC_AHUB0003_RA_P-Static from SSC_AHUB0001_RtnAirDuctPrs.PV to its own SSC_AHUB0003_RtnAirDuctPrs.PV (1 cell), which closed the only gap. Removed 4 surplus points: entity:SSC_AHUB0002_SA_P-Static, entity:SSC_AHUB0003_SA_P-Static and entity:SSC_AHUB0004_SA_P-Static, none of which had a reference row at all, and entity:SSC_AHUB0004_RA_P-Static, which also carried AHUB0001's tag while its _01 and _02 already cover both of AHUB0004's real return sensors. 5 rows, sheet 12,151 -&gt; 12,146. The result is exactly 14 points for 14 tags, each naming its own AHU.</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Client direction 2026-09-09, driven off the IO list rather than off the sheet. THE ONE GAP WAS A WRONG VALUE, NOT A MISSING POINT - AHUB0003 was displaying AHUB0001's return pressure as its own while its real tag reached nothing, which no row-level check can see because the row is complete and well-formed. TWO TRAPS IN THE REMOVAL, both of which validate clean afterwards: entity:SSC_AHUB0004_RA_P-Static is a PREFIX of _RA_P-Static_01 and _02, which are correct, so a startswith match destroys both real return sensors; and AHUB0001 and AHUB0005 carry a bare _SA_P-Static of the same shape as the three removed, but theirs are CORRECT - one supply sensor each, reference row present. The script matches exact strings in both the subject and object columns, names its four targets, and asserts the four look-alikes survive. Findings cleared: W-CON-9 3 -&gt; 0, E-CON-1 12 -&gt; 11, validator warnings 1,007 -&gt; 1,004. STILL OPEN, unchanged: SSC declares para:Static_Pressure_Sensor_Remote_01 and _Remote_02 and nothing uses them; they look like what these points were meant to carry, but switching means editing the subjectType on six delivered reference rows.</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>5 rows, 1 tag corrected</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I21"/>
+  <autoFilter ref="A1:I22"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/projects/Assumption_Log.xlsx
+++ b/projects/Assumption_Log.xlsx
@@ -13,7 +13,7 @@
     <sheet name="RDC" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'SSC'!$A$1:$I$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'SSC'!$A$1:$I$23</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'HQ'!$A$1:$I$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'QNL'!$A$1:$I$51</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'RDC'!$A$1:$I$14</definedName>
@@ -73,17 +73,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00E4DFEC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E2EFDA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E4DFEC"/>
       </patternFill>
     </fill>
     <fill>
@@ -515,7 +515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8.21875" customWidth="1" min="1" max="1"/>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Client direction 2026-09-09, driven off the IO list rather than off the sheet. THE ONE GAP WAS A WRONG VALUE, NOT A MISSING POINT - AHUB0003 was displaying AHUB0001's return pressure as its own while its real tag reached nothing, which no row-level check can see because the row is complete and well-formed. TWO TRAPS IN THE REMOVAL, both of which validate clean afterwards: entity:SSC_AHUB0004_RA_P-Static is a PREFIX of _RA_P-Static_01 and _02, which are correct, so a startswith match destroys both real return sensors; and AHUB0001 and AHUB0005 carry a bare _SA_P-Static of the same shape as the three removed, but theirs are CORRECT - one supply sensor each, reference row present. The script matches exact strings in both the subject and object columns, names its four targets, and asserts the four look-alikes survive. Findings cleared: W-CON-9 3 -&gt; 0, E-CON-1 12 -&gt; 11, validator warnings 1,007 -&gt; 1,004. STILL OPEN, unchanged: SSC declares para:Static_Pressure_Sensor_Remote_01 and _Remote_02 and nothing uses them; they look like what these points were meant to carry, but switching means editing the subjectType on six delivered reference rows.</t>
+          <t>Client direction 2026-09-09, driven off the IO list rather than off the sheet. THE ONE GAP WAS A WRONG VALUE, NOT A MISSING POINT - AHUB0003 was displaying AHUB0001's return pressure as its own while its real tag reached nothing, which no row-level check can see because the row is complete and well-formed. TWO TRAPS IN THE REMOVAL, both of which validate clean afterwards: entity:SSC_AHUB0004_RA_P-Static is a PREFIX of _RA_P-Static_01 and _02, which are correct, so a startswith match destroys both real return sensors; and AHUB0001 and AHUB0005 carry a bare _SA_P-Static of the same shape as the three removed, but theirs are CORRECT - one supply sensor each, reference row present. The script matches exact strings in both the subject and object columns, names its four targets, and asserts the four look-alikes survive. Findings cleared: W-CON-9 3 -&gt; 0, E-CON-1 12 -&gt; 11, validator warnings 1,007 -&gt; 1,004. The unused para:Static_Pressure_Sensor_Remote_01 / _Remote_02 classes were CLOSED the same day by SSC-022 - this entry no longer has an open item.</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1551,8 +1551,55 @@
         </is>
       </c>
     </row>
+    <row r="23" ht="58.05" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>SSC-022</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>Class</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Points</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>the 6 remote supply duct pressure points moved onto the Remote classes</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>SSC coined para:Static_Pressure_Sensor_Remote_01 and _Remote_02, labelled 'Static Pressure Remote Sensor 01 / 02', and nothing ever used them. The six second-supply-sensor points on AHUB0002, 0003 and 0004 were typed para:Static_Pressure_Sensor_01 / _02 instead - Dar Cairo's NON-remote classes, both also declared in this sheet.</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>Retyped all six points to _Remote_01 / _Remote_02 - 12 cells, two per point - and removed the two now-unused para:Static_Pressure_Sensor_01 / _02 declarations. 2 rows, sheet 12,146 -&gt; 12,144.</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>Client direction 2026-09-09, and the evidence agrees: these ARE remote sensors. The IO tag is SupAirDuctPrsRmt1 / Rmt2 and the point label reads 'Supply Air Duct REMOTE Pressure', so the coined pair finally carries the concept it was created for and the sheet stops using a non-remote class for a remote sensor. BOTH CELLS PER POINT HAD TO MOVE TOGETHER: the class is the objectType of the brick:hasPoint row and the subjectType of the ref:hasExternalReference row, and changing one leaves the point with two classes. The script asserts both sides agree for every point and refuses to write otherwise. Removing the two declarations does NOT remove those classes from anywhere else - they are Dar Cairo's (para-classes.csv lines 190-191, sourced from DarCairo_V98.csv) and remain available to any other building; only this sheet stops declaring what it no longer uses. references/data/para-classes.csv was deliberately NOT regenerated: it attributes _01 / _02 to Dar Cairo, which is still true, and _Remote_01 / _Remote_02 to this sheet, which is still true.</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>12 cells, 2 rows</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I22"/>
+  <autoFilter ref="A1:I23"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2158,7 +2205,7 @@
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="C2" s="7" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>Spelling</t>
         </is>
@@ -2203,7 +2250,7 @@
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="C3" s="8" t="inlineStr">
         <is>
           <t>Spelling</t>
         </is>
@@ -2248,7 +2295,7 @@
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>Spelling</t>
         </is>
@@ -2293,7 +2340,7 @@
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>Spelling</t>
         </is>
@@ -2338,7 +2385,7 @@
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="9" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
@@ -2383,7 +2430,7 @@
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C7" s="9" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
@@ -2428,7 +2475,7 @@
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="9" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
@@ -2473,7 +2520,7 @@
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="9" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
@@ -2518,7 +2565,7 @@
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="9" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
@@ -2563,7 +2610,7 @@
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C11" s="9" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
@@ -2608,7 +2655,7 @@
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="9" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
@@ -2653,7 +2700,7 @@
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C13" s="7" t="inlineStr">
         <is>
           <t>Class</t>
         </is>
@@ -2698,7 +2745,7 @@
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="C14" s="7" t="inlineStr">
         <is>
           <t>Class</t>
         </is>
@@ -2878,7 +2925,7 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="C18" s="8" t="inlineStr">
+      <c r="C18" s="9" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
@@ -3148,7 +3195,7 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="C24" s="8" t="inlineStr">
+      <c r="C24" s="9" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
@@ -3332,7 +3379,7 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="C28" s="8" t="inlineStr">
+      <c r="C28" s="9" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
@@ -3469,7 +3516,7 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="C31" s="9" t="inlineStr">
+      <c r="C31" s="7" t="inlineStr">
         <is>
           <t>Class</t>
         </is>
@@ -3884,7 +3931,7 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="C40" s="9" t="inlineStr">
+      <c r="C40" s="7" t="inlineStr">
         <is>
           <t>Class</t>
         </is>
@@ -4164,7 +4211,7 @@
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="C46" s="9" t="inlineStr">
+      <c r="C46" s="7" t="inlineStr">
         <is>
           <t>Class</t>
         </is>
@@ -4305,7 +4352,7 @@
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="C49" s="9" t="inlineStr">
+      <c r="C49" s="7" t="inlineStr">
         <is>
           <t>Class</t>
         </is>
